--- a/formulario/F.O.091.GOCO Analise de Maturidade em Processos.xlsx
+++ b/formulario/F.O.091.GOCO Analise de Maturidade em Processos.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\maturidade-dashboard\formulario\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d23091b390d060c3/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4E440E7-81FF-4C88-A316-1A6A909419EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A4B7DE8-6887-409D-8597-06C3144DC7B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Documentos" sheetId="1" r:id="rId1"/>
-    <sheet name="Indicadores" sheetId="2" r:id="rId2"/>
+    <sheet name="Indicadores" sheetId="9" r:id="rId2"/>
     <sheet name="Treinamento" sheetId="3" r:id="rId3"/>
     <sheet name="Qualidade" sheetId="4" r:id="rId4"/>
     <sheet name="Resumo" sheetId="5" r:id="rId5"/>
@@ -23,27 +23,14 @@
     <sheet name="Como usar" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Documentos!$A$1:$P$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Documentos!$A$1:$P$49</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="286">
   <si>
     <t>ID Avaliação</t>
   </si>
@@ -195,27 +182,6 @@
     <t>Equipe de processos</t>
   </si>
   <si>
-    <t>D.C.232.EXTE - Reclamações de boletos</t>
-  </si>
-  <si>
-    <t>NC 01: divergências de versão e data; o relatório não identifica a frente, o processo nem a data válida.</t>
-  </si>
-  <si>
-    <t>Documento de encerramento de leasing — sem código</t>
-  </si>
-  <si>
-    <t>NC 02: documento existente sem código de identificação. Também não foi demonstrado critério formal para uso do processo manual.</t>
-  </si>
-  <si>
-    <t>Atribuir código, formalizar o critério de elegibilidade e exceção do processo manual, aprovar e publicar a versão vigente.</t>
-  </si>
-  <si>
-    <t>Supervisão do Banco Mobilize</t>
-  </si>
-  <si>
-    <t>Documento de rescisão de leasing — sem código</t>
-  </si>
-  <si>
     <t>Locadora — N1</t>
   </si>
   <si>
@@ -228,24 +194,6 @@
     <t>Corrigir as datas e validar a trilha de criação, modificação e aprovação no controle documental.</t>
   </si>
   <si>
-    <t>D.C.2480.EXTE</t>
-  </si>
-  <si>
-    <t>NC 04: documento atualizado sem alteração do controle de versão; a data da atualização não foi informada no relatório.</t>
-  </si>
-  <si>
-    <t>Regularizar o controle de versão e registrar a data, aprovação e comunicação da versão vigente.</t>
-  </si>
-  <si>
-    <t>D.C.1517.EXTE - Pró-rata e mensalidade</t>
-  </si>
-  <si>
-    <t>NC 05: controles de versão duplicados; o relatório não informa processo, frente ou data válida.</t>
-  </si>
-  <si>
-    <t>Eliminar a duplicidade, confirmar a versão vigente e atualizar o controle documental.</t>
-  </si>
-  <si>
     <t>Backoffice Locadora — N2</t>
   </si>
   <si>
@@ -258,15 +206,6 @@
     <t>Validar a classificação documental, o conteúdo, a versão vigente e o vínculo com o processo aplicável.</t>
   </si>
   <si>
-    <t>P.O.498.OPER - Orientação quanto a solicitação de cancelamento</t>
-  </si>
-  <si>
-    <t>A orientação relativa aos dias adicionais após cinco dias na devolução do veículo não foi localizada.</t>
-  </si>
-  <si>
-    <t>Elaborar ou localizar a orientação, aprovar, versionar e disponibilizar na Wiki vigente.</t>
-  </si>
-  <si>
     <t>Backoffice — Banco N2</t>
   </si>
   <si>
@@ -282,21 +221,6 @@
     <t>Jeferson Oliveira</t>
   </si>
   <si>
-    <t>D.C.017.EXTE - Imput da proposta Connect</t>
-  </si>
-  <si>
-    <t>Backoffice — Locadora N2</t>
-  </si>
-  <si>
-    <t>P.O.523.OPER - ORIENTAR QUANTO A SOLICITAÇÃO CONTESTAÇÃO - INFRAÇÃO TRÂNSITO</t>
-  </si>
-  <si>
-    <t>P.O.535.OPER - ORIENTAR QUANTO A SOLICITAÇÃO DE RECORRER A INFRAÇÃO</t>
-  </si>
-  <si>
-    <t>D.C.1337.EXTE -INFRAÇÕES DE TRÂNSITO</t>
-  </si>
-  <si>
     <t>I.T.179.OPER - ORIENTAR QUANTO A TRATATIVA DE CLIENTES VIA CHAT</t>
   </si>
   <si>
@@ -309,15 +233,6 @@
     <t>Gestão do Clube FIQ e Processos</t>
   </si>
   <si>
-    <t>I.T.176.OPER - ORIENTAR QUANTO A TRATATIVA DE INCENTIVO AO PORTAL</t>
-  </si>
-  <si>
-    <t>Wikis desatualizadas e ausência de classificação de criticidade consolidada para todos os processos.</t>
-  </si>
-  <si>
-    <t>D.C.587.OPER - SCRIPT DE INCENTIVO AO PORTAL</t>
-  </si>
-  <si>
     <t>Nome_Indicador</t>
   </si>
   <si>
@@ -333,66 +248,12 @@
     <t>Score Indicadores</t>
   </si>
   <si>
-    <t>SLA</t>
-  </si>
-  <si>
     <t>Automático</t>
   </si>
   <si>
-    <t>PCA (voz)</t>
-  </si>
-  <si>
-    <t>PCA (chat e whats)</t>
-  </si>
-  <si>
-    <t>TMA</t>
-  </si>
-  <si>
-    <t>CSAT</t>
-  </si>
-  <si>
-    <t>Monitoria</t>
-  </si>
-  <si>
-    <t>FCR</t>
-  </si>
-  <si>
-    <t>HC Logado</t>
-  </si>
-  <si>
-    <t>Hora Logada</t>
-  </si>
-  <si>
-    <t>Nivel de serviço</t>
-  </si>
-  <si>
-    <t>Quantidade de contatos ativos</t>
-  </si>
-  <si>
-    <t>Quantidade de clientes abordados</t>
-  </si>
-  <si>
-    <t>Conversão de retenção</t>
-  </si>
-  <si>
-    <t>Cadastro de acesso ao portal</t>
-  </si>
-  <si>
-    <t>ABS</t>
-  </si>
-  <si>
-    <t>T.O</t>
-  </si>
-  <si>
     <t>Não Conformidade Grave</t>
   </si>
   <si>
-    <t>PCA</t>
-  </si>
-  <si>
-    <t>TME</t>
-  </si>
-  <si>
     <t>Material de treinamento e reciclagem — Banco N1</t>
   </si>
   <si>
@@ -402,9 +263,6 @@
     <t>Versionar o material, vincular as fontes vigentes e completar a evidência individual da reciclagem.</t>
   </si>
   <si>
-    <t>Daniel da Silva</t>
-  </si>
-  <si>
     <t>Material e plano de treinamento — Locadora N1</t>
   </si>
   <si>
@@ -1021,6 +879,15 @@
   </si>
   <si>
     <t>A aba Resumo agora consolida o Score Documentação, Indicadores, Treinamento e Qualidade em um "Score Geral de Maturidade" (média dos 4 pilares).</t>
+  </si>
+  <si>
+    <t>Treinamento e Processos</t>
+  </si>
+  <si>
+    <t>Sube Aplicação</t>
+  </si>
+  <si>
+    <t>Monitoria — Infração</t>
   </si>
 </sst>
 </file>
@@ -1032,7 +899,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1118,6 +985,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1179,7 +1052,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1285,6 +1158,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1299,266 +1173,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="73">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="41">
     <dxf>
       <fill>
         <patternFill>
@@ -1723,21 +1349,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
+          <bgColor rgb="FFFCE4D6"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
+          <bgColor rgb="FFE2F0D9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1787,6 +1406,41 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2079,7 +1733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z61"/>
+  <dimension ref="A1:Z49"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
@@ -2208,34 +1862,34 @@
         <v>26</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>17</v>
       </c>
       <c r="L2" s="4">
-        <f t="shared" ref="L2:L33" si="0">IF(G2="","",IF(G2="SIM",1,0))</f>
+        <f t="shared" ref="L2:L21" si="0">IF(G2="","",IF(G2="SIM",1,0))</f>
         <v>1</v>
       </c>
       <c r="M2" s="4">
-        <f t="shared" ref="M2:M33" si="1">IF(H2="","",IF(H2="SIM",1,0))</f>
+        <f t="shared" ref="M2:M21" si="1">IF(H2="","",IF(H2="SIM",1,0))</f>
         <v>1</v>
       </c>
       <c r="N2" s="4">
-        <f t="shared" ref="N2:N33" si="2">IF(J2="","",IF(J2="SIM",1,0))</f>
-        <v>1</v>
+        <f t="shared" ref="N2:N21" si="2">IF(J2="","",IF(J2="SIM",1,0))</f>
+        <v>0</v>
       </c>
       <c r="O2" s="4" t="str">
-        <f t="shared" ref="O2:O7" si="3">IF(K2="","",IF(K2="Conformidade",1,IF(K2="Não conformidade",0,IF(K2="Não conformidade grave",-1,""))))</f>
+        <f t="shared" ref="O2:O3" si="3">IF(K2="","",IF(K2="Conformidade",1,IF(K2="Não conformidade",0,IF(K2="Não conformidade grave",-1,""))))</f>
         <v/>
       </c>
       <c r="P2" s="4">
         <f>IF(COUNTA(G2,H2,J2,K2)=0,"",ROUND(AVERAGE(L2:O2)*100,0))</f>
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="Q2" s="6">
-        <f t="shared" ref="Q2:Q33" si="4">IFERROR(AVERAGEIF(C$2:C$61,C2,P$2:P$61),"N/A")</f>
-        <v>86.764705882352942</v>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C2,P$2:P$49),"N/A")</f>
+        <v>76.8</v>
       </c>
       <c r="R2" t="s">
         <v>47</v>
@@ -2253,7 +1907,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>928734</v>
       </c>
@@ -2264,10 +1918,10 @@
         <v>22</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F3" s="4">
         <v>1</v>
@@ -2282,7 +1936,7 @@
         <v>26</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>17</v>
@@ -2297,7 +1951,7 @@
       </c>
       <c r="N3" s="4">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" s="4" t="str">
         <f t="shared" si="3"/>
@@ -2305,17 +1959,17 @@
       </c>
       <c r="P3" s="4">
         <f>IF(COUNTA(G3,H3,J3)=0,"",ROUND(AVERAGE(L3:O3)*100,0))</f>
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="Q3" s="6">
-        <f t="shared" si="4"/>
-        <v>86.764705882352942</v>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C3,P$2:P$49),"N/A")</f>
+        <v>76.8</v>
       </c>
       <c r="R3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="S3" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="T3" t="s">
         <v>49</v>
@@ -2327,7 +1981,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>928734</v>
       </c>
@@ -2338,10 +1992,10 @@
         <v>22</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F4" s="4">
         <v>1</v>
@@ -2352,7 +2006,7 @@
       <c r="H4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="36" t="s">
         <v>26</v>
       </c>
       <c r="J4" s="4" t="s">
@@ -2374,34 +2028,34 @@
         <v>1</v>
       </c>
       <c r="O4" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="O4:O27" si="4">IF(K4="","",IF(K4="Conformidade",1,IF(K4="Não Conformidade",0,IF(K4="Não Conformidade Grave",-1,""))))</f>
         <v>1</v>
       </c>
-      <c r="P4" s="4">
-        <f>IF(COUNTA(G4,H4,J4)=0,"",ROUND(AVERAGE(L4:O4)*100,0))</f>
+      <c r="P4" s="38">
+        <f t="shared" ref="P4:P26" si="5">IF(COUNTA(G4,H4,J4,K4)=0,"",ROUND(AVERAGE(L4:O4)*100,0))</f>
         <v>100</v>
       </c>
-      <c r="Q4" s="6">
-        <f t="shared" si="4"/>
-        <v>86.764705882352942</v>
+      <c r="Q4" s="39">
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C4,P$2:P$49),"N/A")</f>
+        <v>76.8</v>
       </c>
       <c r="R4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="S4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="T4" t="s">
-        <v>55</v>
-      </c>
-      <c r="U4" t="s">
+        <v>49</v>
+      </c>
+      <c r="U4" s="37" t="s">
         <v>32</v>
       </c>
       <c r="V4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>928734</v>
       </c>
@@ -2412,10 +2066,10 @@
         <v>22</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F5" s="4">
         <v>1</v>
@@ -2426,7 +2080,7 @@
       <c r="H5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="36" t="s">
         <v>26</v>
       </c>
       <c r="J5" s="4" t="s">
@@ -2448,27 +2102,27 @@
         <v>1</v>
       </c>
       <c r="O5" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="P5" s="4">
-        <f>IF(COUNTA(G5,H5,J5)=0,"",ROUND(AVERAGE(L5:O5)*100,0))</f>
+      <c r="P5" s="38">
+        <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="Q5" s="6">
-        <f t="shared" si="4"/>
-        <v>86.764705882352942</v>
+      <c r="Q5" s="39">
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C5,P$2:P$49),"N/A")</f>
+        <v>76.8</v>
       </c>
       <c r="R5" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="S5" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="T5" t="s">
-        <v>55</v>
-      </c>
-      <c r="U5" t="s">
+        <v>62</v>
+      </c>
+      <c r="U5" s="37" t="s">
         <v>32</v>
       </c>
       <c r="V5" t="s">
@@ -2486,10 +2140,10 @@
         <v>22</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F6" s="4">
         <v>1</v>
@@ -2498,16 +2152,16 @@
         <v>25</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="36" t="s">
         <v>26</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>25</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="L6" s="4">
         <f t="shared" si="0"/>
@@ -2515,34 +2169,34 @@
       </c>
       <c r="M6" s="4">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" s="4">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="O6" s="4">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="P6" s="4">
-        <f>IF(COUNTA(G6,H6,J6)=0,"",ROUND(AVERAGE(L6:O6)*100,0))</f>
-        <v>100</v>
-      </c>
-      <c r="Q6" s="6">
         <f t="shared" si="4"/>
-        <v>86.764705882352942</v>
+        <v>0</v>
+      </c>
+      <c r="P6" s="38">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="Q6" s="39">
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C6,P$2:P$49),"N/A")</f>
+        <v>76.8</v>
       </c>
       <c r="R6" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="S6" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="T6" t="s">
-        <v>49</v>
-      </c>
-      <c r="U6" t="s">
+        <v>66</v>
+      </c>
+      <c r="U6" s="37" t="s">
         <v>32</v>
       </c>
       <c r="V6" t="s">
@@ -2550,882 +2204,462 @@
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>928734</v>
-      </c>
-      <c r="B7" s="36">
-        <v>46283</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F7" s="4">
-        <v>1</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L7" s="4">
+      <c r="A7" s="4"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M7" s="4">
+        <v/>
+      </c>
+      <c r="M7" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="N7" s="4">
+        <v/>
+      </c>
+      <c r="N7" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="O7" s="4">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="P7" s="4">
-        <f t="shared" ref="P7:P38" si="5">IF(COUNTA(G7,H7,J7,K7)=0,"",ROUND(AVERAGE(L7:O7)*100,0))</f>
-        <v>100</v>
-      </c>
-      <c r="Q7" s="6">
+        <v/>
+      </c>
+      <c r="O7" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>86.764705882352942</v>
-      </c>
-      <c r="R7" t="s">
-        <v>62</v>
-      </c>
-      <c r="S7" t="s">
-        <v>63</v>
-      </c>
-      <c r="T7" t="s">
-        <v>49</v>
-      </c>
-      <c r="U7" t="s">
-        <v>32</v>
-      </c>
-      <c r="V7" t="s">
-        <v>33</v>
-      </c>
+        <v/>
+      </c>
+      <c r="P7" s="38" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="Q7" s="39" t="str">
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C7,P$2:P$49),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="U7" s="37"/>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <v>928734</v>
-      </c>
-      <c r="B8" s="36">
-        <v>46283</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F8" s="4">
-        <v>1</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L8" s="4">
+      <c r="A8" s="4"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M8" s="4">
+        <v/>
+      </c>
+      <c r="M8" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="N8" s="4">
+        <v/>
+      </c>
+      <c r="N8" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="O8" s="4">
-        <f t="shared" ref="O8:O39" si="6">IF(K8="","",IF(K8="Conformidade",1,IF(K8="Não Conformidade",0,IF(K8="Não Conformidade Grave",-1,""))))</f>
-        <v>1</v>
-      </c>
-      <c r="P8" s="38">
+        <v/>
+      </c>
+      <c r="O8" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="P8" s="38" t="str">
         <f t="shared" si="5"/>
-        <v>100</v>
-      </c>
-      <c r="Q8" s="39">
+        <v/>
+      </c>
+      <c r="Q8" s="39" t="str">
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C8,P$2:P$49),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="U8" s="37"/>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="M9" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="N9" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O9" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>86.764705882352942</v>
-      </c>
-      <c r="R8" t="s">
-        <v>65</v>
-      </c>
-      <c r="S8" t="s">
-        <v>66</v>
-      </c>
-      <c r="T8" t="s">
-        <v>49</v>
-      </c>
-      <c r="U8" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="V8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>928734</v>
-      </c>
-      <c r="B9" s="36">
-        <v>46283</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F9" s="4">
-        <v>1</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L9" s="4">
+        <v/>
+      </c>
+      <c r="P9" s="38" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="Q9" s="39" t="str">
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C9,P$2:P$49),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="U9" s="37"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M9" s="4">
+        <v/>
+      </c>
+      <c r="M10" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="N9" s="4">
+        <v/>
+      </c>
+      <c r="N10" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="O9" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="P9" s="38">
+        <v/>
+      </c>
+      <c r="O10" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="P10" s="38" t="str">
         <f t="shared" si="5"/>
-        <v>100</v>
-      </c>
-      <c r="Q9" s="39">
+        <v/>
+      </c>
+      <c r="Q10" s="39" t="str">
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C10,P$2:P$49),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="U10" s="37"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="M11" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="N11" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O11" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>86.764705882352942</v>
-      </c>
-      <c r="R9" t="s">
-        <v>69</v>
-      </c>
-      <c r="S9" t="s">
-        <v>70</v>
-      </c>
-      <c r="T9" t="s">
-        <v>49</v>
-      </c>
-      <c r="U9" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="V9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <v>928734</v>
-      </c>
-      <c r="B10" s="36">
-        <v>46283</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F10" s="4">
-        <v>1</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L10" s="4">
+        <v/>
+      </c>
+      <c r="P11" s="38" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="Q11" s="39" t="str">
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C11,P$2:P$49),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="U11" s="37"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M10" s="4">
+        <v/>
+      </c>
+      <c r="M12" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="N10" s="4">
+        <v/>
+      </c>
+      <c r="N12" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="O10" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="P10" s="38">
+        <v/>
+      </c>
+      <c r="O12" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="P12" s="38" t="str">
         <f t="shared" si="5"/>
-        <v>100</v>
-      </c>
-      <c r="Q10" s="39">
+        <v/>
+      </c>
+      <c r="Q12" s="39" t="str">
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C12,P$2:P$49),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="U12" s="37"/>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="M13" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="N13" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O13" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>86.764705882352942</v>
-      </c>
-      <c r="R10" t="s">
-        <v>72</v>
-      </c>
-      <c r="S10" t="s">
-        <v>73</v>
-      </c>
-      <c r="T10" t="s">
-        <v>49</v>
-      </c>
-      <c r="U10" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="V10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <v>928734</v>
-      </c>
-      <c r="B11" s="36">
-        <v>46283</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F11" s="4">
-        <v>1</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L11" s="4">
+        <v/>
+      </c>
+      <c r="P13" s="38" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="Q13" s="39" t="str">
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C13,P$2:P$49),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="U13" s="37"/>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="36"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M11" s="4">
+        <v/>
+      </c>
+      <c r="M14" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="N11" s="4">
+        <v/>
+      </c>
+      <c r="N14" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="O11" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="P11" s="38">
+        <v/>
+      </c>
+      <c r="O14" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="P14" s="38" t="str">
         <f t="shared" si="5"/>
-        <v>100</v>
-      </c>
-      <c r="Q11" s="39">
+        <v/>
+      </c>
+      <c r="Q14" s="39" t="str">
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C14,P$2:P$49),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="U14" s="37"/>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="M15" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="N15" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O15" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>86.764705882352942</v>
-      </c>
-      <c r="R11" t="s">
-        <v>76</v>
-      </c>
-      <c r="S11" t="s">
-        <v>77</v>
-      </c>
-      <c r="T11" t="s">
-        <v>78</v>
-      </c>
-      <c r="U11" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="V11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
-        <v>928734</v>
-      </c>
-      <c r="B12" s="36">
-        <v>46283</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F12" s="4">
-        <v>1</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L12" s="4">
+        <v/>
+      </c>
+      <c r="P15" s="38" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="Q15" s="39" t="str">
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C15,P$2:P$49),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="U15" s="37"/>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M12" s="4">
+        <v/>
+      </c>
+      <c r="M16" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="N12" s="4">
+        <v/>
+      </c>
+      <c r="N16" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="O12" s="4">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="P12" s="38">
+        <v/>
+      </c>
+      <c r="O16" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="P16" s="38" t="str">
         <f t="shared" si="5"/>
-        <v>100</v>
-      </c>
-      <c r="Q12" s="39">
+        <v/>
+      </c>
+      <c r="Q16" s="39" t="str">
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C16,P$2:P$49),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="U16" s="37"/>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="M17" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="N17" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="O17" s="4" t="str">
         <f t="shared" si="4"/>
-        <v>86.764705882352942</v>
-      </c>
-      <c r="S12" t="s">
-        <v>77</v>
-      </c>
-      <c r="T12" t="s">
-        <v>78</v>
-      </c>
-      <c r="U12" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="V12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <v>928734</v>
-      </c>
-      <c r="B13" s="36">
-        <v>46283</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F13" s="4">
-        <v>1</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L13" s="4">
+        <v/>
+      </c>
+      <c r="P17" s="38" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="Q17" s="39" t="str">
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C17,P$2:P$49),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="U17" s="37"/>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M13" s="4">
+        <v/>
+      </c>
+      <c r="M18" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="N13" s="4">
+        <v/>
+      </c>
+      <c r="N18" s="4" t="str">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="O13" s="4">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="P13" s="38">
+        <v/>
+      </c>
+      <c r="O18" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="P18" s="38" t="str">
         <f t="shared" si="5"/>
-        <v>100</v>
-      </c>
-      <c r="Q13" s="39">
-        <f t="shared" si="4"/>
-        <v>86.764705882352942</v>
-      </c>
-      <c r="S13" t="s">
-        <v>77</v>
-      </c>
-      <c r="T13" t="s">
-        <v>78</v>
-      </c>
-      <c r="U13" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="V13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
-        <v>928734</v>
-      </c>
-      <c r="B14" s="36">
-        <v>46283</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F14" s="4">
-        <v>1</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I14" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L14" s="4">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M14" s="4">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="N14" s="4">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="O14" s="4">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="P14" s="38">
-        <f t="shared" si="5"/>
-        <v>100</v>
-      </c>
-      <c r="Q14" s="39">
-        <f t="shared" si="4"/>
-        <v>86.764705882352942</v>
-      </c>
-      <c r="S14" t="s">
-        <v>77</v>
-      </c>
-      <c r="T14" t="s">
-        <v>78</v>
-      </c>
-      <c r="U14" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="V14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <v>928734</v>
-      </c>
-      <c r="B15" s="36">
-        <v>46283</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F15" s="4">
-        <v>1</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I15" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L15" s="4">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M15" s="4">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="N15" s="4">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="O15" s="4">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="P15" s="38">
-        <f t="shared" si="5"/>
-        <v>100</v>
-      </c>
-      <c r="Q15" s="39">
-        <f t="shared" si="4"/>
-        <v>86.764705882352942</v>
-      </c>
-      <c r="S15" t="s">
-        <v>77</v>
-      </c>
-      <c r="T15" t="s">
-        <v>78</v>
-      </c>
-      <c r="U15" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="V15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
-        <v>928734</v>
-      </c>
-      <c r="B16" s="36">
-        <v>46283</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F16" s="4">
-        <v>1</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I16" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L16" s="4">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M16" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N16" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O16" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P16" s="38">
-        <f t="shared" si="5"/>
-        <v>25</v>
-      </c>
-      <c r="Q16" s="39">
-        <f t="shared" si="4"/>
-        <v>86.764705882352942</v>
-      </c>
-      <c r="R16" t="s">
-        <v>85</v>
-      </c>
-      <c r="S16" t="s">
-        <v>86</v>
-      </c>
-      <c r="T16" t="s">
-        <v>87</v>
-      </c>
-      <c r="U16" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="V16" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
-        <v>928734</v>
-      </c>
-      <c r="B17" s="36">
-        <v>46283</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="F17" s="4">
-        <v>1</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I17" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L17" s="4">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M17" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N17" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O17" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P17" s="38">
-        <f t="shared" si="5"/>
-        <v>25</v>
-      </c>
-      <c r="Q17" s="39">
-        <f t="shared" si="4"/>
-        <v>86.764705882352942</v>
-      </c>
-      <c r="R17" t="s">
-        <v>89</v>
-      </c>
-      <c r="S17" t="s">
-        <v>86</v>
-      </c>
-      <c r="T17" t="s">
-        <v>87</v>
-      </c>
-      <c r="U17" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="V17" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
-        <v>928734</v>
-      </c>
-      <c r="B18" s="36">
-        <v>46283</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="F18" s="4">
-        <v>1</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I18" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L18" s="4">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M18" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N18" s="4">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P18" s="38">
-        <f t="shared" si="5"/>
-        <v>25</v>
-      </c>
-      <c r="Q18" s="39">
-        <f t="shared" si="4"/>
-        <v>86.764705882352942</v>
-      </c>
-      <c r="R18" t="s">
-        <v>89</v>
-      </c>
-      <c r="S18" t="s">
-        <v>86</v>
-      </c>
-      <c r="T18" t="s">
-        <v>87</v>
-      </c>
-      <c r="U18" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="V18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+      <c r="Q18" s="39" t="str">
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C18,P$2:P$49),"N/A")</f>
+        <v>N/A</v>
+      </c>
+      <c r="U18" s="37"/>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
       <c r="B19" s="36"/>
       <c r="C19" s="4"/>
@@ -3450,7 +2684,7 @@
         <v/>
       </c>
       <c r="O19" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P19" s="38" t="str">
@@ -3458,12 +2692,12 @@
         <v/>
       </c>
       <c r="Q19" s="39" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C19,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U19" s="37"/>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
       <c r="B20" s="36"/>
       <c r="C20" s="4"/>
@@ -3488,7 +2722,7 @@
         <v/>
       </c>
       <c r="O20" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P20" s="38" t="str">
@@ -3496,12 +2730,12 @@
         <v/>
       </c>
       <c r="Q20" s="39" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C20,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U20" s="37"/>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
       <c r="B21" s="36"/>
       <c r="C21" s="4"/>
@@ -3526,7 +2760,7 @@
         <v/>
       </c>
       <c r="O21" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P21" s="38" t="str">
@@ -3534,12 +2768,12 @@
         <v/>
       </c>
       <c r="Q21" s="39" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C21,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U21" s="37"/>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="B22" s="36"/>
       <c r="C22" s="4"/>
@@ -3552,19 +2786,19 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="L22:L49" si="6">IF(G22="","",IF(G22="SIM",1,0))</f>
         <v/>
       </c>
       <c r="M22" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="M22:M49" si="7">IF(H22="","",IF(H22="SIM",1,0))</f>
         <v/>
       </c>
       <c r="N22" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="N22:N49" si="8">IF(J22="","",IF(J22="SIM",1,0))</f>
         <v/>
       </c>
       <c r="O22" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P22" s="38" t="str">
@@ -3572,12 +2806,12 @@
         <v/>
       </c>
       <c r="Q22" s="39" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C22,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U22" s="37"/>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="36"/>
       <c r="C23" s="4"/>
@@ -3590,19 +2824,19 @@
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="M23" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N23" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="O23" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P23" s="38" t="str">
@@ -3610,12 +2844,12 @@
         <v/>
       </c>
       <c r="Q23" s="39" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C23,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U23" s="37"/>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="36"/>
       <c r="C24" s="4"/>
@@ -3628,19 +2862,19 @@
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="M24" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N24" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="O24" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P24" s="38" t="str">
@@ -3648,12 +2882,12 @@
         <v/>
       </c>
       <c r="Q24" s="39" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C24,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U24" s="37"/>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
       <c r="B25" s="36"/>
       <c r="C25" s="4"/>
@@ -3666,19 +2900,19 @@
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="M25" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N25" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="O25" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P25" s="38" t="str">
@@ -3686,12 +2920,12 @@
         <v/>
       </c>
       <c r="Q25" s="39" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C25,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U25" s="37"/>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
       <c r="B26" s="36"/>
       <c r="C26" s="4"/>
@@ -3704,19 +2938,19 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="M26" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N26" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="O26" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P26" s="38" t="str">
@@ -3724,12 +2958,12 @@
         <v/>
       </c>
       <c r="Q26" s="39" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C26,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U26" s="37"/>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
       <c r="B27" s="36"/>
       <c r="C27" s="4"/>
@@ -3742,32 +2976,32 @@
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="M27" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N27" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="O27" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P27" s="38" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="P27:P49" si="9">IF(COUNTA(G27,H27,J27,K27)=0,"",ROUND(AVERAGE(L27:O27)*100,0))</f>
         <v/>
       </c>
       <c r="Q27" s="39" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C27,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U27" s="37"/>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="36"/>
       <c r="C28" s="4"/>
@@ -3780,32 +3014,32 @@
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="M28" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N28" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="O28" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="O28:O49" si="10">IF(K28="","",IF(K28="Conformidade",1,IF(K28="Não Conformidade",0,IF(K28="Não Conformidade Grave",-1,""))))</f>
         <v/>
       </c>
       <c r="P28" s="38" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q28" s="39" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C28,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U28" s="37"/>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="36"/>
       <c r="C29" s="4"/>
@@ -3818,32 +3052,32 @@
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="M29" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N29" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="O29" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="P29" s="38" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q29" s="39" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C29,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U29" s="37"/>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
       <c r="B30" s="36"/>
       <c r="C30" s="4"/>
@@ -3856,32 +3090,32 @@
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="M30" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N30" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="O30" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="P30" s="38" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q30" s="39" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C30,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U30" s="37"/>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
       <c r="B31" s="36"/>
       <c r="C31" s="4"/>
@@ -3894,32 +3128,32 @@
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="M31" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N31" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="O31" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="P31" s="38" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q31" s="39" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C31,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U31" s="37"/>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="36"/>
       <c r="C32" s="4"/>
@@ -3932,27 +3166,27 @@
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
       <c r="L32" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="M32" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N32" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="O32" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="P32" s="38" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q32" s="39" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C32,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U32" s="37"/>
@@ -3970,27 +3204,27 @@
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
       <c r="L33" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="M33" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N33" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="O33" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="P33" s="38" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q33" s="39" t="str">
-        <f t="shared" si="4"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C33,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U33" s="37"/>
@@ -4008,27 +3242,27 @@
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
       <c r="L34" s="4" t="str">
-        <f t="shared" ref="L34:L61" si="7">IF(G34="","",IF(G34="SIM",1,0))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="M34" s="4" t="str">
-        <f t="shared" ref="M34:M61" si="8">IF(H34="","",IF(H34="SIM",1,0))</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="N34" s="4" t="str">
-        <f t="shared" ref="N34:N61" si="9">IF(J34="","",IF(J34="SIM",1,0))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="O34" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="P34" s="38" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="Q34" s="39" t="str">
-        <f t="shared" ref="Q34:Q65" si="10">IFERROR(AVERAGEIF(C$2:C$61,C34,P$2:P$61),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C34,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U34" s="37"/>
@@ -4046,27 +3280,27 @@
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
       <c r="L35" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="M35" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="M35" s="4" t="str">
+      <c r="N35" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="N35" s="4" t="str">
+      <c r="O35" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="P35" s="38" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O35" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="P35" s="38" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
       <c r="Q35" s="39" t="str">
-        <f t="shared" si="10"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C35,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U35" s="37"/>
@@ -4084,27 +3318,27 @@
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
       <c r="L36" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="M36" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="M36" s="4" t="str">
+      <c r="N36" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="N36" s="4" t="str">
+      <c r="O36" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="P36" s="38" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O36" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="P36" s="38" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
       <c r="Q36" s="39" t="str">
-        <f t="shared" si="10"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C36,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U36" s="37"/>
@@ -4122,27 +3356,27 @@
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
       <c r="L37" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="M37" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="M37" s="4" t="str">
+      <c r="N37" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="N37" s="4" t="str">
+      <c r="O37" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="P37" s="38" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O37" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="P37" s="38" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
       <c r="Q37" s="39" t="str">
-        <f t="shared" si="10"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C37,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U37" s="37"/>
@@ -4160,27 +3394,27 @@
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
       <c r="L38" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="M38" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="M38" s="4" t="str">
+      <c r="N38" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="N38" s="4" t="str">
+      <c r="O38" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="P38" s="38" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O38" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="P38" s="38" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
       <c r="Q38" s="39" t="str">
-        <f t="shared" si="10"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C38,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U38" s="37"/>
@@ -4198,27 +3432,27 @@
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
       <c r="L39" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="M39" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="M39" s="4" t="str">
+      <c r="N39" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="N39" s="4" t="str">
+      <c r="O39" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="P39" s="38" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O39" s="4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="P39" s="38" t="str">
-        <f t="shared" ref="P39:P70" si="11">IF(COUNTA(G39,H39,J39,K39)=0,"",ROUND(AVERAGE(L39:O39)*100,0))</f>
-        <v/>
-      </c>
       <c r="Q39" s="39" t="str">
-        <f t="shared" si="10"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C39,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U39" s="37"/>
@@ -4236,27 +3470,27 @@
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
       <c r="L40" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="M40" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="M40" s="4" t="str">
+      <c r="N40" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="N40" s="4" t="str">
+      <c r="O40" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="P40" s="38" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O40" s="4" t="str">
-        <f t="shared" ref="O40:O61" si="12">IF(K40="","",IF(K40="Conformidade",1,IF(K40="Não Conformidade",0,IF(K40="Não Conformidade Grave",-1,""))))</f>
-        <v/>
-      </c>
-      <c r="P40" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
       <c r="Q40" s="39" t="str">
-        <f t="shared" si="10"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C40,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U40" s="37"/>
@@ -4274,27 +3508,27 @@
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
       <c r="L41" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="M41" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="M41" s="4" t="str">
+      <c r="N41" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="N41" s="4" t="str">
+      <c r="O41" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="P41" s="38" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O41" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P41" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
       <c r="Q41" s="39" t="str">
-        <f t="shared" si="10"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C41,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U41" s="37"/>
@@ -4312,27 +3546,27 @@
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
       <c r="L42" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="M42" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="M42" s="4" t="str">
+      <c r="N42" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="N42" s="4" t="str">
+      <c r="O42" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="P42" s="38" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O42" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P42" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
       <c r="Q42" s="39" t="str">
-        <f t="shared" si="10"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C42,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U42" s="37"/>
@@ -4350,27 +3584,27 @@
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
       <c r="L43" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="M43" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="M43" s="4" t="str">
+      <c r="N43" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="N43" s="4" t="str">
+      <c r="O43" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="P43" s="38" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O43" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P43" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
       <c r="Q43" s="39" t="str">
-        <f t="shared" si="10"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C43,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U43" s="37"/>
@@ -4388,27 +3622,27 @@
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
       <c r="L44" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="M44" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="M44" s="4" t="str">
+      <c r="N44" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="N44" s="4" t="str">
+      <c r="O44" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="P44" s="38" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O44" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P44" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
       <c r="Q44" s="39" t="str">
-        <f t="shared" si="10"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C44,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U44" s="37"/>
@@ -4426,27 +3660,27 @@
       <c r="J45" s="4"/>
       <c r="K45" s="4"/>
       <c r="L45" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="M45" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="M45" s="4" t="str">
+      <c r="N45" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="N45" s="4" t="str">
+      <c r="O45" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="P45" s="38" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O45" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P45" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
       <c r="Q45" s="39" t="str">
-        <f t="shared" si="10"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C45,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U45" s="37"/>
@@ -4464,27 +3698,27 @@
       <c r="J46" s="4"/>
       <c r="K46" s="4"/>
       <c r="L46" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="M46" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="M46" s="4" t="str">
+      <c r="N46" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="N46" s="4" t="str">
+      <c r="O46" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="P46" s="38" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O46" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P46" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
       <c r="Q46" s="39" t="str">
-        <f t="shared" si="10"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C46,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U46" s="37"/>
@@ -4502,27 +3736,27 @@
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
       <c r="L47" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="M47" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="M47" s="4" t="str">
+      <c r="N47" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="N47" s="4" t="str">
+      <c r="O47" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="P47" s="38" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O47" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P47" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
       <c r="Q47" s="39" t="str">
-        <f t="shared" si="10"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C47,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U47" s="37"/>
@@ -4540,27 +3774,27 @@
       <c r="J48" s="4"/>
       <c r="K48" s="4"/>
       <c r="L48" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="M48" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="M48" s="4" t="str">
+      <c r="N48" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="N48" s="4" t="str">
+      <c r="O48" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="P48" s="38" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O48" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P48" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
       <c r="Q48" s="39" t="str">
-        <f t="shared" si="10"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C48,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U48" s="37"/>
@@ -4578,580 +3812,117 @@
       <c r="J49" s="4"/>
       <c r="K49" s="4"/>
       <c r="L49" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="M49" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="M49" s="4" t="str">
+      <c r="N49" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="N49" s="4" t="str">
+      <c r="O49" s="4" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="P49" s="38" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="O49" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P49" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
       <c r="Q49" s="39" t="str">
-        <f t="shared" si="10"/>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C49,P$2:P$49),"N/A")</f>
         <v>N/A</v>
       </c>
       <c r="U49" s="37"/>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A50" s="4"/>
-      <c r="B50" s="36"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="36"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="M50" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="N50" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="O50" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P50" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="Q50" s="39" t="str">
-        <f t="shared" si="10"/>
-        <v>N/A</v>
-      </c>
-      <c r="U50" s="37"/>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A51" s="4"/>
-      <c r="B51" s="36"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="36"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="M51" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="N51" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="O51" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P51" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="Q51" s="39" t="str">
-        <f t="shared" si="10"/>
-        <v>N/A</v>
-      </c>
-      <c r="U51" s="37"/>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A52" s="4"/>
-      <c r="B52" s="36"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="36"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="M52" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="N52" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="O52" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P52" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="Q52" s="39" t="str">
-        <f t="shared" si="10"/>
-        <v>N/A</v>
-      </c>
-      <c r="U52" s="37"/>
-    </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A53" s="4"/>
-      <c r="B53" s="36"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="36"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="M53" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="N53" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="O53" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P53" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="Q53" s="39" t="str">
-        <f t="shared" si="10"/>
-        <v>N/A</v>
-      </c>
-      <c r="U53" s="37"/>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A54" s="4"/>
-      <c r="B54" s="36"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="36"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
-      <c r="L54" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="M54" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="N54" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="O54" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P54" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="Q54" s="39" t="str">
-        <f t="shared" si="10"/>
-        <v>N/A</v>
-      </c>
-      <c r="U54" s="37"/>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A55" s="4"/>
-      <c r="B55" s="36"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="36"/>
-      <c r="J55" s="4"/>
-      <c r="K55" s="4"/>
-      <c r="L55" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="M55" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="N55" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="O55" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P55" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="Q55" s="39" t="str">
-        <f t="shared" si="10"/>
-        <v>N/A</v>
-      </c>
-      <c r="U55" s="37"/>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A56" s="4"/>
-      <c r="B56" s="36"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="36"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-      <c r="L56" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="M56" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="N56" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="O56" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P56" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="Q56" s="39" t="str">
-        <f t="shared" si="10"/>
-        <v>N/A</v>
-      </c>
-      <c r="U56" s="37"/>
-    </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A57" s="4"/>
-      <c r="B57" s="36"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="36"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
-      <c r="L57" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="M57" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="N57" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="O57" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P57" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="Q57" s="39" t="str">
-        <f t="shared" si="10"/>
-        <v>N/A</v>
-      </c>
-      <c r="U57" s="37"/>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A58" s="4"/>
-      <c r="B58" s="36"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="36"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
-      <c r="L58" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="M58" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="N58" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="O58" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P58" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="Q58" s="39" t="str">
-        <f t="shared" si="10"/>
-        <v>N/A</v>
-      </c>
-      <c r="U58" s="37"/>
-    </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A59" s="4"/>
-      <c r="B59" s="36"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="36"/>
-      <c r="J59" s="4"/>
-      <c r="K59" s="4"/>
-      <c r="L59" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="M59" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="N59" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="O59" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P59" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="Q59" s="39" t="str">
-        <f t="shared" si="10"/>
-        <v>N/A</v>
-      </c>
-      <c r="U59" s="37"/>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A60" s="4"/>
-      <c r="B60" s="36"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="36"/>
-      <c r="J60" s="4"/>
-      <c r="K60" s="4"/>
-      <c r="L60" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="M60" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="N60" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="O60" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P60" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="Q60" s="39" t="str">
-        <f t="shared" si="10"/>
-        <v>N/A</v>
-      </c>
-      <c r="U60" s="37"/>
-    </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A61" s="4"/>
-      <c r="B61" s="36"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
-      <c r="I61" s="36"/>
-      <c r="J61" s="4"/>
-      <c r="K61" s="4"/>
-      <c r="L61" s="4" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="M61" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="N61" s="4" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="O61" s="4" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="P61" s="38" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="Q61" s="39" t="str">
-        <f t="shared" si="10"/>
-        <v>N/A</v>
-      </c>
-      <c r="U61" s="37"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P61" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="G2:H61 K4:K1004">
-    <cfRule type="cellIs" dxfId="72" priority="4" operator="equal">
+  <autoFilter ref="A1:P49" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="G2:H49 K3:K992 J3:J49">
+    <cfRule type="cellIs" dxfId="40" priority="4" operator="equal">
       <formula>"SIM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="5" operator="equal">
       <formula>"NÃO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J61">
-    <cfRule type="cellIs" dxfId="70" priority="1" operator="equal">
+  <conditionalFormatting sqref="J2:K2">
+    <cfRule type="cellIs" dxfId="38" priority="6" operator="equal">
       <formula>"SIM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="7" operator="equal">
       <formula>"NÃO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:K3">
-    <cfRule type="cellIs" dxfId="68" priority="6" operator="equal">
-      <formula>"SIM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="7" operator="equal">
-      <formula>"NÃO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2:Q61 Q62:Q1004">
-    <cfRule type="cellIs" dxfId="66" priority="8" operator="lessThan">
+  <conditionalFormatting sqref="Q50:Q992 P2:Q49">
+    <cfRule type="cellIs" dxfId="36" priority="8" operator="lessThan">
       <formula>50</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="9" operator="between">
+    <cfRule type="cellIs" dxfId="35" priority="9" operator="between">
       <formula>50</formula>
       <formula>79</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="10" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="34" priority="10" operator="greaterThanOrEqual">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" sqref="K2:K1004" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="date" allowBlank="1" sqref="I2:I3 B2:B3" xr:uid="{00000000-0002-0000-0000-000002000000}">
+      <formula1>DATE(2000,1,1)</formula1>
+      <formula2>DATE(2100,12,31)</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" sqref="F2:F3" xr:uid="{00000000-0002-0000-0000-000003000000}">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G2:H6 J2:J6" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"SIM,NÃO"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="K2:K992" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Não Conformidade Grave,Não Conformidade,Conformidade,Observação"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:H18 J2:J18" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"SIM,NÃO"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation type="date" allowBlank="1" sqref="B2:B7 I2:I7" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>DATE(2000,1,1)</formula1>
-      <formula2>DATE(2100,12,31)</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" sqref="F2:F7" xr:uid="{00000000-0002-0000-0000-000003000000}">
-      <formula1>0</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="V2:V1004" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="V2:V992" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"Aberto,Em andamento,Concluído"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77E52904-D6E8-4CC9-A67B-383FD537F806}">
+  <dimension ref="A1:V5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.28515625" style="37" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" customWidth="1"/>
     <col min="8" max="8" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12" style="57" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5165,19 +3936,19 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>91</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>92</v>
+        <v>68</v>
+      </c>
+      <c r="G1" s="58" t="s">
+        <v>242</v>
       </c>
       <c r="H1" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="I1" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="J1" t="s">
         <v>10</v>
@@ -5185,38 +3956,41 @@
       <c r="K1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="58" t="s">
+        <v>284</v>
+      </c>
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" t="s">
-        <v>95</v>
-      </c>
-      <c r="P1" s="57" t="s">
+      <c r="P1" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>928734</v>
       </c>
@@ -5229,17 +4003,17 @@
       <c r="D2" t="s">
         <v>34</v>
       </c>
-      <c r="E2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F2">
+      <c r="E2">
         <v>1</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>25</v>
@@ -5248,31 +4022,35 @@
         <v>17</v>
       </c>
       <c r="K2">
+        <f>IF(F2="","",IF(F2="SIM",1,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L2">
         <f>IF(G2="","",IF(G2="SIM",1,0))</f>
         <v>1</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <f>IF(H2="","",IF(H2="Automático",1,IF(H2="Manual",0.5,IF(H2="Não atualizado",0,""))))</f>
         <v>1</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <f>IF(I2="","",IF(I2="SIM",1,0))</f>
         <v>1</v>
       </c>
-      <c r="N2" t="str">
+      <c r="O2" t="str">
         <f>IF(J2="","",IF(J2="Conformidade",1,IF(J2="Não Conformidade",0,IF(J2="Não Conformidade Grave",-1,""))))</f>
         <v/>
       </c>
-      <c r="O2">
-        <f>IF(COUNTA(G2:J2)=0,"",ROUND(AVERAGE(K2:N2)*100,0))</f>
+      <c r="P2">
+        <f>IF(COUNTA(F2:J2)=0,"",ROUND(AVERAGE(K2:O2)*100,0))</f>
         <v>100</v>
       </c>
-      <c r="P2" s="58">
-        <f>IFERROR(AVERAGEIF(C$2:C$201,C2,O$2:O$201),"N/A")</f>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Q2" s="51">
+        <f>IFERROR(AVERAGEIF(C$2:C$171,C2,P$2:P$171),"N/A")</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>928734</v>
       </c>
@@ -5283,52 +4061,56 @@
         <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F3">
+        <v>23</v>
+      </c>
+      <c r="E3">
         <v>1</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K35" si="0">IF(G3="","",IF(G3="SIM",1,0))</f>
+        <f>IF(F3="","",IF(F3="SIM",1,0))</f>
         <v>1</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3:L35" si="1">IF(H3="","",IF(H3="Automático",1,IF(H3="Manual",0.5,IF(H3="Não atualizado",0,""))))</f>
+        <f t="shared" ref="L3:L5" si="0">IF(G3="","",IF(G3="SIM",1,0))</f>
         <v>1</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M35" si="2">IF(I3="","",IF(I3="SIM",1,0))</f>
+        <f>IF(H3="","",IF(H3="Automático",1,IF(H3="Manual",0.5,IF(H3="Não atualizado",0,""))))</f>
         <v>1</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N35" si="3">IF(J3="","",IF(J3="Conformidade",1,IF(J3="Não Conformidade",0,IF(J3="Não Conformidade Grave",-1,""))))</f>
-        <v>1</v>
+        <f>IF(I3="","",IF(I3="SIM",1,0))</f>
+        <v>0</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:O35" si="4">IF(COUNTA(G3:J3)=0,"",ROUND(AVERAGE(K3:N3)*100,0))</f>
-        <v>100</v>
-      </c>
-      <c r="P3" s="58">
-        <f t="shared" ref="P3:P35" si="5">IFERROR(AVERAGEIF(C$2:C$201,C3,O$2:O$201),"N/A")</f>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+        <f>IF(J3="","",IF(J3="Conformidade",1,IF(J3="Não Conformidade",0,IF(J3="Não Conformidade Grave",-1,""))))</f>
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <f>IF(COUNTA(F3:J3)=0,"",ROUND(AVERAGE(K3:O3)*100,0))</f>
+        <v>60</v>
+      </c>
+      <c r="Q3" s="51">
+        <f>IFERROR(AVERAGEIF(C$2:C$171,C3,P$2:P$171),"N/A")</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>928734</v>
       </c>
@@ -5339,52 +4121,56 @@
         <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F4">
+        <v>38</v>
+      </c>
+      <c r="E4">
         <v>1</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="K4">
+        <f>IF(F4="","",IF(F4="SIM",1,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L4">
-        <f t="shared" si="1"/>
+      <c r="M4">
+        <f>IF(H4="","",IF(H4="Automático",1,IF(H4="Manual",0.5,IF(H4="Não atualizado",0,""))))</f>
         <v>1</v>
       </c>
-      <c r="M4">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
       <c r="N4">
-        <f t="shared" si="3"/>
-        <v>1</v>
+        <f>IF(I4="","",IF(I4="SIM",1,0))</f>
+        <v>0</v>
       </c>
       <c r="O4">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P4" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+        <f>IF(J4="","",IF(J4="Conformidade",1,IF(J4="Não Conformidade",0,IF(J4="Não Conformidade Grave",-1,""))))</f>
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <f>IF(COUNTA(F4:J4)=0,"",ROUND(AVERAGE(K4:O4)*100,0))</f>
+        <v>60</v>
+      </c>
+      <c r="Q4" s="51">
+        <f>IFERROR(AVERAGEIF(C$2:C$171,C4,P$2:P$171),"N/A")</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>928734</v>
       </c>
@@ -5395,19 +4181,19 @@
         <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F5">
+        <v>50</v>
+      </c>
+      <c r="E5">
         <v>1</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>25</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>25</v>
@@ -5416,1879 +4202,68 @@
         <v>14</v>
       </c>
       <c r="K5">
+        <f>IF(F5="","",IF(F5="SIM",1,0))</f>
+        <v>1</v>
+      </c>
+      <c r="L5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L5">
-        <f t="shared" si="1"/>
+      <c r="M5">
+        <f>IF(H5="","",IF(H5="Automático",1,IF(H5="Manual",0.5,IF(H5="Não atualizado",0,""))))</f>
         <v>1</v>
       </c>
-      <c r="M5">
-        <f t="shared" si="2"/>
+      <c r="N5">
+        <f>IF(I5="","",IF(I5="SIM",1,0))</f>
         <v>1</v>
       </c>
-      <c r="N5">
-        <f t="shared" si="3"/>
+      <c r="O5">
+        <f>IF(J5="","",IF(J5="Conformidade",1,IF(J5="Não Conformidade",0,IF(J5="Não Conformidade Grave",-1,""))))</f>
         <v>1</v>
       </c>
-      <c r="O5">
-        <f t="shared" si="4"/>
+      <c r="P5">
+        <f>IF(COUNTA(F5:J5)=0,"",ROUND(AVERAGE(K5:O5)*100,0))</f>
         <v>100</v>
       </c>
-      <c r="P5" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>928734</v>
-      </c>
-      <c r="B6" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N6">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O6">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P6" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>928734</v>
-      </c>
-      <c r="B7" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" t="s">
-        <v>102</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O7">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P7" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>928734</v>
-      </c>
-      <c r="B8" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" t="s">
-        <v>103</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L8">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N8">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O8">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P8" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>928734</v>
-      </c>
-      <c r="B9" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" t="s">
-        <v>104</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L9">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M9">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N9">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O9">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P9" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>928734</v>
-      </c>
-      <c r="B10" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" t="s">
-        <v>105</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L10">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M10">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N10">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O10">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P10" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>928734</v>
-      </c>
-      <c r="B11" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" t="s">
-        <v>106</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L11">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M11">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="P11" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>928734</v>
-      </c>
-      <c r="B12" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" t="s">
-        <v>98</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L12">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M12">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N12">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O12">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P12" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>928734</v>
-      </c>
-      <c r="B13" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" t="s">
-        <v>99</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L13">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M13">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N13">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O13">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P13" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>928734</v>
-      </c>
-      <c r="B14" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" t="s">
-        <v>100</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L14">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M14">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N14">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O14">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P14" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>928734</v>
-      </c>
-      <c r="B15" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" t="s">
-        <v>101</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L15">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M15">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N15">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O15">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P15" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>928734</v>
-      </c>
-      <c r="B16" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" t="s">
-        <v>102</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L16">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M16">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N16">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O16">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P16" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>928734</v>
-      </c>
-      <c r="B17" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C17" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" t="s">
-        <v>103</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L17">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M17">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N17">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O17">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P17" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>928734</v>
-      </c>
-      <c r="B18" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" t="s">
-        <v>104</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K18">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L18">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M18">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N18">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O18">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P18" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>928734</v>
-      </c>
-      <c r="B19" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C19" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" t="s">
-        <v>105</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K19">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L19">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M19">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N19">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O19">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P19" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>928734</v>
-      </c>
-      <c r="B20" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C20" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" t="s">
-        <v>38</v>
-      </c>
-      <c r="E20" t="s">
-        <v>107</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K20">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L20">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M20">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N20" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="O20">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P20" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>928734</v>
-      </c>
-      <c r="B21" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" t="s">
-        <v>38</v>
-      </c>
-      <c r="E21" t="s">
-        <v>108</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K21">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L21">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M21">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="O21">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P21" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>928734</v>
-      </c>
-      <c r="B22" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" t="s">
-        <v>109</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K22">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L22">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M22">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N22" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="O22">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P22" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>928734</v>
-      </c>
-      <c r="B23" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" t="s">
-        <v>38</v>
-      </c>
-      <c r="E23" t="s">
-        <v>110</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L23">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M23">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="O23">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P23" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>928734</v>
-      </c>
-      <c r="B24" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C24" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" t="s">
-        <v>102</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K24">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L24">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M24">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N24">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O24">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P24" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>928734</v>
-      </c>
-      <c r="B25" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C25" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" t="s">
-        <v>38</v>
-      </c>
-      <c r="E25" t="s">
-        <v>111</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J25" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K25">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L25">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M25">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N25">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O25">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P25" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>928734</v>
-      </c>
-      <c r="B26" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C26" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" t="s">
-        <v>112</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K26">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L26">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M26">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N26">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O26">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P26" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>928734</v>
-      </c>
-      <c r="B27" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C27" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" t="s">
-        <v>57</v>
-      </c>
-      <c r="E27" t="s">
-        <v>106</v>
-      </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="K27">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L27">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M27">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="N27">
-        <f t="shared" si="3"/>
-        <v>-1</v>
-      </c>
-      <c r="O27">
-        <f t="shared" si="4"/>
-        <v>25</v>
-      </c>
-      <c r="P27" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>928734</v>
-      </c>
-      <c r="B28" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C28" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28" t="s">
-        <v>57</v>
-      </c>
-      <c r="E28" t="s">
-        <v>114</v>
-      </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K28">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L28">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M28">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N28">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O28">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P28" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>928734</v>
-      </c>
-      <c r="B29" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C29" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29" t="s">
-        <v>57</v>
-      </c>
-      <c r="E29" t="s">
-        <v>114</v>
-      </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K29">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L29">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M29">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N29">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O29">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P29" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>928734</v>
-      </c>
-      <c r="B30" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C30" t="s">
-        <v>22</v>
-      </c>
-      <c r="D30" t="s">
-        <v>57</v>
-      </c>
-      <c r="E30" t="s">
-        <v>100</v>
-      </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K30">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L30">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M30">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N30">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O30">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P30" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>928734</v>
-      </c>
-      <c r="B31" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C31" t="s">
-        <v>22</v>
-      </c>
-      <c r="D31" t="s">
-        <v>57</v>
-      </c>
-      <c r="E31" t="s">
-        <v>115</v>
-      </c>
-      <c r="F31">
-        <v>1</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K31">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L31">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M31">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N31">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O31">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P31" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>928734</v>
-      </c>
-      <c r="B32" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C32" t="s">
-        <v>22</v>
-      </c>
-      <c r="D32" t="s">
-        <v>57</v>
-      </c>
-      <c r="E32" t="s">
-        <v>102</v>
-      </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K32">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L32">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M32">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N32">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O32">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P32" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>928734</v>
-      </c>
-      <c r="B33" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C33" t="s">
-        <v>22</v>
-      </c>
-      <c r="D33" t="s">
-        <v>57</v>
-      </c>
-      <c r="E33" t="s">
-        <v>101</v>
-      </c>
-      <c r="F33">
-        <v>1</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L33">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M33">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N33">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O33">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P33" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>928734</v>
-      </c>
-      <c r="B34" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C34" t="s">
-        <v>22</v>
-      </c>
-      <c r="D34" t="s">
-        <v>57</v>
-      </c>
-      <c r="E34" t="s">
-        <v>103</v>
-      </c>
-      <c r="F34">
-        <v>1</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K34">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L34">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M34">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N34">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O34">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P34" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>928734</v>
-      </c>
-      <c r="B35" s="37">
-        <v>46283</v>
-      </c>
-      <c r="C35" t="s">
-        <v>22</v>
-      </c>
-      <c r="D35" t="s">
-        <v>57</v>
-      </c>
-      <c r="E35" t="s">
-        <v>104</v>
-      </c>
-      <c r="F35">
-        <v>1</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K35">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L35">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M35">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N35">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="O35">
-        <f t="shared" si="4"/>
-        <v>100</v>
-      </c>
-      <c r="P35" s="58">
-        <f t="shared" si="5"/>
-        <v>96.32352941176471</v>
+      <c r="Q5" s="51">
+        <f>IFERROR(AVERAGEIF(C$2:C$171,C5,P$2:P$171),"N/A")</f>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2">
-    <cfRule type="cellIs" dxfId="35" priority="35" operator="equal">
+  <conditionalFormatting sqref="I2:J5 F2:G5">
+    <cfRule type="cellIs" dxfId="33" priority="3" operator="equal">
       <formula>"SIM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="36" operator="equal">
-      <formula>"NÃO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="cellIs" dxfId="33" priority="33" operator="equal">
-      <formula>"SIM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="34" operator="equal">
-      <formula>"NÃO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G35">
-    <cfRule type="cellIs" dxfId="31" priority="31" operator="equal">
-      <formula>"SIM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="32" operator="equal">
-      <formula>"NÃO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I11">
-    <cfRule type="cellIs" dxfId="29" priority="29" operator="equal">
-      <formula>"SIM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="30" operator="equal">
-      <formula>"NÃO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I12:I26">
-    <cfRule type="cellIs" dxfId="27" priority="27" operator="equal">
-      <formula>"SIM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="28" operator="equal">
-      <formula>"NÃO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I28:I35">
-    <cfRule type="cellIs" dxfId="25" priority="25" operator="equal">
-      <formula>"SIM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="26" operator="equal">
-      <formula>"NÃO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I27">
-    <cfRule type="cellIs" dxfId="23" priority="23" operator="equal">
-      <formula>"SIM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="24" operator="equal">
-      <formula>"NÃO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J3">
-    <cfRule type="cellIs" dxfId="21" priority="21" operator="equal">
-      <formula>"SIM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="22" operator="equal">
-      <formula>"NÃO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J10">
-    <cfRule type="cellIs" dxfId="19" priority="19" operator="equal">
-      <formula>"SIM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="20" operator="equal">
-      <formula>"NÃO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2">
-    <cfRule type="cellIs" dxfId="17" priority="17" operator="equal">
-      <formula>"SIM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="18" operator="equal">
-      <formula>"NÃO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J11">
-    <cfRule type="cellIs" dxfId="15" priority="15" operator="equal">
-      <formula>"SIM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="16" operator="equal">
-      <formula>"NÃO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J12:J19">
-    <cfRule type="cellIs" dxfId="13" priority="13" operator="equal">
-      <formula>"SIM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="14" operator="equal">
-      <formula>"NÃO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J20:J23">
-    <cfRule type="cellIs" dxfId="11" priority="11" operator="equal">
-      <formula>"SIM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
-      <formula>"NÃO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J24">
-    <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
-      <formula>"SIM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
-      <formula>"NÃO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J25">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
-      <formula>"SIM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
-      <formula>"NÃO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J26">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
-      <formula>"SIM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
-      <formula>"NÃO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J27">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
-      <formula>"SIM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
-      <formula>"NÃO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J28:J35">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>"SIM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="4" operator="equal">
       <formula>"NÃO"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="G2:G35 I2:I35" xr:uid="{508DDCA8-31D9-4AA8-B47D-76025D1F4C8F}">
-      <formula1>"SIM,NÃO"</formula1>
+    <dataValidation type="list" allowBlank="1" sqref="H2:H5" xr:uid="{C3BB923A-7C00-4145-9F4D-51BD86D8D251}">
+      <formula1>"Automático,Manual,Não atualizado"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J35" xr:uid="{C6271172-70DE-4E56-A25C-BB6B4FCD508C}">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J5" xr:uid="{69B316C6-6E8C-4750-8B48-0B95D02A3253}">
       <formula1>"Não Conformidade Grave,Não Conformidade,Conformidade,Observação"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H35" xr:uid="{A393994B-4E4B-4A04-8977-426AC00CBE7A}">
-      <formula1>"Automático,Manual,Não atualizado"</formula1>
+    <dataValidation type="list" allowBlank="1" sqref="I2:I5 F2:G5" xr:uid="{99D6AFA3-078F-4A18-8D26-749847694146}">
+      <formula1>"SIM,NÃO"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="L2 L3:L35" formula="1"/>
+    <ignoredError sqref="M2:M5" formula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -7298,22 +4273,23 @@
     <col min="5" max="5" width="41.85546875" style="31" customWidth="1"/>
     <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="49.5703125" style="31" customWidth="1"/>
-    <col min="20" max="20" width="14" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="49.5703125" style="31" customWidth="1"/>
+    <col min="21" max="21" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
@@ -7336,52 +4312,55 @@
         <v>6</v>
       </c>
       <c r="H1" s="46" t="s">
+        <v>242</v>
+      </c>
+      <c r="I1" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="46" t="s">
+      <c r="J1" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="46" t="s">
+      <c r="K1" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="46" t="s">
+      <c r="L1" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="46" t="s">
+      <c r="M1" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="46" t="s">
+      <c r="N1" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="46" t="s">
+      <c r="O1" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="46" t="s">
+      <c r="P1" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="46" t="s">
+      <c r="Q1" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="46" t="s">
+      <c r="R1" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="49" t="s">
+      <c r="S1" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="49" t="s">
+      <c r="T1" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="47" t="s">
+      <c r="U1" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="47" t="s">
+      <c r="V1" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="47" t="s">
+      <c r="W1" s="47" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>928734</v>
       </c>
@@ -7395,7 +4374,7 @@
         <v>23</v>
       </c>
       <c r="E2" s="48" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="F2" s="8">
         <v>1</v>
@@ -7406,130 +4385,136 @@
       <c r="H2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="I2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="L2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="7">
-        <f t="shared" ref="L2:M4" si="0">IF(G2="","",IF(G2="SIM",1,IF(G2="NÃO",0,"")))</f>
+      <c r="M2" s="7">
+        <f>IF(G2="","",IF(G2="SIM",1,IF(G2="NÃO",0,"")))</f>
         <v>1</v>
       </c>
-      <c r="M2" s="7">
+      <c r="N2" s="7">
+        <f t="shared" ref="N2:N4" si="0">IF(I2="","",IF(I2="SIM",1,IF(I2="NÃO",0,"")))</f>
+        <v>1</v>
+      </c>
+      <c r="O2" s="7">
+        <f>IF(K2="","",IF(K2="SIM",1,IF(K2="NÃO",0,"")))</f>
+        <v>1</v>
+      </c>
+      <c r="P2" s="7" t="str">
+        <f>IF(L2="","",IF(L2="Conformidade",1,IF(L2="Não Conformidade",0,IF(L2="Não Conformidade Grave",-1,""))))</f>
+        <v/>
+      </c>
+      <c r="Q2" s="7">
+        <f>IF(COUNTA(G2:I2,K2:L2)=0,"",ROUND(AVERAGE(M2:P2)*100,0))</f>
+        <v>100</v>
+      </c>
+      <c r="R2" s="8">
+        <f>IFERROR(AVERAGEIF(C$2:C$5,C2,Q$2:Q$5),"N/A")</f>
+        <v>62.5</v>
+      </c>
+      <c r="S2" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="T2" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="U2" t="s">
+        <v>283</v>
+      </c>
+      <c r="V2" t="s">
+        <v>32</v>
+      </c>
+      <c r="W2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>928734</v>
+      </c>
+      <c r="B3" s="40">
+        <v>46283</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="8">
+        <v>1</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" s="7">
+        <f>IF(G3="","",IF(G3="SIM",1,IF(G3="NÃO",0,"")))</f>
+        <v>1</v>
+      </c>
+      <c r="N3" s="7">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="N2" s="7">
-        <f>IF(J2="","",IF(J2="SIM",1,IF(J2="NÃO",0,"")))</f>
+      <c r="O3" s="7">
+        <f>IF(K3="","",IF(K3="SIM",1,IF(K3="NÃO",0,"")))</f>
         <v>1</v>
       </c>
-      <c r="O2" s="7" t="str">
-        <f>IF(K2="","",IF(K2="Conformidade",1,IF(K2="Não Conformidade",0,IF(K2="Não Conformidade Grave",-1,""))))</f>
-        <v/>
-      </c>
-      <c r="P2" s="7">
-        <f>IF(COUNTA(G2:H2,J2:K2)=0,"",ROUND(AVERAGE(L2:O2)*100,0))</f>
+      <c r="P3" s="41" t="str">
+        <f>IF(L3="","",IF(L3="Conformidade",1,IF(L3="Não Conformidade",0,IF(L3="Não Conformidade Grave",-1,""))))</f>
+        <v/>
+      </c>
+      <c r="Q3" s="50">
+        <f>IF(COUNTA(G3:I3,K3:L3)=0,"",ROUND(AVERAGE(M3:P3)*100,0))</f>
         <v>100</v>
       </c>
-      <c r="Q2" s="8">
-        <f>IFERROR(AVERAGEIF(C$2:C$4,C2,P$2:P$4),"N/A")</f>
-        <v>100</v>
-      </c>
-      <c r="R2" s="31" t="s">
-        <v>117</v>
-      </c>
-      <c r="S2" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="T2" t="s">
-        <v>119</v>
-      </c>
-      <c r="U2" t="s">
+      <c r="R3" s="8">
+        <f>IFERROR(AVERAGEIF(C$2:C$5,C3,Q$2:Q$5),"N/A")</f>
+        <v>62.5</v>
+      </c>
+      <c r="S3" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="T3" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="U3" t="s">
+        <v>283</v>
+      </c>
+      <c r="V3" t="s">
         <v>32</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <v>928734</v>
-      </c>
-      <c r="B3" s="40">
-        <v>46283</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="48" t="s">
-        <v>120</v>
-      </c>
-      <c r="F3" s="8">
-        <v>1</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M3" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="N3" s="7">
-        <f>IF(J3="","",IF(J3="SIM",1,IF(J3="NÃO",0,"")))</f>
-        <v>1</v>
-      </c>
-      <c r="O3" s="41" t="str">
-        <f>IF(K3="","",IF(K3="Conformidade",1,IF(K3="Não Conformidade",0,IF(K3="Não Conformidade Grave",-1,""))))</f>
-        <v/>
-      </c>
-      <c r="P3" s="50">
-        <f>IF(COUNTA(G3:H3,J3:K3)=0,"",ROUND(AVERAGE(L3:O3)*100,0))</f>
-        <v>100</v>
-      </c>
-      <c r="Q3" s="8">
-        <f>IFERROR(AVERAGEIF(C$2:C$4,C3,P$2:P$4),"N/A")</f>
-        <v>100</v>
-      </c>
-      <c r="R3" s="31" t="s">
-        <v>121</v>
-      </c>
-      <c r="S3" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="T3" s="37" t="s">
-        <v>119</v>
-      </c>
-      <c r="U3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>928734</v>
       </c>
@@ -7543,85 +4528,163 @@
         <v>34</v>
       </c>
       <c r="E4" s="48" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="F4" s="8">
         <v>1</v>
       </c>
       <c r="G4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="60" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="60" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="60" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" s="60" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="M4" s="7">
+        <f>IF(G4="","",IF(G4="SIM",1,IF(G4="NÃO",0,"")))</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="7" t="str">
+        <f>IF(I4="","",IF(I4="SIM",1,IF(I4="NÃO",0,"")))</f>
+        <v/>
+      </c>
+      <c r="O4" s="7" t="str">
+        <f>IF(K4="","",IF(K4="SIM",1,IF(K4="NÃO",0,"")))</f>
+        <v/>
+      </c>
+      <c r="P4" s="41">
+        <f>IF(L4="","",IF(L4="Conformidade",1,IF(L4="Não Conformidade",0,IF(L4="Não Conformidade Grave",-1,""))))</f>
+        <v>-1</v>
+      </c>
+      <c r="Q4" s="50">
+        <f>IF(COUNTA(G4:I4,K4:L4)=0,"",ROUND(AVERAGE(M4:P4)*100,0))</f>
+        <v>-50</v>
+      </c>
+      <c r="R4" s="8">
+        <f>IFERROR(AVERAGEIF(C$2:C$5,C5,Q$2:Q$5),"N/A")</f>
+        <v>62.5</v>
+      </c>
+      <c r="S4" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="T4" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="U4" t="s">
+        <v>283</v>
+      </c>
+      <c r="V4" t="s">
+        <v>32</v>
+      </c>
+      <c r="W4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A5" s="7">
+        <v>928734</v>
+      </c>
+      <c r="B5" s="40">
+        <v>46283</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="58" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="59">
+        <v>0</v>
+      </c>
+      <c r="G5" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="8" t="s">
+      <c r="I5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="7">
-        <f t="shared" si="0"/>
+      <c r="J5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" s="7">
+        <f>IF(G5="","",IF(G5="SIM",1,IF(G5="NÃO",0,"")))</f>
         <v>1</v>
       </c>
-      <c r="M4" s="7">
-        <f t="shared" si="0"/>
+      <c r="N5" s="7">
+        <f>IF(I5="","",IF(I5="SIM",1,IF(I5="NÃO",0,"")))</f>
         <v>1</v>
       </c>
-      <c r="N4" s="7">
-        <f>IF(J4="","",IF(J4="SIM",1,IF(J4="NÃO",0,"")))</f>
+      <c r="O5" s="7">
+        <f>IF(K5="","",IF(K5="SIM",1,IF(K5="NÃO",0,"")))</f>
         <v>1</v>
       </c>
-      <c r="O4" s="41" t="str">
-        <f>IF(K4="","",IF(K4="Conformidade",1,IF(K4="Não Conformidade",0,IF(K4="Não Conformidade Grave",-1,""))))</f>
-        <v/>
-      </c>
-      <c r="P4" s="50">
-        <f>IF(COUNTA(G4:H4,J4:K4)=0,"",ROUND(AVERAGE(L4:O4)*100,0))</f>
+      <c r="P5" s="41">
+        <f>IF(L5="","",IF(L5="Conformidade",1,IF(L5="Não Conformidade",0,IF(L5="Não Conformidade Grave",-1,""))))</f>
+        <v>1</v>
+      </c>
+      <c r="Q5" s="50">
+        <f>IF(COUNTA(G5:I5,K5:L5)=0,"",ROUND(AVERAGE(M5:P5)*100,0))</f>
         <v>100</v>
       </c>
-      <c r="Q4" s="8">
-        <f>IFERROR(AVERAGEIF(C$2:C$4,C4,P$2:P$4),"N/A")</f>
-        <v>100</v>
-      </c>
-      <c r="R4" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="S4" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="T4" s="37" t="s">
-        <v>119</v>
-      </c>
-      <c r="U4" t="s">
-        <v>32</v>
-      </c>
-      <c r="V4" t="s">
-        <v>33</v>
+      <c r="R5" s="8">
+        <f>IFERROR(AVERAGEIF(C$2:C$5,C5,Q$2:Q$5),"N/A")</f>
+        <v>62.5</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:J4">
-    <cfRule type="cellIs" dxfId="63" priority="1" operator="equal">
+  <conditionalFormatting sqref="G2:G5 I2:K3 H4:K4">
+    <cfRule type="cellIs" dxfId="31" priority="7" operator="equal">
       <formula>"SIM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="8" operator="equal">
       <formula>"NÃO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:P4">
-    <cfRule type="cellIs" dxfId="61" priority="14" operator="lessThan">
+  <conditionalFormatting sqref="P2:Q5">
+    <cfRule type="cellIs" dxfId="29" priority="20" operator="lessThan">
       <formula>50</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="15" operator="between">
+    <cfRule type="cellIs" dxfId="28" priority="21" operator="between">
       <formula>50</formula>
       <formula>79</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="16" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="27" priority="22" operator="greaterThanOrEqual">
       <formula>80</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H3">
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="4" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5:K5">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
+      <formula>"NÃO"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
@@ -7629,30 +4692,33 @@
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:I4 J2:J4" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G2:K5" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"SIM,NÃO"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="K2:K4" xr:uid="{00000000-0002-0000-0200-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="L2:L5" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>"Não Conformidade Grave,Não Conformidade,Conformidade,Observação"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" sqref="B2:B4" xr:uid="{00000000-0002-0000-0200-000003000000}">
+    <dataValidation type="date" allowBlank="1" sqref="B2:B5" xr:uid="{00000000-0002-0000-0200-000003000000}">
       <formula1>DATE(2000,1,1)</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="U2:U4" xr:uid="{00000000-0002-0000-0200-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="V2:V4" xr:uid="{00000000-0002-0000-0200-000004000000}">
       <formula1>"Aberto,Em andamento,Concluído"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="R4" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -7670,7 +4736,7 @@
     <col min="13" max="13" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="5.7109375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="72.85546875" style="31" customWidth="1"/>
     <col min="19" max="19" width="49.5703125" style="31" customWidth="1"/>
@@ -7775,34 +4841,34 @@
         <v>26</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="L2" s="7">
-        <f t="shared" ref="L2:M4" si="0">IF(G2="","",IF(G2="SIM",1,IF(G2="NÃO",0,"")))</f>
-        <v>1</v>
+        <f>IF(G2="","",IF(G2="SIM",0.5,IF(G2="NÃO",0,"")))</f>
+        <v>0.5</v>
       </c>
       <c r="M2" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="L2:M5" si="0">IF(H2="","",IF(H2="SIM",1,IF(H2="NÃO",0,"")))</f>
         <v>1</v>
       </c>
       <c r="N2" s="7">
         <f>IF(J2="","",IF(J2="SIM",1,IF(J2="NÃO",0,"")))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" s="8">
         <f>IF(K2="","",IF(K2="Conformidade",1,IF(K2="Não Conformidade",0,IF(K2="Não Conformidade Grave",-1,""))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2">
         <f>IF(COUNTA(G2:H2,J2:K2)=0,"",ROUND(AVERAGE(L2:O2)*100,0))</f>
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="Q2">
-        <f>IFERROR(AVERAGEIF(C$2:C$201,C2,P$2:P$201),"N/A")</f>
-        <v>33.333333333333336</v>
+        <f>IFERROR(AVERAGEIF(C$2:C$202,C2,P$2:P$202),"N/A")</f>
+        <v>59.5</v>
       </c>
       <c r="R2" s="31" t="s">
         <v>29</v>
@@ -7820,7 +4886,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>928734</v>
       </c>
@@ -7849,10 +4915,10 @@
         <v>26</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="L3" s="7">
         <f t="shared" si="0"/>
@@ -7864,19 +4930,19 @@
       </c>
       <c r="N3" s="41">
         <f>IF(J3="","",IF(J3="SIM",1,IF(J3="NÃO",0,"")))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" s="8">
         <f>IF(K3="","",IF(K3="Conformidade",1,IF(K3="Não Conformidade",0,IF(K3="Não Conformidade Grave",-1,""))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3">
         <f>IF(COUNTA(G3:H3,J3:K3)=0,"",ROUND(AVERAGE(L3:O3)*100,0))</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q3">
-        <f>IFERROR(AVERAGEIF(C$2:C$201,C3,P$2:P$201),"N/A")</f>
-        <v>33.333333333333336</v>
+        <f>IFERROR(AVERAGEIF(C$2:C$202,C3,P$2:P$202),"N/A")</f>
+        <v>59.5</v>
       </c>
       <c r="R3" s="31" t="s">
         <v>36</v>
@@ -7894,72 +4960,72 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4">
+    <row r="4" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+      <c r="A4" s="7">
         <v>928734</v>
       </c>
-      <c r="B4" s="37">
+      <c r="B4" s="40">
         <v>46283</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4">
+      <c r="D4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="61" t="s">
+        <v>285</v>
+      </c>
+      <c r="F4" s="8">
         <v>1</v>
       </c>
-      <c r="G4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="G4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N4" t="str">
+      <c r="J4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4" s="7">
+        <f t="shared" ref="L4" si="1">IF(G4="","",IF(G4="SIM",1,IF(G4="NÃO",0,"")))</f>
+        <v>1</v>
+      </c>
+      <c r="M4" s="41">
+        <f t="shared" ref="M4" si="2">IF(H4="","",IF(H4="SIM",1,IF(H4="NÃO",0,"")))</f>
+        <v>1</v>
+      </c>
+      <c r="N4" s="41">
         <f>IF(J4="","",IF(J4="SIM",1,IF(J4="NÃO",0,"")))</f>
-        <v/>
-      </c>
-      <c r="O4" t="str">
+        <v>1</v>
+      </c>
+      <c r="O4" s="8">
         <f>IF(K4="","",IF(K4="Conformidade",1,IF(K4="Não Conformidade",0,IF(K4="Não Conformidade Grave",-1,""))))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="P4">
         <f>IF(COUNTA(G4:H4,J4:K4)=0,"",ROUND(AVERAGE(L4:O4)*100,0))</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
-        <f>IFERROR(AVERAGEIF(C$2:C$201,C4,P$2:P$201),"N/A")</f>
-        <v>33.333333333333336</v>
+        <f>IFERROR(AVERAGEIF(C$2:C$202,C4,P$2:P$202),"N/A")</f>
+        <v>59.5</v>
       </c>
       <c r="R4" s="31" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S4" s="31" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="T4" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="U4" t="s">
         <v>32</v>
@@ -7968,47 +5034,120 @@
         <v>33</v>
       </c>
     </row>
+    <row r="5" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>928734</v>
+      </c>
+      <c r="B5" s="37">
+        <v>46283</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <f>IF(J5="","",IF(J5="SIM",1,IF(J5="NÃO",0,"")))</f>
+        <v/>
+      </c>
+      <c r="O5">
+        <f>IF(K5="","",IF(K5="Conformidade",1,IF(K5="Não Conformidade",0,IF(K5="Não Conformidade Grave",-1,""))))</f>
+        <v>-1</v>
+      </c>
+      <c r="P5">
+        <f>IF(COUNTA(G5:H5,I5:K5)=0,"",ROUND(AVERAGE(L5:O5)*100,0))</f>
+        <v>-50</v>
+      </c>
+      <c r="Q5">
+        <f>IFERROR(AVERAGEIF(C$2:C$202,C5,P$2:P$202),"N/A")</f>
+        <v>59.5</v>
+      </c>
+      <c r="R5" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="S5" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="T5" t="s">
+        <v>42</v>
+      </c>
+      <c r="U5" t="s">
+        <v>32</v>
+      </c>
+      <c r="V5" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:J3">
-    <cfRule type="cellIs" dxfId="58" priority="1" operator="equal">
+  <conditionalFormatting sqref="G2:J4">
+    <cfRule type="cellIs" dxfId="22" priority="5" operator="equal">
       <formula>"SIM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="6" operator="equal">
       <formula>"NÃO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:N3">
-    <cfRule type="cellIs" dxfId="56" priority="16" operator="lessThan">
+  <conditionalFormatting sqref="M2:N4">
+    <cfRule type="cellIs" dxfId="20" priority="20" operator="lessThan">
       <formula>50</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="17" operator="between">
+    <cfRule type="cellIs" dxfId="19" priority="21" operator="between">
       <formula>50</formula>
       <formula>79</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="18" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="18" priority="22" operator="greaterThanOrEqual">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" sqref="F2:F3" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" sqref="F2:F4" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G3 H2:J3" xr:uid="{00000000-0002-0000-0300-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G2:J4" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"SIM,NÃO"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="K2:K3" xr:uid="{00000000-0002-0000-0300-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K5" xr:uid="{00000000-0002-0000-0300-000002000000}">
       <formula1>"Não Conformidade Grave,Não Conformidade,Conformidade,Observação"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" sqref="B2:B3" xr:uid="{00000000-0002-0000-0300-000003000000}">
+    <dataValidation type="date" allowBlank="1" sqref="B2:B4" xr:uid="{00000000-0002-0000-0300-000003000000}">
       <formula1>DATE(2000,1,1)</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8027,241 +5166,241 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
-        <v>126</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
+      <c r="A1" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>130</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="B4" s="12">
-        <f>COUNT(Documentos!P2:P61)</f>
-        <v>17</v>
+        <f>COUNT(Documentos!P2:P49)</f>
+        <v>5</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>132</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>133</v>
+        <v>90</v>
       </c>
       <c r="F4" s="13"/>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>134</v>
+        <v>91</v>
       </c>
       <c r="B5" s="12">
-        <f>COUNTIF(Documentos!G2:G61,"SIM")</f>
-        <v>17</v>
+        <f>COUNTIF(Documentos!G2:G49,"SIM")</f>
+        <v>5</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>135</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>136</v>
+        <v>93</v>
       </c>
       <c r="F5" s="13"/>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>137</v>
+        <v>94</v>
       </c>
       <c r="B6" s="12">
-        <f>COUNTIF(Documentos!H2:H61,"SIM")</f>
-        <v>14</v>
+        <f>COUNTIF(Documentos!H2:H49,"SIM")</f>
+        <v>4</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>138</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>139</v>
+        <v>96</v>
       </c>
       <c r="F6" s="14"/>
     </row>
     <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="B7" s="12">
-        <f>COUNTIF(Documentos!J2:J61,"SIM")</f>
-        <v>14</v>
+        <f>COUNTIF(Documentos!J2:J49,"SIM")</f>
+        <v>3</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="F7" s="14"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>143</v>
+        <v>100</v>
       </c>
       <c r="B8" s="12">
-        <f>IFERROR(COUNTIF(Documentos!K2:K61,"Conformidade")-COUNTIF(Documentos!K2:K61,"Não Conformidade Grave"),"")</f>
-        <v>9</v>
+        <f>IFERROR(COUNTIF(Documentos!K2:K49,"Conformidade")-COUNTIF(Documentos!K2:K49,"Não Conformidade Grave"),"")</f>
+        <v>2</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>144</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="F8" s="15"/>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="B9" s="16">
-        <f>IFERROR(AVERAGE(Documentos!P2:P61),0)</f>
-        <v>86.764705882352942</v>
+        <f>IFERROR(AVERAGE(Documentos!P2:P49),0)</f>
+        <v>76.8</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="B10" s="17">
-        <f>IFERROR(COUNTIF(Documentos!G2:G61,"SIM")/COUNTA(Documentos!G2:G61),0)</f>
+        <f>IFERROR(COUNTIF(Documentos!G2:G49,"SIM")/COUNTA(Documentos!G2:G49),0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="B11" s="17">
-        <f>IFERROR(COUNTIF(Documentos!H2:H61,"SIM")/COUNTA(Documentos!H2:H61),0)</f>
-        <v>0.82352941176470584</v>
+        <f>IFERROR(COUNTIF(Documentos!H2:H49,"SIM")/COUNTA(Documentos!H2:H49),0)</f>
+        <v>0.8</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>149</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>150</v>
+        <v>107</v>
       </c>
       <c r="B12" s="17">
-        <f>IFERROR(COUNTIF(Documentos!J2:J61,"SIM")/COUNTA(Documentos!J2:J61),0)</f>
-        <v>0.82352941176470584</v>
-      </c>
-      <c r="D12" s="53" t="s">
-        <v>151</v>
-      </c>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
+        <f>IFERROR(COUNTIF(Documentos!J2:J49,"SIM")/COUNTA(Documentos!J2:J49),0)</f>
+        <v>0.6</v>
+      </c>
+      <c r="D12" s="54" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="53"/>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
     </row>
     <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D15" s="52"/>
-      <c r="E15" s="52"/>
-      <c r="F15" s="52"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="52"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="53"/>
     </row>
     <row r="17" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="54" t="s">
-        <v>152</v>
-      </c>
-      <c r="B17" s="52"/>
+      <c r="A17" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" s="53"/>
     </row>
     <row r="18" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>153</v>
+        <v>110</v>
       </c>
       <c r="B18" s="20">
-        <f>COUNT(Indicadores!O2:O201)</f>
-        <v>34</v>
+        <f>COUNT(Indicadores!P2:P201)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="B19" s="20">
-        <f>COUNTIF(Indicadores!G2:G201,"SIM")</f>
-        <v>34</v>
+        <f>COUNTIF(Indicadores!F2:F201,"SIM")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
-        <v>155</v>
+        <v>112</v>
       </c>
       <c r="B20" s="20">
         <f>COUNTIF(Indicadores!H2:H201,"Automático")+COUNTIF(Indicadores!H2:H201,"Manual")</f>
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
-        <v>156</v>
+        <v>113</v>
       </c>
       <c r="B21" s="20">
         <f>COUNTIF(Indicadores!I2:I201,"SIM")</f>
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="B22" s="20">
         <f>IFERROR(COUNTIF(Indicadores!J2:J201,"Conformidade")*1+COUNTIF(Indicadores!J2:J201,"Não Conformidade")*0+COUNTIF(Indicadores!J2:J201,"Não Conformidade Grave")*-1,"")</f>
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>158</v>
+        <v>115</v>
       </c>
       <c r="B23" s="21">
-        <f>IFERROR(AVERAGE(Indicadores!O2:O201),0)</f>
-        <v>96.32352941176471</v>
+        <f>IFERROR(AVERAGE(Indicadores!P2:P201),0)</f>
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="B24" s="22">
         <f>IFERROR(COUNTIF(Indicadores!G2:G201,"SIM")/COUNTA(Indicadores!G2:G201),0)</f>
@@ -8270,7 +5409,7 @@
     </row>
     <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="B25" s="22">
         <f>IFERROR((COUNTIF(Indicadores!H2:H201,"Automático")+COUNTIF(Indicadores!H2:H201,"Manual"))/COUNTA(Indicadores!H2:H201),0)</f>
@@ -8279,225 +5418,225 @@
     </row>
     <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
-        <v>150</v>
+        <v>107</v>
       </c>
       <c r="B26" s="22">
         <f>IFERROR(COUNTIF(Indicadores!I2:I201,"SIM")/COUNTA(Indicadores!I2:I201),0)</f>
-        <v>0.94117647058823528</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="54" t="s">
-        <v>160</v>
-      </c>
-      <c r="B28" s="52"/>
+      <c r="A28" s="55" t="s">
+        <v>117</v>
+      </c>
+      <c r="B28" s="53"/>
     </row>
     <row r="29" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
-        <v>161</v>
+        <v>118</v>
       </c>
       <c r="B29" s="20">
-        <f>COUNT(Treinamento!P2:P4)</f>
-        <v>3</v>
+        <f>COUNT(Treinamento!Q2:Q5)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="B30" s="20">
-        <f>COUNTIF(Treinamento!G2:G4,"SIM")</f>
+        <f>COUNTIF(Treinamento!G2:G5,"SIM")</f>
         <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
-        <v>163</v>
+        <v>120</v>
       </c>
       <c r="B31" s="20">
-        <f>COUNTIF(Treinamento!H2:H4,"SIM")</f>
+        <f>COUNTIF(Treinamento!I2:I5,"SIM")</f>
         <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
-        <v>164</v>
+        <v>121</v>
       </c>
       <c r="B32" s="20">
-        <f>COUNTIF(Treinamento!J2:J4,"SIM")</f>
+        <f>COUNTIF(Treinamento!K2:K5,"SIM")</f>
         <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>165</v>
+        <v>122</v>
       </c>
       <c r="B33" s="20">
-        <f>COUNTIF(Treinamento!K2:K4,"Conformidade")</f>
-        <v>0</v>
+        <f>COUNTIF(Treinamento!L2:L5,"Conformidade")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
-        <v>166</v>
+        <v>123</v>
       </c>
       <c r="B34" s="21">
-        <f>IFERROR(AVERAGE(Treinamento!P2:P4),0)</f>
-        <v>100</v>
+        <f>IFERROR(AVERAGE(Treinamento!Q2:Q5),0)</f>
+        <v>62.5</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="B35" s="22">
-        <f>IFERROR(COUNTIF(Treinamento!G2:G4,"SIM")/COUNTA(Treinamento!G2:G4),0)</f>
-        <v>1</v>
+        <f>IFERROR(COUNTIF(Treinamento!G2:G5,"SIM")/COUNTA(Treinamento!G2:G5),0)</f>
+        <v>0.75</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="B36" s="22">
-        <f>IFERROR(COUNTIF(Treinamento!H2:H4,"SIM")/COUNTIF(Treinamento!H2:H4,"&lt;&gt;N/A"),0)</f>
+        <f>IFERROR(COUNTIF(Treinamento!I2:I5,"SIM")/COUNTIF(Treinamento!I2:I5,"&lt;&gt;N/A"),0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>150</v>
+        <v>107</v>
       </c>
       <c r="B37" s="22">
-        <f>IFERROR(COUNTIF(Treinamento!J2:J4,"SIM")/COUNTIF(Treinamento!J2:J4,"&lt;&gt;N/A"),0)</f>
+        <f>IFERROR(COUNTIF(Treinamento!K2:K5,"SIM")/COUNTIF(Treinamento!K2:K5,"&lt;&gt;N/A"),0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="54" t="s">
-        <v>167</v>
-      </c>
-      <c r="B39" s="52"/>
+      <c r="A39" s="55" t="s">
+        <v>124</v>
+      </c>
+      <c r="B39" s="53"/>
     </row>
     <row r="40" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
-        <v>168</v>
+        <v>125</v>
       </c>
       <c r="B40" s="20">
-        <f>COUNT(Qualidade!P2:P4)</f>
-        <v>3</v>
+        <f>COUNT(Qualidade!P2:P5)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
-        <v>169</v>
+        <v>126</v>
       </c>
       <c r="B41" s="20">
-        <f>COUNTIF(Qualidade!G2:G4,"SIM")</f>
-        <v>2</v>
+        <f>COUNTIF(Qualidade!G2:G5,"SIM")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
-        <v>170</v>
+        <v>127</v>
       </c>
       <c r="B42" s="20">
-        <f>COUNTIF(Qualidade!H2:H4,"SIM")</f>
-        <v>2</v>
+        <f>COUNTIF(Qualidade!H2:H5,"SIM")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="B43" s="20">
-        <f>COUNTIF(Qualidade!J2:J4,"SIM")</f>
-        <v>0</v>
+        <f>COUNTIF(Qualidade!J2:J5,"SIM")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="B44" s="20">
-        <f>COUNTIF(Qualidade!K2:K4,"Conformidade")</f>
-        <v>0</v>
+        <f>COUNTIF(Qualidade!K2:K5,"Conformidade")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="19" t="s">
-        <v>173</v>
+        <v>130</v>
       </c>
       <c r="B45" s="21">
-        <f>IFERROR(AVERAGE(Qualidade!P2:P4),0)</f>
-        <v>33.333333333333336</v>
+        <f>IFERROR(AVERAGE(Qualidade!P2:P5),0)</f>
+        <v>59.5</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="B46" s="22">
-        <f>IFERROR(COUNTIF(Qualidade!G2:G4,"SIM")/COUNTA(Qualidade!G2:G4),0)</f>
-        <v>0.66666666666666663</v>
+        <f>IFERROR(COUNTIF(Qualidade!G2:G5,"SIM")/COUNTA(Qualidade!G2:G5),0)</f>
+        <v>0.75</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="48" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="54" t="s">
-        <v>174</v>
-      </c>
-      <c r="B48" s="52"/>
-      <c r="C48" s="52"/>
-      <c r="D48" s="52"/>
-      <c r="E48" s="52"/>
+      <c r="A48" s="55" t="s">
+        <v>131</v>
+      </c>
+      <c r="B48" s="53"/>
+      <c r="C48" s="53"/>
+      <c r="D48" s="53"/>
+      <c r="E48" s="53"/>
     </row>
     <row r="49" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
-        <v>175</v>
+        <v>132</v>
       </c>
       <c r="B49" s="21">
         <f>B9</f>
-        <v>86.764705882352942</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="B50" s="21">
         <f>B23</f>
-        <v>96.32352941176471</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="19" t="s">
-        <v>176</v>
+        <v>133</v>
       </c>
       <c r="B51" s="21">
         <f>B34</f>
-        <v>100</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="19" t="s">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="B52" s="21">
         <f>B45</f>
-        <v>33.333333333333336</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="54" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="23" t="s">
-        <v>178</v>
+        <v>135</v>
       </c>
       <c r="B54" s="24">
         <f>IFERROR(AVERAGE(B49:B52),0)</f>
-        <v>79.105392156862749</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9456,74 +6595,74 @@
     <mergeCell ref="A39:B39"/>
   </mergeCells>
   <conditionalFormatting sqref="B9">
-    <cfRule type="cellIs" dxfId="53" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="lessThan">
       <formula>26</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="3" operator="between">
+    <cfRule type="cellIs" dxfId="16" priority="3" operator="between">
       <formula>26</formula>
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="4" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="15" priority="4" operator="greaterThanOrEqual">
       <formula>76</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="cellIs" dxfId="50" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="5" operator="lessThan">
       <formula>26</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="6" operator="between">
+    <cfRule type="cellIs" dxfId="13" priority="6" operator="between">
       <formula>26</formula>
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="7" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="12" priority="7" operator="greaterThanOrEqual">
       <formula>76</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B34">
-    <cfRule type="cellIs" dxfId="47" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="8" operator="lessThan">
       <formula>26</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="9" operator="between">
+    <cfRule type="cellIs" dxfId="10" priority="9" operator="between">
       <formula>26</formula>
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="10" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="greaterThanOrEqual">
       <formula>76</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="cellIs" dxfId="44" priority="11" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="11" operator="lessThan">
       <formula>26</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="12" operator="between">
+    <cfRule type="cellIs" dxfId="7" priority="12" operator="between">
       <formula>26</formula>
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="13" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="6" priority="13" operator="greaterThanOrEqual">
       <formula>76</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B52">
-    <cfRule type="cellIs" dxfId="41" priority="14" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="14" operator="lessThan">
       <formula>26</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="15" operator="between">
+    <cfRule type="cellIs" dxfId="4" priority="15" operator="between">
       <formula>26</formula>
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="16" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="3" priority="16" operator="greaterThanOrEqual">
       <formula>76</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B54">
-    <cfRule type="cellIs" dxfId="38" priority="29" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="29" operator="lessThan">
       <formula>26</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="30" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="30" operator="between">
       <formula>26</formula>
       <formula>75</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="31" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="0" priority="31" operator="greaterThanOrEqual">
       <formula>76</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9546,33 +6685,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
-        <v>179</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
+      <c r="A1" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>181</v>
+        <v>138</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>182</v>
+        <v>139</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>184</v>
+        <v>141</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>185</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9580,19 +6719,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>186</v>
+        <v>143</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>187</v>
+        <v>144</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>190</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9600,39 +6739,39 @@
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>192</v>
+        <v>149</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>193</v>
+        <v>150</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>194</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>195</v>
+        <v>152</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>196</v>
+        <v>153</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>192</v>
+        <v>149</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>197</v>
+        <v>154</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>198</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9640,19 +6779,19 @@
         <v>45</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>199</v>
+        <v>156</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>192</v>
+        <v>149</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>200</v>
+        <v>157</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>201</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -9660,19 +6799,19 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>202</v>
+        <v>159</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>203</v>
+        <v>160</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>205</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -9680,16 +6819,16 @@
         <v>11</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>207</v>
+        <v>164</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>208</v>
+        <v>165</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>25</v>
@@ -9700,16 +6839,16 @@
         <v>12</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>209</v>
+        <v>166</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>207</v>
+        <v>164</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>210</v>
+        <v>167</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>25</v>
@@ -9720,36 +6859,36 @@
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>211</v>
+        <v>168</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>187</v>
+        <v>144</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>212</v>
+        <v>169</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>213</v>
+        <v>170</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>214</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>215</v>
+        <v>172</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>207</v>
+        <v>164</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>216</v>
+        <v>173</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>27</v>
@@ -9757,22 +6896,22 @@
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>218</v>
-      </c>
       <c r="D13" s="4" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>219</v>
+        <v>176</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>220</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -9780,7 +6919,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>221</v>
+        <v>178</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
@@ -9792,60 +6931,60 @@
         <v>17</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>222</v>
+        <v>179</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>192</v>
+        <v>149</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>188</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="55" t="s">
-        <v>152</v>
-      </c>
-      <c r="B17" s="52"/>
-      <c r="C17" s="52"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="52"/>
-      <c r="F17" s="52"/>
+      <c r="A17" s="56" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" s="53"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>223</v>
+        <v>180</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>192</v>
+        <v>149</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>224</v>
+        <v>181</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>225</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="26" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>226</v>
+        <v>183</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>207</v>
+        <v>164</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>208</v>
+        <v>165</v>
       </c>
       <c r="F19" s="26" t="s">
         <v>25</v>
@@ -9853,39 +6992,39 @@
     </row>
     <row r="20" spans="1:6" ht="41.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>227</v>
+        <v>184</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>228</v>
+        <v>185</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>229</v>
+        <v>186</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>230</v>
+        <v>187</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>207</v>
+        <v>164</v>
       </c>
       <c r="D21" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="E21" s="26" t="s">
         <v>188</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>231</v>
       </c>
       <c r="F21" s="26" t="s">
         <v>25</v>
@@ -9893,70 +7032,70 @@
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>217</v>
+        <v>174</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>218</v>
+        <v>175</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>232</v>
+        <v>189</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="55" t="s">
-        <v>160</v>
-      </c>
-      <c r="B24" s="52"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="52"/>
-    </row>
-    <row r="25" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="56" t="s">
+        <v>117</v>
+      </c>
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
-        <v>234</v>
+        <v>191</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>235</v>
+        <v>192</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>192</v>
+        <v>149</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>236</v>
+        <v>193</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>237</v>
+        <v>194</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="26" t="s">
-        <v>238</v>
+        <v>195</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>239</v>
+        <v>196</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>207</v>
+        <v>164</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>240</v>
+        <v>197</v>
       </c>
       <c r="F26" s="26" t="s">
         <v>25</v>
@@ -9964,19 +7103,19 @@
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
-        <v>241</v>
+        <v>198</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>242</v>
+        <v>199</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>207</v>
+        <v>164</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="F27" s="26" t="s">
         <v>25</v>
@@ -9984,19 +7123,19 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="26" t="s">
-        <v>244</v>
+        <v>201</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>245</v>
+        <v>202</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>207</v>
+        <v>164</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="E28" s="26" t="s">
-        <v>246</v>
+        <v>203</v>
       </c>
       <c r="F28" s="26" t="s">
         <v>27</v>
@@ -10004,70 +7143,70 @@
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
-        <v>176</v>
+        <v>133</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>217</v>
+        <v>174</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>218</v>
+        <v>175</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="55" t="s">
-        <v>167</v>
-      </c>
-      <c r="B31" s="52"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="52"/>
+      <c r="A31" s="56" t="s">
+        <v>124</v>
+      </c>
+      <c r="B31" s="53"/>
+      <c r="C31" s="53"/>
+      <c r="D31" s="53"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="53"/>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="26" t="s">
-        <v>248</v>
+        <v>205</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>249</v>
+        <v>206</v>
       </c>
       <c r="C32" s="26" t="s">
-        <v>192</v>
+        <v>149</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>250</v>
+        <v>207</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>198</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="26" t="s">
-        <v>251</v>
+        <v>208</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>252</v>
+        <v>209</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>207</v>
+        <v>164</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="E33" s="26" t="s">
-        <v>253</v>
+        <v>210</v>
       </c>
       <c r="F33" s="26" t="s">
         <v>25</v>
@@ -10075,42 +7214,42 @@
     </row>
     <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="26" t="s">
-        <v>254</v>
+        <v>211</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>255</v>
+        <v>212</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>228</v>
+        <v>185</v>
       </c>
       <c r="D34" s="26" t="s">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="E34" s="26" t="s">
-        <v>256</v>
+        <v>213</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>257</v>
+        <v>214</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>217</v>
+        <v>174</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>218</v>
+        <v>175</v>
       </c>
       <c r="D35" s="26" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>258</v>
+        <v>215</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>233</v>
+        <v>190</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -11106,34 +8245,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
-        <v>259</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
+      <c r="A1" s="52" t="s">
+        <v>216</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
-        <v>260</v>
+        <v>217</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>261</v>
+        <v>218</v>
       </c>
       <c r="D3" s="25" t="s">
-        <v>262</v>
+        <v>219</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>263</v>
+        <v>220</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>264</v>
+        <v>221</v>
       </c>
       <c r="G3" s="25" t="s">
         <v>17</v>
@@ -11144,23 +8283,23 @@
         <v>11</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>265</v>
+        <v>222</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>266</v>
+        <v>223</v>
       </c>
       <c r="D4" s="42">
         <v>0.33329999999999999</v>
       </c>
       <c r="E4" s="42">
-        <f>IFERROR(COUNTIF(Documentos!G2:G7,"SIM")/COUNTA(Documentos!G2:G7)*D4,0)</f>
+        <f>IFERROR(COUNTIF(Documentos!G2:G3,"SIM")/COUNTA(Documentos!G2:G3)*D4,0)</f>
         <v>0.33329999999999999</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>267</v>
+        <v>224</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>268</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11171,20 +8310,20 @@
         <v>7</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>266</v>
+        <v>223</v>
       </c>
       <c r="D5" s="42">
         <v>0.33329999999999999</v>
       </c>
       <c r="E5" s="42">
-        <f>IFERROR(COUNTIF(Documentos!H2:H7,"SIM")/COUNTA(Documentos!H2:H7)*D5,0)</f>
+        <f>IFERROR(COUNTIF(Documentos!H2:H3,"SIM")/COUNTA(Documentos!H2:H3)*D5,0)</f>
         <v>0.33329999999999999</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>267</v>
+        <v>224</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>269</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11192,86 +8331,86 @@
         <v>13</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>270</v>
+        <v>227</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>266</v>
+        <v>223</v>
       </c>
       <c r="D6" s="42">
         <v>0.33339999999999997</v>
       </c>
       <c r="E6" s="42">
-        <f>IFERROR(COUNTIF(Documentos!J2:J7,"SIM")/COUNTA(Documentos!J2:J7)*D6,0)</f>
-        <v>0.33339999999999997</v>
+        <f>IFERROR(COUNTIF(Documentos!J2:J3,"SIM")/COUNTA(Documentos!J2:J3)*D6,0)</f>
+        <v>0</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>267</v>
+        <v>224</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>271</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>272</v>
+        <v>229</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>273</v>
+        <v>230</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4" t="s">
-        <v>267</v>
+        <v>224</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>274</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E8" s="27" t="s">
-        <v>275</v>
+        <v>232</v>
       </c>
       <c r="F8" s="28">
         <f>SUM(E4:E6)*100</f>
-        <v>100</v>
+        <v>66.66</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="55" t="s">
-        <v>276</v>
-      </c>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
+      <c r="A10" s="56" t="s">
+        <v>233</v>
+      </c>
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>266</v>
+        <v>223</v>
       </c>
       <c r="D11" s="44">
         <v>0.33329999999999999</v>
       </c>
       <c r="E11" s="43">
-        <f>IFERROR(COUNTIF(Indicadores!G2:G201,"SIM")/COUNTA(Indicadores!G2:G201)*D11,0)</f>
-        <v>0.33329999999999999</v>
+        <f>IFERROR(COUNTIF(#REF!,"SIM")/COUNTA(#REF!)*D11,0)</f>
+        <v>0</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>267</v>
+        <v>224</v>
       </c>
       <c r="G11" s="26" t="s">
-        <v>277</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="41.85" customHeight="1" x14ac:dyDescent="0.25">
@@ -11279,23 +8418,23 @@
         <v>12</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>278</v>
+        <v>235</v>
       </c>
       <c r="D12" s="44">
         <v>0.33329999999999999</v>
       </c>
       <c r="E12" s="43">
-        <f>IFERROR((COUNTIF(Indicadores!H2:H201,"Automático")+COUNTIF(Indicadores!H2:H201,"Manual")*0.5)/COUNTA(Indicadores!H2:H201)*D12,0)</f>
-        <v>0.33329999999999999</v>
+        <f>IFERROR((COUNTIF(#REF!,"Automático")+COUNTIF(#REF!,"Manual")*0.5)/COUNTA(#REF!)*D12,0)</f>
+        <v>0</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>267</v>
+        <v>224</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>279</v>
+        <v>236</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11303,91 +8442,91 @@
         <v>13</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>270</v>
+        <v>227</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>266</v>
+        <v>223</v>
       </c>
       <c r="D13" s="44">
         <v>0.33339999999999997</v>
       </c>
       <c r="E13" s="43">
-        <f>IFERROR(COUNTIF(Indicadores!I2:I201,"SIM")/COUNTA(Indicadores!I2:I201)*D13,0)</f>
-        <v>0.31378823529411765</v>
+        <f>IFERROR(COUNTIF(#REF!,"SIM")/COUNTA(#REF!)*D13,0)</f>
+        <v>0</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>267</v>
+        <v>224</v>
       </c>
       <c r="G13" s="26" t="s">
-        <v>280</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E14" s="10" t="s">
-        <v>275</v>
+        <v>232</v>
       </c>
       <c r="F14" s="29">
         <f>SUM(E11:E13)*100</f>
-        <v>98.038823529411758</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="55" t="s">
-        <v>281</v>
-      </c>
-      <c r="B16" s="52"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
-      <c r="F16" s="52"/>
-      <c r="G16" s="52"/>
+      <c r="A16" s="56" t="s">
+        <v>238</v>
+      </c>
+      <c r="B16" s="53"/>
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="53"/>
     </row>
     <row r="17" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>282</v>
+        <v>239</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>283</v>
+        <v>240</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>266</v>
+        <v>223</v>
       </c>
       <c r="D17" s="44">
         <v>0.33329999999999999</v>
       </c>
       <c r="E17" s="43">
         <f>IFERROR(COUNTIF(Treinamento!G2:G4,"SIM")/COUNTA(Treinamento!G2:G4)*D17,0)</f>
-        <v>0.33329999999999999</v>
+        <v>0.22219999999999998</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>267</v>
+        <v>224</v>
       </c>
       <c r="G17" s="26" t="s">
-        <v>284</v>
+        <v>241</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
-        <v>285</v>
+        <v>242</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>241</v>
+        <v>198</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>266</v>
+        <v>223</v>
       </c>
       <c r="D18" s="44">
         <v>0.33329999999999999</v>
       </c>
       <c r="E18" s="43">
-        <f>IFERROR(COUNTIF(Treinamento!H2:H4,"SIM")/COUNTA(Treinamento!H2:H4)*D18,0)</f>
-        <v>0.33329999999999999</v>
+        <f>IFERROR(COUNTIF(Treinamento!I2:I4,"SIM")/COUNTA(Treinamento!I2:I4)*D18,0)</f>
+        <v>0.22219999999999998</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>267</v>
+        <v>224</v>
       </c>
       <c r="G18" s="26" t="s">
-        <v>286</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11395,55 +8534,55 @@
         <v>12</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>244</v>
+        <v>201</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>266</v>
+        <v>223</v>
       </c>
       <c r="D19" s="44">
         <v>0.33339999999999997</v>
       </c>
       <c r="E19" s="43">
-        <f>IFERROR(COUNTIF(Treinamento!I2:I4,"SIM")/COUNTA(Treinamento!I2:I4)*D19,0)</f>
+        <f>IFERROR(COUNTIF(Treinamento!J2:J4,"SIM")/COUNTA(Treinamento!J2:J4)*D19,0)</f>
         <v>0</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>267</v>
+        <v>224</v>
       </c>
       <c r="G19" s="26" t="s">
-        <v>287</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E20" s="10" t="s">
-        <v>275</v>
+        <v>232</v>
       </c>
       <c r="F20" s="29">
         <f>SUM(E17:E19)*100</f>
-        <v>66.66</v>
+        <v>44.44</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="55" t="s">
-        <v>288</v>
-      </c>
-      <c r="B22" s="52"/>
-      <c r="C22" s="52"/>
-      <c r="D22" s="52"/>
-      <c r="E22" s="52"/>
-      <c r="F22" s="52"/>
-      <c r="G22" s="52"/>
+      <c r="A22" s="56" t="s">
+        <v>245</v>
+      </c>
+      <c r="B22" s="53"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="53"/>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
         <v>11</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>251</v>
+        <v>208</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>266</v>
+        <v>223</v>
       </c>
       <c r="D23" s="44">
         <v>0.5</v>
@@ -11453,21 +8592,21 @@
         <v>0.5</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>267</v>
+        <v>224</v>
       </c>
       <c r="G23" s="26" t="s">
-        <v>289</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="26" t="s">
-        <v>290</v>
+        <v>247</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>254</v>
+        <v>211</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>291</v>
+        <v>248</v>
       </c>
       <c r="D24" s="44">
         <v>0.5</v>
@@ -11477,15 +8616,15 @@
         <v>0</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>267</v>
+        <v>224</v>
       </c>
       <c r="G24" s="26" t="s">
-        <v>292</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E25" s="10" t="s">
-        <v>275</v>
+        <v>232</v>
       </c>
       <c r="F25" s="29">
         <f>SUM(E23:E24)*100</f>
@@ -12492,150 +9631,150 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
-        <v>293</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
+      <c r="A1" s="52" t="s">
+        <v>250</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>294</v>
+        <v>251</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>295</v>
+        <v>252</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>296</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>297</v>
+        <v>254</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>298</v>
+        <v>255</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>299</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>205</v>
+        <v>162</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>300</v>
+        <v>257</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>301</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>302</v>
+        <v>259</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>303</v>
+        <v>260</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>304</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>305</v>
+        <v>262</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>306</v>
+        <v>263</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>307</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>308</v>
+        <v>265</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>309</v>
+        <v>266</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>310</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="30" t="s">
-        <v>311</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="55.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="31" t="s">
-        <v>312</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="32" t="s">
-        <v>313</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
-        <v>314</v>
+        <v>271</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>315</v>
+        <v>272</v>
       </c>
       <c r="C14" s="34" t="s">
-        <v>316</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="33" t="s">
-        <v>317</v>
+        <v>274</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>318</v>
+        <v>275</v>
       </c>
       <c r="C15" s="34" t="s">
-        <v>319</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="33" t="s">
-        <v>320</v>
+        <v>277</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>321</v>
+        <v>278</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>322</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="33" t="s">
-        <v>323</v>
+        <v>280</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>324</v>
+        <v>281</v>
       </c>
       <c r="C17" s="34" t="s">
-        <v>325</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="35"/>
     </row>
     <row r="20" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="56"/>
-      <c r="B20" s="52"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
+      <c r="A20" s="57"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/formulario/F.O.091.GOCO Analise de Maturidade em Processos.xlsx
+++ b/formulario/F.O.091.GOCO Analise de Maturidade em Processos.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d23091b390d060c3/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A4B7DE8-6887-409D-8597-06C3144DC7B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{5A4B7DE8-6887-409D-8597-06C3144DC7B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A196019E-5078-45E1-AEA5-0481B8AF3854}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Documentos" sheetId="1" r:id="rId1"/>
-    <sheet name="Indicadores" sheetId="9" r:id="rId2"/>
+    <sheet name="Indicadores" sheetId="10" r:id="rId2"/>
     <sheet name="Treinamento" sheetId="3" r:id="rId3"/>
     <sheet name="Qualidade" sheetId="4" r:id="rId4"/>
     <sheet name="Resumo" sheetId="5" r:id="rId5"/>
@@ -23,14 +23,14 @@
     <sheet name="Como usar" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Documentos!$A$1:$P$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Documentos!$A$1:$O$49</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="275">
   <si>
     <t>ID Avaliação</t>
   </si>
@@ -44,9 +44,6 @@
     <t>Frente avaliada</t>
   </si>
   <si>
-    <t>Item avaliado</t>
-  </si>
-  <si>
     <t>Quantidade</t>
   </si>
   <si>
@@ -104,15 +101,9 @@
     <t>Banco — N1</t>
   </si>
   <si>
-    <t>Monitoria — Encerramento de leasing</t>
-  </si>
-  <si>
     <t>SIM</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>NÃO</t>
   </si>
   <si>
@@ -137,9 +128,6 @@
     <t>Backoffice — N2</t>
   </si>
   <si>
-    <t>Monitoria — Cessão de Direitos</t>
-  </si>
-  <si>
     <t>A monitoria existe e a avaliação registrada recebeu nota 100. Entretanto, o formulário é genérico para Banco e Locadora e não separa aspectos comportamentais e processuais solicitados pela operação. Foram evidenciados acompanhamento de telas e consulta à Wiki 'Cessão de Direitos - dúvidas e informações'. O documento D.C.198.EXTE, versão 2.0, de 21/06/2024, apresenta problema na data de edição.</t>
   </si>
   <si>
@@ -149,9 +137,6 @@
     <t>Clube FIQ</t>
   </si>
   <si>
-    <t>Monitoria — Clube FIQ</t>
-  </si>
-  <si>
     <t>Não há monitoria do Clube FIQ há três meses devido à reformulação em andamento.</t>
   </si>
   <si>
@@ -161,18 +146,12 @@
     <t>Qualidade e gestão do Clube FIQ</t>
   </si>
   <si>
-    <t>Nome_Documento</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Padrão</t>
   </si>
   <si>
     <t>Documentação</t>
   </si>
   <si>
-    <t>D.C.231.EXTE - Emissão de boletos e duvidas frequêntes</t>
-  </si>
-  <si>
     <t>NC 01: divergências de versão e data; o relatório não identifica a frente, o processo nem a data válida. Data da avaliação registrada pelo cabeçalho: 18/09/2026; o rodapé do relatório indica 16/09/2026.</t>
   </si>
   <si>
@@ -185,9 +164,6 @@
     <t>Locadora — N1</t>
   </si>
   <si>
-    <t>D.C.1504.EXTE - Promessa de pagamento e baixa de pagamento</t>
-  </si>
-  <si>
     <t>NC 03: datas de criação, modificação e aprovação duplicadas; o relatório não informa processo ou frente.</t>
   </si>
   <si>
@@ -197,9 +173,6 @@
     <t>Backoffice Locadora — N2</t>
   </si>
   <si>
-    <t>D.C.136.EXTE - Seguros e Sinistros</t>
-  </si>
-  <si>
     <t>O documento é denominado fluxograma, mas foi descrito como material de orientação ou passo a passo. Processo, frente e atualização não foram informados.</t>
   </si>
   <si>
@@ -209,9 +182,6 @@
     <t>Backoffice — Banco N2</t>
   </si>
   <si>
-    <t>D.C.016.EXTE - Kit pós aprovado - Cessão de direitos</t>
-  </si>
-  <si>
     <t>A sequência documental deve ser explicitada e os SLAs por fila precisam ser confirmados.</t>
   </si>
   <si>
@@ -221,7 +191,7 @@
     <t>Jeferson Oliveira</t>
   </si>
   <si>
-    <t>I.T.179.OPER - ORIENTAR QUANTO A TRATATIVA DE CLIENTES VIA CHAT</t>
+    <t>Backoffice — Locadora N2</t>
   </si>
   <si>
     <t xml:space="preserve"> Wikis desatualizadas e ausência de classificação de criticidade consolidada para todos os processos.</t>
@@ -254,27 +224,18 @@
     <t>Não Conformidade Grave</t>
   </si>
   <si>
-    <t>Material de treinamento e reciclagem — Banco N1</t>
-  </si>
-  <si>
     <t>NC 08: material existente sem controle de versão e sem evidência individual completa da reciclagem. Atualização e padronização não foram demonstradas.</t>
   </si>
   <si>
     <t>Versionar o material, vincular as fontes vigentes e completar a evidência individual da reciclagem.</t>
   </si>
   <si>
-    <t>Material e plano de treinamento — Locadora N1</t>
-  </si>
-  <si>
     <t>Há planos e materiais, porém faltou rastreabilidade da evidência individual. Atualização e padronização não foram demonstradas de forma suficiente.</t>
   </si>
   <si>
     <t>Vincular fontes vigentes, registrar versão e manter evidência individual da aplicação e reciclagem.</t>
   </si>
   <si>
-    <t>Estrutura de treinamento — BackOffice N2</t>
-  </si>
-  <si>
     <t>A estrutura foi considerada compatível, mas o relatório não apresenta data de atualização nem evidência suficiente de padronização do material.</t>
   </si>
   <si>
@@ -368,9 +329,6 @@
     <t>Indicadores existentes</t>
   </si>
   <si>
-    <t>Indicadores atualizados (automático ou manual)</t>
-  </si>
-  <si>
     <t>Indicadores no padrão</t>
   </si>
   <si>
@@ -884,22 +842,30 @@
     <t>Treinamento e Processos</t>
   </si>
   <si>
-    <t>Sube Aplicação</t>
-  </si>
-  <si>
-    <t>Monitoria — Infração</t>
+    <t xml:space="preserve">Indicadores atualizados </t>
+  </si>
+  <si>
+    <t>Aplicação?</t>
+  </si>
+  <si>
+    <t>Sub aplicação</t>
+  </si>
+  <si>
+    <t>Sub Aplicação</t>
+  </si>
+  <si>
+    <t>Conforme</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
+  <numFmts count="2">
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -991,6 +957,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1052,7 +1024,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1062,9 +1034,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1151,9 +1120,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1174,38 +1140,20 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="41">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="94">
     <dxf>
       <fill>
         <patternFill>
@@ -1377,6 +1325,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFE2F0D9"/>
         </patternFill>
       </fill>
@@ -1384,7 +1339,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1392,6 +1354,363 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1455,6 +1774,27 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1733,35 +2073,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z49"/>
+  <dimension ref="A1:Y49"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.5703125" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="181.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="110.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="26" width="8.7109375" customWidth="1"/>
+    <col min="5" max="6" width="16.42578125" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="181.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="110.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1774,46 +2112,46 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>5</v>
+      </c>
+      <c r="F1" s="60" t="s">
+        <v>271</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="K1" s="60" t="s">
+        <v>272</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="3" t="s">
@@ -1825,2066 +2163,1994 @@
       <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="3" t="s">
-        <v>21</v>
-      </c>
+      <c r="V1" s="3"/>
       <c r="W1" s="3"/>
       <c r="X1" s="3"/>
       <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
-    </row>
-    <row r="2" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+    </row>
+    <row r="2" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
         <v>928734</v>
       </c>
-      <c r="B2" s="36">
+      <c r="B2" s="35">
         <v>46283</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>23</v>
-      </c>
       <c r="E2" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="4">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>17</v>
+      <c r="I2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="4">
+        <f>IF(E2="","",IF(E2="Conformidade",1,IF(E2="Não conformidade",0,IF(E2="Não conformidade grave",-1,""))))</f>
+        <v>1</v>
+      </c>
+      <c r="K2" s="4">
+        <f>IF(F2="","",IF(F2="Conformidade",1,IF(F2="Não conformidade",0,IF(F2="Não conformidade grave",-1,""))))</f>
+        <v>1</v>
       </c>
       <c r="L2" s="4">
-        <f t="shared" ref="L2:L21" si="0">IF(G2="","",IF(G2="SIM",1,0))</f>
+        <f>IF(G2="","",IF(G2="Conformidade",1,IF(G2="Não conformidade",0,IF(G2="Não conformidade grave",-1,""))))</f>
         <v>1</v>
       </c>
       <c r="M2" s="4">
-        <f t="shared" ref="M2:M21" si="1">IF(H2="","",IF(H2="SIM",1,0))</f>
+        <f>IF(H2="","",IF(H2="Conformidade",1,IF(H2="Não conformidade",0,IF(H2="Não conformidade grave",-1,""))))</f>
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <f t="shared" ref="N2:N3" si="0">IF(I2="","",IF(I2="Conformidade",1,IF(I2="Não conformidade",0,IF(I2="Não conformidade grave",-1,""))))</f>
         <v>1</v>
       </c>
-      <c r="N2" s="4">
-        <f t="shared" ref="N2:N21" si="2">IF(J2="","",IF(J2="SIM",1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="O2" s="4" t="str">
-        <f t="shared" ref="O2:O3" si="3">IF(K2="","",IF(K2="Conformidade",1,IF(K2="Não conformidade",0,IF(K2="Não conformidade grave",-1,""))))</f>
-        <v/>
-      </c>
-      <c r="P2" s="4">
-        <f>IF(COUNTA(G2,H2,J2,K2)=0,"",ROUND(AVERAGE(L2:O2)*100,0))</f>
-        <v>67</v>
-      </c>
-      <c r="Q2" s="6">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C2,P$2:P$49),"N/A")</f>
-        <v>76.8</v>
+      <c r="O2" s="4">
+        <f>IF(COUNTA(E2,G2,H2,I2)=0,"",ROUND(AVERAGE(J2:N2)*100,0))</f>
+        <v>80</v>
+      </c>
+      <c r="P2" s="5">
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C2,O$2:O$49),"N/A")</f>
+        <v>84</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>40</v>
       </c>
       <c r="R2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="S2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="T2" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="U2" t="s">
-        <v>32</v>
-      </c>
-      <c r="V2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>928734</v>
       </c>
-      <c r="B3" s="36">
+      <c r="B3" s="35">
         <v>46283</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" s="4">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>17</v>
+      <c r="I3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="4">
+        <f t="shared" ref="J3:J6" si="1">IF(E3="","",IF(E3="Conformidade",1,IF(E3="Não conformidade",0,IF(E3="Não conformidade grave",-1,""))))</f>
+        <v>1</v>
+      </c>
+      <c r="K3" s="4">
+        <f t="shared" ref="K3:K6" si="2">IF(F3="","",IF(F3="Conformidade",1,IF(F3="Não conformidade",0,IF(F3="Não conformidade grave",-1,""))))</f>
+        <v>1</v>
       </c>
       <c r="L3" s="4">
+        <f t="shared" ref="L3:L49" si="3">IF(G3="","",IF(G3="Conformidade",1,IF(G3="Não conformidade",0,IF(G3="Não conformidade grave",-1,""))))</f>
+        <v>1</v>
+      </c>
+      <c r="M3" s="4">
+        <f t="shared" ref="M3:M49" si="4">IF(H3="","",IF(H3="Conformidade",1,IF(H3="Não conformidade",0,IF(H3="Não conformidade grave",-1,""))))</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="M3" s="4">
+      <c r="O3" s="4">
+        <f>IF(COUNTA(E3,G3,H3)=0,"",ROUND(AVERAGE(J3:N3)*100,0))</f>
+        <v>80</v>
+      </c>
+      <c r="P3" s="5">
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C3,O$2:O$49),"N/A")</f>
+        <v>84</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S3" t="s">
+        <v>42</v>
+      </c>
+      <c r="T3" t="s">
+        <v>29</v>
+      </c>
+      <c r="U3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>928734</v>
+      </c>
+      <c r="B4" s="35">
+        <v>46283</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="4">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N3" s="4">
+      <c r="K4" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O3" s="4" t="str">
+        <v>1</v>
+      </c>
+      <c r="L4" s="4">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="P3" s="4">
-        <f>IF(COUNTA(G3,H3,J3)=0,"",ROUND(AVERAGE(L3:O3)*100,0))</f>
-        <v>67</v>
-      </c>
-      <c r="Q3" s="6">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C3,P$2:P$49),"N/A")</f>
-        <v>76.8</v>
-      </c>
-      <c r="R3" t="s">
-        <v>52</v>
-      </c>
-      <c r="S3" t="s">
-        <v>53</v>
-      </c>
-      <c r="T3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" s="4">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <f t="shared" ref="N4:N27" si="5">IF(I4="","",IF(I4="Conformidade",1,IF(I4="Não Conformidade",0,IF(I4="Não Conformidade Grave",-1,""))))</f>
+        <v>1</v>
+      </c>
+      <c r="O4" s="37">
+        <f>IF(COUNTA(E4,G4,H4,I4)=0,"",ROUND(AVERAGE(J4:N4)*100,0))</f>
+        <v>100</v>
+      </c>
+      <c r="P4" s="38">
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C4,O$2:O$49),"N/A")</f>
+        <v>84</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>47</v>
+      </c>
+      <c r="R4" t="s">
+        <v>48</v>
+      </c>
+      <c r="S4" t="s">
+        <v>42</v>
+      </c>
+      <c r="T4" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="U4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>928734</v>
+      </c>
+      <c r="B5" s="35">
+        <v>46283</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="U3" t="s">
-        <v>32</v>
-      </c>
-      <c r="V3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>928734</v>
-      </c>
-      <c r="B4" s="36">
-        <v>46283</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F4" s="4">
-        <v>1</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L4" s="4">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M4" s="4">
+      <c r="E5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="4">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N4" s="4">
+      <c r="K5" s="4">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="O4" s="4">
-        <f t="shared" ref="O4:O27" si="4">IF(K4="","",IF(K4="Conformidade",1,IF(K4="Não Conformidade",0,IF(K4="Não Conformidade Grave",-1,""))))</f>
+      <c r="L5" s="4">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="P4" s="38">
-        <f t="shared" ref="P4:P26" si="5">IF(COUNTA(G4,H4,J4,K4)=0,"",ROUND(AVERAGE(L4:O4)*100,0))</f>
+      <c r="M5" s="4">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="N5" s="4">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O5" s="37">
+        <f>IF(COUNTA(E5,G5,H5,I5)=0,"",ROUND(AVERAGE(J5:N5)*100,0))</f>
         <v>100</v>
       </c>
-      <c r="Q4" s="39">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C4,P$2:P$49),"N/A")</f>
-        <v>76.8</v>
-      </c>
-      <c r="R4" t="s">
-        <v>56</v>
-      </c>
-      <c r="S4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T4" t="s">
-        <v>49</v>
-      </c>
-      <c r="U4" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="V4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+      <c r="P5" s="38">
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C5,O$2:O$49),"N/A")</f>
+        <v>84</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>50</v>
+      </c>
+      <c r="R5" t="s">
+        <v>51</v>
+      </c>
+      <c r="S5" t="s">
+        <v>52</v>
+      </c>
+      <c r="T5" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="U5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>928734</v>
       </c>
-      <c r="B5" s="36">
+      <c r="B6" s="35">
         <v>46283</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F5" s="4">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4" t="s">
+      <c r="C6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L5" s="4">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M5" s="4">
+      <c r="J6" s="4">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N5" s="4">
+      <c r="K6" s="4">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="O5" s="4">
+      <c r="L6" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M6" s="4">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="P5" s="38">
+      <c r="N6" s="4">
         <f t="shared" si="5"/>
-        <v>100</v>
-      </c>
-      <c r="Q5" s="39">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C5,P$2:P$49),"N/A")</f>
-        <v>76.8</v>
-      </c>
-      <c r="R5" t="s">
+        <v>0</v>
+      </c>
+      <c r="O6" s="37">
+        <f>IF(COUNTA(E6,G6,H6,I6)=0,"",ROUND(AVERAGE(J6:N6)*100,0))</f>
         <v>60</v>
       </c>
-      <c r="S5" t="s">
-        <v>61</v>
-      </c>
-      <c r="T5" t="s">
-        <v>62</v>
-      </c>
-      <c r="U5" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="V5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>928734</v>
-      </c>
-      <c r="B6" s="36">
-        <v>46283</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F6" s="4">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L6" s="4">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="M6" s="4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N6" s="4">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="O6" s="4">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
       <c r="P6" s="38">
-        <f t="shared" si="5"/>
-        <v>50</v>
-      </c>
-      <c r="Q6" s="39">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C6,P$2:P$49),"N/A")</f>
-        <v>76.8</v>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C6,O$2:O$49),"N/A")</f>
+        <v>84</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>54</v>
       </c>
       <c r="R6" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="S6" t="s">
-        <v>65</v>
-      </c>
-      <c r="T6" t="s">
-        <v>66</v>
-      </c>
-      <c r="U6" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="V6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="T6" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="U6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
-      <c r="B7" s="36"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4" t="str">
+        <f t="shared" ref="J7:J49" si="6">IF(E7="","",IF(E7="Conformidade",1,IF(E7="Não conformidade",0,IF(E7="Não conformidade grave",-1,""))))</f>
+        <v/>
+      </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M7" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N7" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O7" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O7" s="37" t="str">
+        <f>IF(COUNTA(E7,G7,H7,I7)=0,"",ROUND(AVERAGE(J7:N7)*100,0))</f>
         <v/>
       </c>
       <c r="P7" s="38" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Q7" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C7,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C7,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U7" s="37"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="T7" s="36"/>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
-      <c r="B8" s="36"/>
+      <c r="B8" s="35"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M8" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N8" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O8" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O8" s="37" t="str">
+        <f>IF(COUNTA(E8,G8,H8,I8)=0,"",ROUND(AVERAGE(J8:N8)*100,0))</f>
         <v/>
       </c>
       <c r="P8" s="38" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Q8" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C8,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C8,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U8" s="37"/>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="T8" s="36"/>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
-      <c r="B9" s="36"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M9" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N9" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O9" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O9" s="37" t="str">
+        <f>IF(COUNTA(E9,G9,H9,I9)=0,"",ROUND(AVERAGE(J9:N9)*100,0))</f>
         <v/>
       </c>
       <c r="P9" s="38" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Q9" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C9,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C9,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U9" s="37"/>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="T9" s="36"/>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="4"/>
-      <c r="B10" s="36"/>
+      <c r="B10" s="35"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M10" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N10" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O10" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O10" s="37" t="str">
+        <f>IF(COUNTA(E10,G10,H10,I10)=0,"",ROUND(AVERAGE(J10:N10)*100,0))</f>
         <v/>
       </c>
       <c r="P10" s="38" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Q10" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C10,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C10,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U10" s="37"/>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="T10" s="36"/>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
-      <c r="B11" s="36"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M11" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N11" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O11" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O11" s="37" t="str">
+        <f>IF(COUNTA(E11,G11,H11,I11)=0,"",ROUND(AVERAGE(J11:N11)*100,0))</f>
         <v/>
       </c>
       <c r="P11" s="38" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Q11" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C11,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C11,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U11" s="37"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="T11" s="36"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="4"/>
-      <c r="B12" s="36"/>
+      <c r="B12" s="35"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M12" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N12" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O12" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O12" s="37" t="str">
+        <f>IF(COUNTA(E12,G12,H12,I12)=0,"",ROUND(AVERAGE(J12:N12)*100,0))</f>
         <v/>
       </c>
       <c r="P12" s="38" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Q12" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C12,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C12,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U12" s="37"/>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="T12" s="36"/>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="4"/>
-      <c r="B13" s="36"/>
+      <c r="B13" s="35"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M13" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N13" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O13" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O13" s="37" t="str">
+        <f>IF(COUNTA(E13,G13,H13,I13)=0,"",ROUND(AVERAGE(J13:N13)*100,0))</f>
         <v/>
       </c>
       <c r="P13" s="38" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Q13" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C13,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C13,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U13" s="37"/>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="T13" s="36"/>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
-      <c r="B14" s="36"/>
+      <c r="B14" s="35"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M14" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N14" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O14" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O14" s="37" t="str">
+        <f>IF(COUNTA(E14,G14,H14,I14)=0,"",ROUND(AVERAGE(J14:N14)*100,0))</f>
         <v/>
       </c>
       <c r="P14" s="38" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Q14" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C14,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C14,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U14" s="37"/>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="T14" s="36"/>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="4"/>
-      <c r="B15" s="36"/>
+      <c r="B15" s="35"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M15" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N15" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O15" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O15" s="37" t="str">
+        <f>IF(COUNTA(E15,G15,H15,I15)=0,"",ROUND(AVERAGE(J15:N15)*100,0))</f>
         <v/>
       </c>
       <c r="P15" s="38" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Q15" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C15,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C15,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U15" s="37"/>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="T15" s="36"/>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="4"/>
-      <c r="B16" s="36"/>
+      <c r="B16" s="35"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
-      <c r="I16" s="36"/>
-      <c r="J16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M16" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N16" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O16" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O16" s="37" t="str">
+        <f>IF(COUNTA(E16,G16,H16,I16)=0,"",ROUND(AVERAGE(J16:N16)*100,0))</f>
         <v/>
       </c>
       <c r="P16" s="38" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Q16" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C16,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C16,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U16" s="37"/>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T16" s="36"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
-      <c r="B17" s="36"/>
+      <c r="B17" s="35"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M17" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N17" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O17" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O17" s="37" t="str">
+        <f>IF(COUNTA(E17,G17,H17,I17)=0,"",ROUND(AVERAGE(J17:N17)*100,0))</f>
         <v/>
       </c>
       <c r="P17" s="38" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Q17" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C17,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C17,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U17" s="37"/>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T17" s="36"/>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="4"/>
-      <c r="B18" s="36"/>
+      <c r="B18" s="35"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M18" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N18" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O18" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O18" s="37" t="str">
+        <f>IF(COUNTA(E18,G18,H18,I18)=0,"",ROUND(AVERAGE(J18:N18)*100,0))</f>
         <v/>
       </c>
       <c r="P18" s="38" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Q18" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C18,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C18,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U18" s="37"/>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T18" s="36"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="4"/>
-      <c r="B19" s="36"/>
+      <c r="B19" s="35"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
-      <c r="I19" s="36"/>
-      <c r="J19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M19" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N19" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O19" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O19" s="37" t="str">
+        <f>IF(COUNTA(E19,G19,H19,I19)=0,"",ROUND(AVERAGE(J19:N19)*100,0))</f>
         <v/>
       </c>
       <c r="P19" s="38" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Q19" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C19,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C19,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U19" s="37"/>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T19" s="36"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
-      <c r="B20" s="36"/>
+      <c r="B20" s="35"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M20" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N20" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O20" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O20" s="37" t="str">
+        <f>IF(COUNTA(E20,G20,H20,I20)=0,"",ROUND(AVERAGE(J20:N20)*100,0))</f>
         <v/>
       </c>
       <c r="P20" s="38" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Q20" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C20,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C20,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U20" s="37"/>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T20" s="36"/>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
-      <c r="B21" s="36"/>
+      <c r="B21" s="35"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M21" s="4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N21" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="O21" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O21" s="37" t="str">
+        <f>IF(COUNTA(E21,G21,H21,I21)=0,"",ROUND(AVERAGE(J21:N21)*100,0))</f>
         <v/>
       </c>
       <c r="P21" s="38" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Q21" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C21,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C21,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U21" s="37"/>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T21" s="36"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
-      <c r="B22" s="36"/>
+      <c r="B22" s="35"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4" t="str">
-        <f t="shared" ref="L22:L49" si="6">IF(G22="","",IF(G22="SIM",1,0))</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M22" s="4" t="str">
-        <f t="shared" ref="M22:M49" si="7">IF(H22="","",IF(H22="SIM",1,0))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N22" s="4" t="str">
-        <f t="shared" ref="N22:N49" si="8">IF(J22="","",IF(J22="SIM",1,0))</f>
-        <v/>
-      </c>
-      <c r="O22" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O22" s="37" t="str">
+        <f>IF(COUNTA(E22,G22,H22,I22)=0,"",ROUND(AVERAGE(J22:N22)*100,0))</f>
         <v/>
       </c>
       <c r="P22" s="38" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Q22" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C22,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C22,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U22" s="37"/>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T22" s="36"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
-      <c r="B23" s="36"/>
+      <c r="B23" s="35"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M23" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N23" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O23" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O23" s="37" t="str">
+        <f>IF(COUNTA(E23,G23,H23,I23)=0,"",ROUND(AVERAGE(J23:N23)*100,0))</f>
         <v/>
       </c>
       <c r="P23" s="38" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Q23" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C23,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C23,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U23" s="37"/>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T23" s="36"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
-      <c r="B24" s="36"/>
+      <c r="B24" s="35"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M24" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N24" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O24" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O24" s="37" t="str">
+        <f>IF(COUNTA(E24,G24,H24,I24)=0,"",ROUND(AVERAGE(J24:N24)*100,0))</f>
         <v/>
       </c>
       <c r="P24" s="38" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Q24" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C24,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C24,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U24" s="37"/>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T24" s="36"/>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="4"/>
-      <c r="B25" s="36"/>
+      <c r="B25" s="35"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M25" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N25" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O25" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O25" s="37" t="str">
+        <f>IF(COUNTA(E25,G25,H25,I25)=0,"",ROUND(AVERAGE(J25:N25)*100,0))</f>
         <v/>
       </c>
       <c r="P25" s="38" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Q25" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C25,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C25,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U25" s="37"/>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T25" s="36"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
-      <c r="B26" s="36"/>
+      <c r="B26" s="35"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M26" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N26" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O26" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O26" s="37" t="str">
+        <f>IF(COUNTA(E26,G26,H26,I26)=0,"",ROUND(AVERAGE(J26:N26)*100,0))</f>
         <v/>
       </c>
       <c r="P26" s="38" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Q26" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C26,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C26,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U26" s="37"/>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T26" s="36"/>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="4"/>
-      <c r="B27" s="36"/>
+      <c r="B27" s="35"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M27" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N27" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O27" s="4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="O27" s="37" t="str">
+        <f>IF(COUNTA(E27,G27,H27,I27)=0,"",ROUND(AVERAGE(J27:N27)*100,0))</f>
         <v/>
       </c>
       <c r="P27" s="38" t="str">
-        <f t="shared" ref="P27:P49" si="9">IF(COUNTA(G27,H27,J27,K27)=0,"",ROUND(AVERAGE(L27:O27)*100,0))</f>
-        <v/>
-      </c>
-      <c r="Q27" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C27,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C27,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U27" s="37"/>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T27" s="36"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
-      <c r="B28" s="36"/>
+      <c r="B28" s="35"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M28" s="4" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="N28" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O28" s="4" t="str">
-        <f t="shared" ref="O28:O49" si="10">IF(K28="","",IF(K28="Conformidade",1,IF(K28="Não Conformidade",0,IF(K28="Não Conformidade Grave",-1,""))))</f>
+        <f t="shared" ref="N28:N49" si="7">IF(I28="","",IF(I28="Conformidade",1,IF(I28="Não Conformidade",0,IF(I28="Não Conformidade Grave",-1,""))))</f>
+        <v/>
+      </c>
+      <c r="O28" s="37" t="str">
+        <f>IF(COUNTA(E28,G28,H28,I28)=0,"",ROUND(AVERAGE(J28:N28)*100,0))</f>
         <v/>
       </c>
       <c r="P28" s="38" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q28" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C28,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C28,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U28" s="37"/>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T28" s="36"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
-      <c r="B29" s="36"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
-      <c r="I29" s="36"/>
-      <c r="J29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M29" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N29" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N29" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O29" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="O29" s="37" t="str">
+        <f>IF(COUNTA(E29,G29,H29,I29)=0,"",ROUND(AVERAGE(J29:N29)*100,0))</f>
         <v/>
       </c>
       <c r="P29" s="38" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q29" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C29,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C29,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U29" s="37"/>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T29" s="36"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="4"/>
-      <c r="B30" s="36"/>
+      <c r="B30" s="35"/>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M30" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N30" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N30" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O30" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="O30" s="37" t="str">
+        <f>IF(COUNTA(E30,G30,H30,I30)=0,"",ROUND(AVERAGE(J30:N30)*100,0))</f>
         <v/>
       </c>
       <c r="P30" s="38" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q30" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C30,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C30,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U30" s="37"/>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T30" s="36"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="4"/>
-      <c r="B31" s="36"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
       <c r="H31" s="4"/>
-      <c r="I31" s="36"/>
-      <c r="J31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M31" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N31" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N31" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O31" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="O31" s="37" t="str">
+        <f>IF(COUNTA(E31,G31,H31,I31)=0,"",ROUND(AVERAGE(J31:N31)*100,0))</f>
         <v/>
       </c>
       <c r="P31" s="38" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q31" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C31,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C31,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U31" s="37"/>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T31" s="36"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
-      <c r="B32" s="36"/>
+      <c r="B32" s="35"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M32" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N32" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N32" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O32" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="O32" s="37" t="str">
+        <f>IF(COUNTA(E32,G32,H32,I32)=0,"",ROUND(AVERAGE(J32:N32)*100,0))</f>
         <v/>
       </c>
       <c r="P32" s="38" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q32" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C32,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C32,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U32" s="37"/>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T32" s="36"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
-      <c r="B33" s="36"/>
+      <c r="B33" s="35"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
-      <c r="I33" s="36"/>
-      <c r="J33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M33" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N33" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N33" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O33" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="O33" s="37" t="str">
+        <f>IF(COUNTA(E33,G33,H33,I33)=0,"",ROUND(AVERAGE(J33:N33)*100,0))</f>
         <v/>
       </c>
       <c r="P33" s="38" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q33" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C33,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C33,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U33" s="37"/>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T33" s="36"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
-      <c r="B34" s="36"/>
+      <c r="B34" s="35"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M34" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N34" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N34" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O34" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="O34" s="37" t="str">
+        <f>IF(COUNTA(E34,G34,H34,I34)=0,"",ROUND(AVERAGE(J34:N34)*100,0))</f>
         <v/>
       </c>
       <c r="P34" s="38" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q34" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C34,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C34,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U34" s="37"/>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T34" s="36"/>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
-      <c r="B35" s="36"/>
+      <c r="B35" s="35"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
       <c r="H35" s="4"/>
-      <c r="I35" s="36"/>
-      <c r="J35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M35" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N35" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N35" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O35" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="O35" s="37" t="str">
+        <f>IF(COUNTA(E35,G35,H35,I35)=0,"",ROUND(AVERAGE(J35:N35)*100,0))</f>
         <v/>
       </c>
       <c r="P35" s="38" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q35" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C35,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C35,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U35" s="37"/>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T35" s="36"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
-      <c r="B36" s="36"/>
+      <c r="B36" s="35"/>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
-      <c r="I36" s="36"/>
-      <c r="J36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M36" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N36" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N36" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O36" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="O36" s="37" t="str">
+        <f>IF(COUNTA(E36,G36,H36,I36)=0,"",ROUND(AVERAGE(J36:N36)*100,0))</f>
         <v/>
       </c>
       <c r="P36" s="38" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q36" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C36,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C36,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U36" s="37"/>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T36" s="36"/>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
-      <c r="B37" s="36"/>
+      <c r="B37" s="35"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
-      <c r="I37" s="36"/>
-      <c r="J37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M37" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N37" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N37" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O37" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="O37" s="37" t="str">
+        <f>IF(COUNTA(E37,G37,H37,I37)=0,"",ROUND(AVERAGE(J37:N37)*100,0))</f>
         <v/>
       </c>
       <c r="P37" s="38" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q37" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C37,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C37,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U37" s="37"/>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T37" s="36"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
-      <c r="B38" s="36"/>
+      <c r="B38" s="35"/>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
       <c r="H38" s="4"/>
-      <c r="I38" s="36"/>
-      <c r="J38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M38" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N38" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N38" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O38" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="O38" s="37" t="str">
+        <f>IF(COUNTA(E38,G38,H38,I38)=0,"",ROUND(AVERAGE(J38:N38)*100,0))</f>
         <v/>
       </c>
       <c r="P38" s="38" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q38" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C38,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C38,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U38" s="37"/>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T38" s="36"/>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="4"/>
-      <c r="B39" s="36"/>
+      <c r="B39" s="35"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
-      <c r="I39" s="36"/>
-      <c r="J39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M39" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N39" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N39" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O39" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="O39" s="37" t="str">
+        <f>IF(COUNTA(E39,G39,H39,I39)=0,"",ROUND(AVERAGE(J39:N39)*100,0))</f>
         <v/>
       </c>
       <c r="P39" s="38" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q39" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C39,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C39,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U39" s="37"/>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T39" s="36"/>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="4"/>
-      <c r="B40" s="36"/>
+      <c r="B40" s="35"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
-      <c r="I40" s="36"/>
-      <c r="J40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M40" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N40" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N40" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O40" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="O40" s="37" t="str">
+        <f>IF(COUNTA(E40,G40,H40,I40)=0,"",ROUND(AVERAGE(J40:N40)*100,0))</f>
         <v/>
       </c>
       <c r="P40" s="38" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q40" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C40,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C40,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U40" s="37"/>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T40" s="36"/>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="4"/>
-      <c r="B41" s="36"/>
+      <c r="B41" s="35"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
-      <c r="I41" s="36"/>
-      <c r="J41" s="4"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M41" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N41" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N41" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O41" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="O41" s="37" t="str">
+        <f>IF(COUNTA(E41,G41,H41,I41)=0,"",ROUND(AVERAGE(J41:N41)*100,0))</f>
         <v/>
       </c>
       <c r="P41" s="38" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q41" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C41,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C41,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U41" s="37"/>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T41" s="36"/>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="4"/>
-      <c r="B42" s="36"/>
+      <c r="B42" s="35"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
-      <c r="I42" s="36"/>
-      <c r="J42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M42" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N42" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N42" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O42" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="O42" s="37" t="str">
+        <f>IF(COUNTA(E42,G42,H42,I42)=0,"",ROUND(AVERAGE(J42:N42)*100,0))</f>
         <v/>
       </c>
       <c r="P42" s="38" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q42" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C42,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C42,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U42" s="37"/>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T42" s="36"/>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" s="4"/>
-      <c r="B43" s="36"/>
+      <c r="B43" s="35"/>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
-      <c r="I43" s="36"/>
-      <c r="J43" s="4"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M43" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N43" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N43" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O43" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="O43" s="37" t="str">
+        <f>IF(COUNTA(E43,G43,H43,I43)=0,"",ROUND(AVERAGE(J43:N43)*100,0))</f>
         <v/>
       </c>
       <c r="P43" s="38" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q43" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C43,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C43,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U43" s="37"/>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T43" s="36"/>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="4"/>
-      <c r="B44" s="36"/>
+      <c r="B44" s="35"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
       <c r="H44" s="4"/>
-      <c r="I44" s="36"/>
-      <c r="J44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M44" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N44" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N44" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O44" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="O44" s="37" t="str">
+        <f>IF(COUNTA(E44,G44,H44,I44)=0,"",ROUND(AVERAGE(J44:N44)*100,0))</f>
         <v/>
       </c>
       <c r="P44" s="38" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q44" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C44,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C44,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U44" s="37"/>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T44" s="36"/>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>
-      <c r="B45" s="36"/>
+      <c r="B45" s="35"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
       <c r="H45" s="4"/>
-      <c r="I45" s="36"/>
-      <c r="J45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M45" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N45" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N45" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O45" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="O45" s="37" t="str">
+        <f>IF(COUNTA(E45,G45,H45,I45)=0,"",ROUND(AVERAGE(J45:N45)*100,0))</f>
         <v/>
       </c>
       <c r="P45" s="38" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q45" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C45,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C45,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U45" s="37"/>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T45" s="36"/>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="4"/>
-      <c r="B46" s="36"/>
+      <c r="B46" s="35"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
-      <c r="I46" s="36"/>
-      <c r="J46" s="4"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M46" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N46" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N46" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O46" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="O46" s="37" t="str">
+        <f>IF(COUNTA(E46,G46,H46,I46)=0,"",ROUND(AVERAGE(J46:N46)*100,0))</f>
         <v/>
       </c>
       <c r="P46" s="38" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q46" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C46,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C46,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U46" s="37"/>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T46" s="36"/>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
-      <c r="B47" s="36"/>
+      <c r="B47" s="35"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
-      <c r="I47" s="36"/>
-      <c r="J47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M47" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N47" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N47" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O47" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="O47" s="37" t="str">
+        <f>IF(COUNTA(E47,G47,H47,I47)=0,"",ROUND(AVERAGE(J47:N47)*100,0))</f>
         <v/>
       </c>
       <c r="P47" s="38" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q47" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C47,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C47,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U47" s="37"/>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T47" s="36"/>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
-      <c r="B48" s="36"/>
+      <c r="B48" s="35"/>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
-      <c r="I48" s="36"/>
-      <c r="J48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M48" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N48" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N48" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O48" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="O48" s="37" t="str">
+        <f>IF(COUNTA(E48,G48,H48,I48)=0,"",ROUND(AVERAGE(J48:N48)*100,0))</f>
         <v/>
       </c>
       <c r="P48" s="38" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q48" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C48,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C48,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U48" s="37"/>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="T48" s="36"/>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
-      <c r="B49" s="36"/>
+      <c r="B49" s="35"/>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
       <c r="H49" s="4"/>
-      <c r="I49" s="36"/>
-      <c r="J49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="M49" s="4" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="N49" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="N49" s="4" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="O49" s="4" t="str">
-        <f t="shared" si="10"/>
+      <c r="O49" s="37" t="str">
+        <f>IF(COUNTA(E49,G49,H49,I49)=0,"",ROUND(AVERAGE(J49:N49)*100,0))</f>
         <v/>
       </c>
       <c r="P49" s="38" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="Q49" s="39" t="str">
-        <f>IFERROR(AVERAGEIF(C$2:C$49,C49,P$2:P$49),"N/A")</f>
+        <f>IFERROR(AVERAGEIF(C$2:C$49,C49,O$2:O$49),"N/A")</f>
         <v>N/A</v>
       </c>
-      <c r="U49" s="37"/>
+      <c r="T49" s="36"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P49" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="G2:H49 K3:K992 J3:J49">
-    <cfRule type="cellIs" dxfId="40" priority="4" operator="equal">
+  <autoFilter ref="A1:O49" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="I2:I992 E2:H49">
+    <cfRule type="cellIs" dxfId="93" priority="14" operator="equal">
       <formula>"SIM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="15" operator="equal">
       <formula>"NÃO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:K2">
-    <cfRule type="cellIs" dxfId="38" priority="6" operator="equal">
-      <formula>"SIM"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="7" operator="equal">
-      <formula>"NÃO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q50:Q992 P2:Q49">
-    <cfRule type="cellIs" dxfId="36" priority="8" operator="lessThan">
+  <conditionalFormatting sqref="P50:P992 O2:P49">
+    <cfRule type="cellIs" dxfId="91" priority="18" operator="lessThan">
       <formula>50</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="9" operator="between">
+    <cfRule type="cellIs" dxfId="90" priority="19" operator="between">
       <formula>50</formula>
       <formula>79</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="10" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="89" priority="20" operator="greaterThanOrEqual">
       <formula>80</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="5">
-    <dataValidation type="date" allowBlank="1" sqref="I2:I3 B2:B3" xr:uid="{00000000-0002-0000-0000-000002000000}">
+  <dataValidations count="3">
+    <dataValidation type="date" allowBlank="1" sqref="B2:B3" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>DATE(2000,1,1)</formula1>
       <formula2>DATE(2100,12,31)</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" sqref="F2:F3" xr:uid="{00000000-0002-0000-0000-000003000000}">
-      <formula1>0</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:H6 J2:J6" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"SIM,NÃO"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="K2:K992" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I992 E2:H6" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Não Conformidade Grave,Não Conformidade,Conformidade,Observação"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="V2:V992" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="U2:U992" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"Aberto,Em andamento,Concluído"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3894,39 +4160,38 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77E52904-D6E8-4CC9-A67B-383FD537F806}">
-  <dimension ref="A1:V5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF11285C-61F3-45E4-8207-1F00B97B91FD}">
+  <dimension ref="A1:U5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" style="37" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" style="36" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" customWidth="1"/>
-    <col min="8" max="8" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.140625" customWidth="1"/>
+    <col min="9" max="9" width="18.28515625" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="36" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -3936,40 +4201,40 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="58" t="s">
-        <v>242</v>
+        <v>58</v>
+      </c>
+      <c r="F1" s="56" t="s">
+        <v>228</v>
+      </c>
+      <c r="G1" t="s">
+        <v>60</v>
       </c>
       <c r="H1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" t="s">
-        <v>70</v>
+        <v>9</v>
+      </c>
+      <c r="I1" s="56" t="s">
+        <v>11</v>
       </c>
       <c r="J1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="56" t="s">
+        <v>273</v>
+      </c>
+      <c r="L1" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="56" t="s">
+        <v>274</v>
+      </c>
+      <c r="N1" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="58" t="s">
-        <v>284</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
       <c r="O1" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="P1" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="Q1" t="s">
         <v>16</v>
@@ -3986,163 +4251,155 @@
       <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>928734</v>
       </c>
-      <c r="B2" s="37">
+      <c r="B2" s="36">
         <v>46283</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2">
+        <v>31</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2">
+        <f>IF(E2="","",IF(E2="Conformidade",1,IF(E2="Não Conformidade",0,IF(E2="Não Conformidade Grave",-1,""))))</f>
         <v>1</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="K2">
-        <f>IF(F2="","",IF(F2="SIM",1,0))</f>
+        <f t="shared" ref="K2:M5" si="0">IF(F2="","",IF(F2="Conformidade",1,IF(F2="Não Conformidade",0,IF(F2="Não Conformidade Grave",-1,""))))</f>
         <v>1</v>
       </c>
       <c r="L2">
-        <f>IF(G2="","",IF(G2="SIM",1,0))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="M2">
-        <f>IF(H2="","",IF(H2="Automático",1,IF(H2="Manual",0.5,IF(H2="Não atualizado",0,""))))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="N2">
-        <f>IF(I2="","",IF(I2="SIM",1,0))</f>
+        <f>IF(I2="","",IF(I2="Conformidade",1,IF(I2="Não Conformidade",0,IF(I2="Não Conformidade Grave",-1,""))))</f>
         <v>1</v>
       </c>
-      <c r="O2" t="str">
-        <f>IF(J2="","",IF(J2="Conformidade",1,IF(J2="Não Conformidade",0,IF(J2="Não Conformidade Grave",-1,""))))</f>
-        <v/>
-      </c>
-      <c r="P2">
-        <f>IF(COUNTA(F2:J2)=0,"",ROUND(AVERAGE(K2:O2)*100,0))</f>
+      <c r="O2">
+        <f>IF(COUNTA(E2:I2)=0,"",ROUND(AVERAGE(J2:N2)*100,0))</f>
         <v>100</v>
       </c>
-      <c r="Q2" s="51">
-        <f>IFERROR(AVERAGEIF(C$2:C$171,C2,P$2:P$171),"N/A")</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="P2" s="49">
+        <f>IFERROR(AVERAGEIF(C$2:C$171,C2,O$2:O$171),"N/A")</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>928734</v>
       </c>
-      <c r="B3" s="37">
+      <c r="B3" s="36">
         <v>46283</v>
       </c>
       <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3">
+      <c r="E3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J5" si="1">IF(E3="","",IF(E3="Conformidade",1,IF(E3="Não Conformidade",0,IF(E3="Não Conformidade Grave",-1,""))))</f>
         <v>1</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="K3">
-        <f>IF(F3="","",IF(F3="SIM",1,0))</f>
+        <f>IF(F3="","",IF(F3="Conformidade",1,IF(F3="Não Conformidade",0,IF(F3="Não Conformidade Grave",-1,""))))</f>
         <v>1</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3:L5" si="0">IF(G3="","",IF(G3="SIM",1,0))</f>
+        <f>IF(G3="","",IF(G3="Conformidade",1,IF(G3="Não Conformidade",0,IF(G3="Não Conformidade Grave",-1,""))))</f>
         <v>1</v>
       </c>
       <c r="M3">
-        <f>IF(H3="","",IF(H3="Automático",1,IF(H3="Manual",0.5,IF(H3="Não atualizado",0,""))))</f>
+        <f>IF(H3="","",IF(H3="Conformidade",1,IF(H3="Não Conformidade",0,IF(H3="Não Conformidade Grave",-1,""))))</f>
         <v>1</v>
       </c>
       <c r="N3">
-        <f>IF(I3="","",IF(I3="SIM",1,0))</f>
+        <f>IF(I3="","",IF(I3="Conformidade",1,IF(I3="Não Conformidade",0,IF(I3="Não Conformidade Grave",-1,""))))</f>
         <v>0</v>
       </c>
       <c r="O3">
-        <f>IF(J3="","",IF(J3="Conformidade",1,IF(J3="Não Conformidade",0,IF(J3="Não Conformidade Grave",-1,""))))</f>
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <f>IF(COUNTA(F3:J3)=0,"",ROUND(AVERAGE(K3:O3)*100,0))</f>
-        <v>60</v>
-      </c>
-      <c r="Q3" s="51">
-        <f>IFERROR(AVERAGEIF(C$2:C$171,C3,P$2:P$171),"N/A")</f>
+        <f>IF(COUNTA(E3:I3)=0,"",ROUND(AVERAGE(J3:N3)*100,0))</f>
         <v>80</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="P3" s="49">
+        <f>IFERROR(AVERAGEIF(C$2:C$171,C3,O$2:O$171),"N/A")</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>928734</v>
       </c>
-      <c r="B4" s="37">
+      <c r="B4" s="36">
         <v>46283</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4">
+        <v>34</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="K4">
-        <f>IF(F4="","",IF(F4="SIM",1,0))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="L4">
@@ -4150,59 +4407,56 @@
         <v>1</v>
       </c>
       <c r="M4">
-        <f>IF(H4="","",IF(H4="Automático",1,IF(H4="Manual",0.5,IF(H4="Não atualizado",0,""))))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="N4">
-        <f>IF(I4="","",IF(I4="SIM",1,0))</f>
-        <v>0</v>
+        <f t="shared" ref="N4:N5" si="2">IF(I4="","",IF(I4="Conformidade",1,IF(I4="Não Conformidade",0,IF(I4="Não Conformidade Grave",-1,""))))</f>
+        <v>1</v>
       </c>
       <c r="O4">
-        <f>IF(J4="","",IF(J4="Conformidade",1,IF(J4="Não Conformidade",0,IF(J4="Não Conformidade Grave",-1,""))))</f>
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <f>IF(COUNTA(F4:J4)=0,"",ROUND(AVERAGE(K4:O4)*100,0))</f>
-        <v>60</v>
-      </c>
-      <c r="Q4" s="51">
-        <f>IFERROR(AVERAGEIF(C$2:C$171,C4,P$2:P$171),"N/A")</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+        <f>IF(COUNTA(E4:I4)=0,"",ROUND(AVERAGE(J4:N4)*100,0))</f>
+        <v>100</v>
+      </c>
+      <c r="P4" s="49">
+        <f>IFERROR(AVERAGEIF(C$2:C$171,C4,O$2:O$171),"N/A")</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>928734</v>
       </c>
-      <c r="B5" s="37">
+      <c r="B5" s="36">
         <v>46283</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
+        <v>43</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>72</v>
+        <v>13</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>14</v>
+      <c r="J5">
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="K5">
-        <f>IF(F5="","",IF(F5="SIM",1,0))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="L5">
@@ -4210,940 +4464,1066 @@
         <v>1</v>
       </c>
       <c r="M5">
-        <f>IF(H5="","",IF(H5="Automático",1,IF(H5="Manual",0.5,IF(H5="Não atualizado",0,""))))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="N5">
-        <f>IF(I5="","",IF(I5="SIM",1,0))</f>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="O5">
-        <f>IF(J5="","",IF(J5="Conformidade",1,IF(J5="Não Conformidade",0,IF(J5="Não Conformidade Grave",-1,""))))</f>
-        <v>1</v>
-      </c>
-      <c r="P5">
-        <f>IF(COUNTA(F5:J5)=0,"",ROUND(AVERAGE(K5:O5)*100,0))</f>
-        <v>100</v>
-      </c>
-      <c r="Q5" s="51">
-        <f>IFERROR(AVERAGEIF(C$2:C$171,C5,P$2:P$171),"N/A")</f>
+        <f>IF(COUNTA(E5:I5)=0,"",ROUND(AVERAGE(J5:N5)*100,0))</f>
         <v>80</v>
       </c>
+      <c r="P5" s="49">
+        <f>IFERROR(AVERAGEIF(C$2:C$171,C5,O$2:O$171),"N/A")</f>
+        <v>90</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I2:J5 F2:G5">
-    <cfRule type="cellIs" dxfId="33" priority="3" operator="equal">
+  <conditionalFormatting sqref="E2:I5">
+    <cfRule type="cellIs" dxfId="88" priority="3" operator="equal">
       <formula>"SIM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="4" operator="equal">
       <formula>"NÃO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="H2:H5" xr:uid="{C3BB923A-7C00-4145-9F4D-51BD86D8D251}">
-      <formula1>"Automático,Manual,Não atualizado"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J5" xr:uid="{69B316C6-6E8C-4750-8B48-0B95D02A3253}">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="E2:I5" xr:uid="{417C900A-6A14-4389-8EFE-8723D40E0F04}">
       <formula1>"Não Conformidade Grave,Não Conformidade,Conformidade,Observação"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I5 F2:G5" xr:uid="{99D6AFA3-078F-4A18-8D26-749847694146}">
-      <formula1>"SIM,NÃO"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="M2:M5" formula="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.85546875" style="31" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="49.5703125" style="31" customWidth="1"/>
-    <col min="21" max="21" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="49.5703125" style="30" customWidth="1"/>
+    <col min="18" max="18" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
+    <row r="1" spans="1:20" s="46" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="45" t="s">
+      <c r="D1" s="44" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="45" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="46" t="s">
+        <v>228</v>
+      </c>
+      <c r="G1" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="46" t="s">
-        <v>242</v>
-      </c>
-      <c r="I1" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="46" t="s">
+      <c r="H1" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="46" t="s">
+      <c r="I1" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="46" t="s">
+      <c r="J1" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="46" t="s">
+      <c r="K1" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="46" t="s">
+      <c r="L1" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="46" t="s">
+      <c r="M1" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="46" t="s">
+      <c r="N1" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="46" t="s">
+      <c r="O1" s="45" t="s">
         <v>15</v>
       </c>
+      <c r="P1" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q1" s="47" t="s">
+        <v>17</v>
+      </c>
       <c r="R1" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="S1" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="T1" s="46" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>928734</v>
+      </c>
+      <c r="B2" s="39">
+        <v>46283</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="6">
+        <f>IF(E2="","",IF(E2="Conformidade",1,IF(E2="Não Conformidade",0,IF(E2="Não Conformidade Grave",-1,""))))</f>
+        <v>1</v>
+      </c>
+      <c r="K2" s="6">
+        <f>IF(G2="","",IF(G2="Conformidade",1,IF(G2="Não Conformidade",0,IF(G2="Não Conformidade Grave",-1,""))))</f>
+        <v>1</v>
+      </c>
+      <c r="L2" s="6">
+        <f>IF(H2="","",IF(H2="Conformidade",1,IF(H2="Não Conformidade",0,IF(NH2="Não Conformidade Grave",-1,""))))</f>
+        <v>1</v>
+      </c>
+      <c r="M2" s="6">
+        <f>IF(I2="","",IF(I2="Conformidade",1,IF(I2="Não Conformidade",0,IF(I2="Não Conformidade Grave",-1,""))))</f>
+        <v>1</v>
+      </c>
+      <c r="N2" s="6">
+        <f>IF(COUNTA(E2:G2,H2:I2)=0,"",ROUND(AVERAGE(J2:M2)*100,0))</f>
+        <v>100</v>
+      </c>
+      <c r="O2" s="7">
+        <f>IFERROR(AVERAGEIF(C$2:C$5,C2,N$2:N$5),"N/A")</f>
+        <v>50</v>
+      </c>
+      <c r="P2" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q2" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="R2" t="s">
+        <v>269</v>
+      </c>
+      <c r="S2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>928734</v>
+      </c>
+      <c r="B3" s="39">
+        <v>46283</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="6">
+        <f>IF(E3="","",IF(E3="Conformidade",1,IF(E3="Não Conformidade",0,IF(E3="Não Conformidade Grave",-1,""))))</f>
+        <v>1</v>
+      </c>
+      <c r="K3" s="6">
+        <f>IF(G3="","",IF(G3="Conformidade",1,IF(G3="Não Conformidade",0,IF(G3="Não Conformidade Grave",-1,""))))</f>
+        <v>1</v>
+      </c>
+      <c r="L3" s="6">
+        <f t="shared" ref="L3:L5" si="0">IF(H3="","",IF(H3="Conformidade",1,IF(H3="Não Conformidade",0,IF(NH3="Não Conformidade Grave",-1,""))))</f>
+        <v>1</v>
+      </c>
+      <c r="M3" s="40">
+        <f>IF(I3="","",IF(I3="Conformidade",1,IF(I3="Não Conformidade",0,IF(I3="Não Conformidade Grave",-1,""))))</f>
+        <v>1</v>
+      </c>
+      <c r="N3" s="48">
+        <f>IF(COUNTA(E3:G3,H3:I3)=0,"",ROUND(AVERAGE(J3:M3)*100,0))</f>
+        <v>100</v>
+      </c>
+      <c r="O3" s="7">
+        <f>IFERROR(AVERAGEIF(C$2:C$5,C3,N$2:N$5),"N/A")</f>
+        <v>50</v>
+      </c>
+      <c r="P3" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q3" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="R3" t="s">
+        <v>269</v>
+      </c>
+      <c r="S3" t="s">
+        <v>29</v>
+      </c>
+      <c r="T3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>928734</v>
+      </c>
+      <c r="B4" s="39">
+        <v>46283</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="47" t="s">
+      <c r="G4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="6">
+        <f>IF(E4="","",IF(E4="Conformidade",1,IF(E4="Não Conformidade",0,IF(E4="Não Conformidade Grave",-1,""))))</f>
+        <v>-1</v>
+      </c>
+      <c r="K4" s="6" t="str">
+        <f>IF(G4="","",IF(G4="Conformidade",1,IF(G4="Não Conformidade",0,IF(G4="Não Conformidade Grave",-1,""))))</f>
+        <v/>
+      </c>
+      <c r="L4" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="M4" s="40" t="str">
+        <f>IF(I4="","",IF(I4="Conformidade",1,IF(I4="Não Conformidade",0,IF(I4="Não Conformidade Grave",-1,""))))</f>
+        <v/>
+      </c>
+      <c r="N4" s="48">
+        <f>IF(COUNTA(E4:G4,H4:I4)=0,"",ROUND(AVERAGE(J4:M4)*100,0))</f>
+        <v>-100</v>
+      </c>
+      <c r="O4" s="7">
+        <f>IFERROR(AVERAGEIF(C$2:C$5,C5,N$2:N$5),"N/A")</f>
+        <v>50</v>
+      </c>
+      <c r="P4" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q4" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="R4" t="s">
+        <v>269</v>
+      </c>
+      <c r="S4" t="s">
+        <v>29</v>
+      </c>
+      <c r="T4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>928734</v>
+      </c>
+      <c r="B5" s="39">
+        <v>46283</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
-        <v>928734</v>
-      </c>
-      <c r="B2" s="40">
-        <v>46283</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="48" t="s">
-        <v>74</v>
-      </c>
-      <c r="F2" s="8">
+      <c r="D5" s="56" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="6">
+        <f>IF(E5="","",IF(E5="Conformidade",1,IF(E5="Não Conformidade",0,IF(E5="Não Conformidade Grave",-1,""))))</f>
         <v>1</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="7">
-        <f>IF(G2="","",IF(G2="SIM",1,IF(G2="NÃO",0,"")))</f>
+      <c r="K5" s="6">
+        <f>IF(G5="","",IF(G5="Conformidade",1,IF(G5="Não Conformidade",0,IF(G5="Não Conformidade Grave",-1,""))))</f>
         <v>1</v>
       </c>
-      <c r="N2" s="7">
-        <f t="shared" ref="N2:N4" si="0">IF(I2="","",IF(I2="SIM",1,IF(I2="NÃO",0,"")))</f>
-        <v>1</v>
-      </c>
-      <c r="O2" s="7">
-        <f>IF(K2="","",IF(K2="SIM",1,IF(K2="NÃO",0,"")))</f>
-        <v>1</v>
-      </c>
-      <c r="P2" s="7" t="str">
-        <f>IF(L2="","",IF(L2="Conformidade",1,IF(L2="Não Conformidade",0,IF(L2="Não Conformidade Grave",-1,""))))</f>
-        <v/>
-      </c>
-      <c r="Q2" s="7">
-        <f>IF(COUNTA(G2:I2,K2:L2)=0,"",ROUND(AVERAGE(M2:P2)*100,0))</f>
-        <v>100</v>
-      </c>
-      <c r="R2" s="8">
-        <f>IFERROR(AVERAGEIF(C$2:C$5,C2,Q$2:Q$5),"N/A")</f>
-        <v>62.5</v>
-      </c>
-      <c r="S2" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="T2" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="U2" t="s">
-        <v>283</v>
-      </c>
-      <c r="V2" t="s">
-        <v>32</v>
-      </c>
-      <c r="W2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <v>928734</v>
-      </c>
-      <c r="B3" s="40">
-        <v>46283</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3" s="48" t="s">
-        <v>77</v>
-      </c>
-      <c r="F3" s="8">
-        <v>1</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="M3" s="7">
-        <f>IF(G3="","",IF(G3="SIM",1,IF(G3="NÃO",0,"")))</f>
-        <v>1</v>
-      </c>
-      <c r="N3" s="7">
+      <c r="L5" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="O3" s="7">
-        <f>IF(K3="","",IF(K3="SIM",1,IF(K3="NÃO",0,"")))</f>
+      <c r="M5" s="40">
+        <f>IF(I5="","",IF(I5="Conformidade",1,IF(I5="Não Conformidade",0,IF(I5="Não Conformidade Grave",-1,""))))</f>
         <v>1</v>
       </c>
-      <c r="P3" s="41" t="str">
-        <f>IF(L3="","",IF(L3="Conformidade",1,IF(L3="Não Conformidade",0,IF(L3="Não Conformidade Grave",-1,""))))</f>
-        <v/>
-      </c>
-      <c r="Q3" s="50">
-        <f>IF(COUNTA(G3:I3,K3:L3)=0,"",ROUND(AVERAGE(M3:P3)*100,0))</f>
+      <c r="N5" s="48">
+        <f>IF(COUNTA(E5:G5,H5:I5)=0,"",ROUND(AVERAGE(J5:M5)*100,0))</f>
         <v>100</v>
       </c>
-      <c r="R3" s="8">
-        <f>IFERROR(AVERAGEIF(C$2:C$5,C3,Q$2:Q$5),"N/A")</f>
-        <v>62.5</v>
-      </c>
-      <c r="S3" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="T3" s="31" t="s">
-        <v>79</v>
-      </c>
-      <c r="U3" t="s">
-        <v>283</v>
-      </c>
-      <c r="V3" t="s">
-        <v>32</v>
-      </c>
-      <c r="W3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <v>928734</v>
-      </c>
-      <c r="B4" s="40">
-        <v>46283</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="48" t="s">
-        <v>80</v>
-      </c>
-      <c r="F4" s="8">
-        <v>1</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="60" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="60" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="60" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" s="60" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="M4" s="7">
-        <f>IF(G4="","",IF(G4="SIM",1,IF(G4="NÃO",0,"")))</f>
-        <v>0</v>
-      </c>
-      <c r="N4" s="7" t="str">
-        <f>IF(I4="","",IF(I4="SIM",1,IF(I4="NÃO",0,"")))</f>
-        <v/>
-      </c>
-      <c r="O4" s="7" t="str">
-        <f>IF(K4="","",IF(K4="SIM",1,IF(K4="NÃO",0,"")))</f>
-        <v/>
-      </c>
-      <c r="P4" s="41">
-        <f>IF(L4="","",IF(L4="Conformidade",1,IF(L4="Não Conformidade",0,IF(L4="Não Conformidade Grave",-1,""))))</f>
-        <v>-1</v>
-      </c>
-      <c r="Q4" s="50">
-        <f>IF(COUNTA(G4:I4,K4:L4)=0,"",ROUND(AVERAGE(M4:P4)*100,0))</f>
-        <v>-50</v>
-      </c>
-      <c r="R4" s="8">
-        <f>IFERROR(AVERAGEIF(C$2:C$5,C5,Q$2:Q$5),"N/A")</f>
-        <v>62.5</v>
-      </c>
-      <c r="S4" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="T4" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="U4" t="s">
-        <v>283</v>
-      </c>
-      <c r="V4" t="s">
-        <v>32</v>
-      </c>
-      <c r="W4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <v>928734</v>
-      </c>
-      <c r="B5" s="40">
-        <v>46283</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="58" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="59">
-        <v>0</v>
-      </c>
-      <c r="G5" s="60" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M5" s="7">
-        <f>IF(G5="","",IF(G5="SIM",1,IF(G5="NÃO",0,"")))</f>
-        <v>1</v>
-      </c>
-      <c r="N5" s="7">
-        <f>IF(I5="","",IF(I5="SIM",1,IF(I5="NÃO",0,"")))</f>
-        <v>1</v>
-      </c>
       <c r="O5" s="7">
-        <f>IF(K5="","",IF(K5="SIM",1,IF(K5="NÃO",0,"")))</f>
-        <v>1</v>
-      </c>
-      <c r="P5" s="41">
-        <f>IF(L5="","",IF(L5="Conformidade",1,IF(L5="Não Conformidade",0,IF(L5="Não Conformidade Grave",-1,""))))</f>
-        <v>1</v>
-      </c>
-      <c r="Q5" s="50">
-        <f>IF(COUNTA(G5:I5,K5:L5)=0,"",ROUND(AVERAGE(M5:P5)*100,0))</f>
-        <v>100</v>
-      </c>
-      <c r="R5" s="8">
-        <f>IFERROR(AVERAGEIF(C$2:C$5,C5,Q$2:Q$5),"N/A")</f>
-        <v>62.5</v>
+        <f>IFERROR(AVERAGEIF(C$2:C$5,C5,N$2:N$5),"N/A")</f>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:G5 I2:K3 H4:K4">
-    <cfRule type="cellIs" dxfId="31" priority="7" operator="equal">
+  <conditionalFormatting sqref="M2:N5">
+    <cfRule type="cellIs" dxfId="86" priority="64" operator="lessThan">
+      <formula>50</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="85" priority="65" operator="between">
+      <formula>50</formula>
+      <formula>79</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="84" priority="66" operator="greaterThanOrEqual">
+      <formula>80</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2 H4:I4">
+    <cfRule type="cellIs" dxfId="83" priority="43" operator="equal">
       <formula>"SIM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="44" operator="equal">
       <formula>"NÃO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:Q5">
-    <cfRule type="cellIs" dxfId="29" priority="20" operator="lessThan">
-      <formula>50</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="21" operator="between">
-      <formula>50</formula>
-      <formula>79</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="22" operator="greaterThanOrEqual">
-      <formula>80</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="26" priority="3" operator="equal">
+  <conditionalFormatting sqref="F2">
+    <cfRule type="cellIs" dxfId="81" priority="41" operator="equal">
       <formula>"SIM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="42" operator="equal">
       <formula>"NÃO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:K5">
-    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
+  <conditionalFormatting sqref="G2">
+    <cfRule type="cellIs" dxfId="79" priority="39" operator="equal">
       <formula>"SIM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="40" operator="equal">
       <formula>"NÃO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="5">
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" sqref="F2:F4" xr:uid="{00000000-0002-0000-0200-000000000000}">
-      <formula1>0</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:K5" xr:uid="{00000000-0002-0000-0200-000001000000}">
-      <formula1>"SIM,NÃO"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="L2:L5" xr:uid="{00000000-0002-0000-0200-000002000000}">
-      <formula1>"Não Conformidade Grave,Não Conformidade,Conformidade,Observação"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
+  <conditionalFormatting sqref="H2">
+    <cfRule type="cellIs" dxfId="77" priority="35" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="76" priority="36" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2">
+    <cfRule type="cellIs" dxfId="75" priority="33" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="74" priority="34" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3">
+    <cfRule type="cellIs" dxfId="73" priority="31" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="72" priority="32" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3">
+    <cfRule type="cellIs" dxfId="71" priority="29" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="70" priority="30" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="cellIs" dxfId="69" priority="27" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="68" priority="28" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="cellIs" dxfId="67" priority="23" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="66" priority="24" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I3">
+    <cfRule type="cellIs" dxfId="65" priority="21" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="64" priority="22" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4">
+    <cfRule type="cellIs" dxfId="63" priority="19" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="62" priority="20" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="cellIs" dxfId="61" priority="17" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="60" priority="18" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4">
+    <cfRule type="cellIs" dxfId="59" priority="15" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="58" priority="16" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5">
+    <cfRule type="cellIs" dxfId="57" priority="11" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="56" priority="12" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
+    <cfRule type="cellIs" dxfId="55" priority="9" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="54" priority="10" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5">
+    <cfRule type="cellIs" dxfId="53" priority="7" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="52" priority="8" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5">
+    <cfRule type="cellIs" dxfId="51" priority="3" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="50" priority="4" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I5">
+    <cfRule type="cellIs" dxfId="49" priority="1" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="48" priority="2" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
     <dataValidation type="date" allowBlank="1" sqref="B2:B5" xr:uid="{00000000-0002-0000-0200-000003000000}">
       <formula1>DATE(2000,1,1)</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="V2:V4" xr:uid="{00000000-0002-0000-0200-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="S2:S4" xr:uid="{00000000-0002-0000-0200-000004000000}">
       <formula1>"Aberto,Em andamento,Concluído"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E2:I5" xr:uid="{00000000-0002-0000-0200-000002000000}">
+      <formula1>"Não Conformidade Grave,Não Conformidade,Conformidade,Observação"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="R4" formula="1"/>
+    <ignoredError sqref="O4" formula="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.85546875" style="31" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="72.85546875" style="31" customWidth="1"/>
-    <col min="19" max="19" width="49.5703125" style="31" customWidth="1"/>
-    <col min="20" max="20" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="20.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.85546875" customWidth="1"/>
+    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.85546875" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="72.85546875" style="30" customWidth="1"/>
+    <col min="18" max="18" width="49.5703125" style="30" customWidth="1"/>
+    <col min="19" max="19" width="30.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
+    <row r="1" spans="1:21" s="46" customFormat="1" ht="24" x14ac:dyDescent="0.25">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="45" t="s">
+      <c r="D1" s="44" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="45" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="46" t="s">
+        <v>228</v>
+      </c>
+      <c r="G1" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="46" t="s">
+      <c r="H1" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="46" t="s">
+      <c r="I1" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="46" t="s">
+      <c r="J1" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="46" t="s">
+      <c r="K1" s="45" t="s">
+        <v>273</v>
+      </c>
+      <c r="L1" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="46" t="s">
+      <c r="M1" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="46" t="s">
+      <c r="N1" s="45" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="47" t="s">
+      <c r="P1" s="46" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="49" t="s">
+      <c r="R1" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="49" t="s">
+      <c r="S1" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="47" t="s">
+      <c r="T1" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="47" t="s">
+      <c r="U1" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="47" t="s">
+    </row>
+    <row r="2" spans="1:21" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>928734</v>
+      </c>
+      <c r="B2" s="39">
+        <v>46283</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+      <c r="D2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="59" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="6">
+        <f>IF(E2="","",IF(E2="Conformidade",1,IF(E2="Não Conformidade",0,IF(E2="Não Conformidade Grave",-1,""))))</f>
+        <v>1</v>
+      </c>
+      <c r="K2" s="6">
+        <f>IF(F2="","",IF(F2="Conformidade",1,IF(F2="Não Conformidade",0,IF(F2="Não Conformidade Grave",-1,""))))</f>
+        <v>1</v>
+      </c>
+      <c r="L2" s="6">
+        <f>IF(G2="","",IF(G2="Conformidade",1,IF(G2="Não Conformidade",0,IF(G2="Não Conformidade Grave",-1,""))))</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="6">
+        <f>IF(H2="","",IF(H2="Conformidade",1,IF(H2="Não Conformidade",0,IF(H2="Não Conformidade Grave",-1,""))))</f>
+        <v>1</v>
+      </c>
+      <c r="N2" s="6">
+        <f>IF(I2="","",IF(I2="Conformidade",1,IF(I2="Não Conformidade",0,IF(I2="Não Conformidade Grave",-1,""))))</f>
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <f>IF(COUNTA(E2:G2,H2:I2)=0,"",ROUND(AVERAGE(J2:N2)*100,0))</f>
+        <v>80</v>
+      </c>
+      <c r="P2">
+        <f>IFERROR(AVERAGEIF(C$2:C$202,C2,O$2:O$202),"N/A")</f>
+        <v>45</v>
+      </c>
+      <c r="Q2" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="R2" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" t="s">
+        <v>29</v>
+      </c>
+      <c r="U2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="90" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
         <v>928734</v>
       </c>
-      <c r="B2" s="40">
+      <c r="B3" s="39">
         <v>46283</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="8">
+      <c r="C3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="57" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="6">
+        <f t="shared" ref="J3:J5" si="0">IF(E3="","",IF(E3="Conformidade",1,IF(E3="Não Conformidade",0,IF(E3="Não Conformidade Grave",-1,""))))</f>
         <v>1</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="7">
-        <f>IF(G2="","",IF(G2="SIM",0.5,IF(G2="NÃO",0,"")))</f>
-        <v>0.5</v>
-      </c>
-      <c r="M2" s="7">
-        <f t="shared" ref="L2:M5" si="0">IF(H2="","",IF(H2="SIM",1,IF(H2="NÃO",0,"")))</f>
+      <c r="K3" s="6">
+        <f t="shared" ref="K3:K5" si="1">IF(F3="","",IF(F3="Conformidade",1,IF(F3="Não Conformidade",0,IF(F3="Não Conformidade Grave",-1,""))))</f>
         <v>1</v>
       </c>
-      <c r="N2" s="7">
-        <f>IF(J2="","",IF(J2="SIM",1,IF(J2="NÃO",0,"")))</f>
+      <c r="L3" s="6">
+        <f t="shared" ref="L3:L5" si="2">IF(G3="","",IF(G3="Conformidade",1,IF(G3="Não Conformidade",0,IF(G3="Não Conformidade Grave",-1,""))))</f>
         <v>1</v>
       </c>
-      <c r="O2" s="8">
-        <f>IF(K2="","",IF(K2="Conformidade",1,IF(K2="Não Conformidade",0,IF(K2="Não Conformidade Grave",-1,""))))</f>
+      <c r="M3" s="6">
+        <f t="shared" ref="M3:M5" si="3">IF(H3="","",IF(H3="Conformidade",1,IF(H3="Não Conformidade",0,IF(H3="Não Conformidade Grave",-1,""))))</f>
         <v>1</v>
       </c>
-      <c r="P2">
-        <f>IF(COUNTA(G2:H2,J2:K2)=0,"",ROUND(AVERAGE(L2:O2)*100,0))</f>
-        <v>88</v>
-      </c>
-      <c r="Q2">
-        <f>IFERROR(AVERAGEIF(C$2:C$202,C2,P$2:P$202),"N/A")</f>
-        <v>59.5</v>
-      </c>
-      <c r="R2" s="31" t="s">
+      <c r="N3" s="6">
+        <f t="shared" ref="N3:N5" si="4">IF(I3="","",IF(I3="Conformidade",1,IF(I3="Não Conformidade",0,IF(I3="Não Conformidade Grave",-1,""))))</f>
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <f>IF(COUNTA(E3:G3,H3:I3)=0,"",ROUND(AVERAGE(J3:N3)*100,0))</f>
+        <v>100</v>
+      </c>
+      <c r="P3">
+        <f>IFERROR(AVERAGEIF(C$2:C$202,C3,O$2:O$202),"N/A")</f>
+        <v>45</v>
+      </c>
+      <c r="Q3" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="S3" t="s">
+        <v>28</v>
+      </c>
+      <c r="T3" t="s">
         <v>29</v>
       </c>
-      <c r="S2" s="31" t="s">
+      <c r="U3" t="s">
         <v>30</v>
       </c>
-      <c r="T2" t="s">
+    </row>
+    <row r="4" spans="1:21" ht="90" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>928734</v>
+      </c>
+      <c r="B4" s="39">
+        <v>46283</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="U2" t="s">
-        <v>32</v>
-      </c>
-      <c r="V2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" ht="90" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
-        <v>928734</v>
-      </c>
-      <c r="B3" s="40">
-        <v>46283</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" s="8">
-        <v>1</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L3" s="7">
+      <c r="E4" s="59" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="59" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="6">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="M3" s="41">
-        <f t="shared" si="0"/>
+      <c r="K4" s="6">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N3" s="41">
-        <f>IF(J3="","",IF(J3="SIM",1,IF(J3="NÃO",0,"")))</f>
+      <c r="L4" s="6">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="O3" s="8">
-        <f>IF(K3="","",IF(K3="Conformidade",1,IF(K3="Não Conformidade",0,IF(K3="Não Conformidade Grave",-1,""))))</f>
+      <c r="M4" s="6">
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="P3">
-        <f>IF(COUNTA(G3:H3,J3:K3)=0,"",ROUND(AVERAGE(L3:O3)*100,0))</f>
+      <c r="N4" s="6">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <f>IF(COUNTA(E4:G4,H4:I4)=0,"",ROUND(AVERAGE(J4:N4)*100,0))</f>
         <v>100</v>
       </c>
-      <c r="Q3">
-        <f>IFERROR(AVERAGEIF(C$2:C$202,C3,P$2:P$202),"N/A")</f>
-        <v>59.5</v>
-      </c>
-      <c r="R3" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="S3" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="T3" t="s">
-        <v>31</v>
-      </c>
-      <c r="U3" t="s">
+      <c r="P4">
+        <f>IFERROR(AVERAGEIF(C$2:C$202,C4,O$2:O$202),"N/A")</f>
+        <v>45</v>
+      </c>
+      <c r="Q4" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="V3" t="s">
+      <c r="R4" s="30" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="4" spans="1:22" ht="90" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <v>928734</v>
-      </c>
-      <c r="B4" s="40">
-        <v>46283</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="61" t="s">
-        <v>285</v>
-      </c>
-      <c r="F4" s="8">
-        <v>1</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L4" s="7">
-        <f t="shared" ref="L4" si="1">IF(G4="","",IF(G4="SIM",1,IF(G4="NÃO",0,"")))</f>
-        <v>1</v>
-      </c>
-      <c r="M4" s="41">
-        <f t="shared" ref="M4" si="2">IF(H4="","",IF(H4="SIM",1,IF(H4="NÃO",0,"")))</f>
-        <v>1</v>
-      </c>
-      <c r="N4" s="41">
-        <f>IF(J4="","",IF(J4="SIM",1,IF(J4="NÃO",0,"")))</f>
-        <v>1</v>
-      </c>
-      <c r="O4" s="8">
-        <f>IF(K4="","",IF(K4="Conformidade",1,IF(K4="Não Conformidade",0,IF(K4="Não Conformidade Grave",-1,""))))</f>
-        <v>1</v>
-      </c>
-      <c r="P4">
-        <f>IF(COUNTA(G4:H4,J4:K4)=0,"",ROUND(AVERAGE(L4:O4)*100,0))</f>
-        <v>100</v>
-      </c>
-      <c r="Q4">
-        <f>IFERROR(AVERAGEIF(C$2:C$202,C4,P$2:P$202),"N/A")</f>
-        <v>59.5</v>
-      </c>
-      <c r="R4" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="S4" s="31" t="s">
-        <v>37</v>
+      <c r="S4" t="s">
+        <v>28</v>
       </c>
       <c r="T4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="U4" t="s">
-        <v>32</v>
-      </c>
-      <c r="V4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>928734</v>
       </c>
-      <c r="B5" s="37">
+      <c r="B5" s="36">
         <v>46283</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5" t="str">
+        <v>34</v>
+      </c>
+      <c r="E5" s="59" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="6">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="N5" t="str">
-        <f>IF(J5="","",IF(J5="SIM",1,IF(J5="NÃO",0,"")))</f>
+        <v>-1</v>
+      </c>
+      <c r="K5" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L5" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M5" s="6" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="N5" s="6" t="str">
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O5">
-        <f>IF(K5="","",IF(K5="Conformidade",1,IF(K5="Não Conformidade",0,IF(K5="Não Conformidade Grave",-1,""))))</f>
-        <v>-1</v>
+        <f>IF(COUNTA(E5:G5,H5:I5)=0,"",ROUND(AVERAGE(J5:N5)*100,0))</f>
+        <v>-100</v>
       </c>
       <c r="P5">
-        <f>IF(COUNTA(G5:H5,I5:K5)=0,"",ROUND(AVERAGE(L5:O5)*100,0))</f>
-        <v>-50</v>
-      </c>
-      <c r="Q5">
-        <f>IFERROR(AVERAGEIF(C$2:C$202,C5,P$2:P$202),"N/A")</f>
-        <v>59.5</v>
-      </c>
-      <c r="R5" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="S5" s="31" t="s">
-        <v>41</v>
+        <f>IFERROR(AVERAGEIF(C$2:C$202,C5,O$2:O$202),"N/A")</f>
+        <v>45</v>
+      </c>
+      <c r="Q5" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="R5" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="S5" t="s">
+        <v>37</v>
       </c>
       <c r="T5" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="U5" t="s">
-        <v>32</v>
-      </c>
-      <c r="V5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:J4">
-    <cfRule type="cellIs" dxfId="22" priority="5" operator="equal">
+  <conditionalFormatting sqref="E2:F2">
+    <cfRule type="cellIs" dxfId="47" priority="31" operator="equal">
       <formula>"SIM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="32" operator="equal">
       <formula>"NÃO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:N4">
-    <cfRule type="cellIs" dxfId="20" priority="20" operator="lessThan">
-      <formula>50</formula>
+  <conditionalFormatting sqref="G2">
+    <cfRule type="cellIs" dxfId="45" priority="29" operator="equal">
+      <formula>"SIM"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="21" operator="between">
-      <formula>50</formula>
-      <formula>79</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="22" operator="greaterThanOrEqual">
-      <formula>80</formula>
+    <cfRule type="cellIs" dxfId="44" priority="30" operator="equal">
+      <formula>"NÃO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" sqref="F2:F4" xr:uid="{00000000-0002-0000-0300-000000000000}">
-      <formula1>0</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:J4" xr:uid="{00000000-0002-0000-0300-000001000000}">
-      <formula1>"SIM,NÃO"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="K2:K5" xr:uid="{00000000-0002-0000-0300-000002000000}">
+  <conditionalFormatting sqref="H2">
+    <cfRule type="cellIs" dxfId="43" priority="25" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="42" priority="26" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:F3">
+    <cfRule type="cellIs" dxfId="39" priority="21" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="38" priority="22" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="cellIs" dxfId="37" priority="19" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="36" priority="20" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3">
+    <cfRule type="cellIs" dxfId="35" priority="17" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="34" priority="18" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I3">
+    <cfRule type="cellIs" dxfId="33" priority="15" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="32" priority="16" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4:F4">
+    <cfRule type="cellIs" dxfId="31" priority="13" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="14" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4">
+    <cfRule type="cellIs" dxfId="29" priority="11" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="12" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4">
+    <cfRule type="cellIs" dxfId="27" priority="9" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="10" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4">
+    <cfRule type="cellIs" dxfId="25" priority="7" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="8" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:F5">
+    <cfRule type="cellIs" dxfId="23" priority="5" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="22" priority="6" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5">
+    <cfRule type="cellIs" dxfId="21" priority="3" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="20" priority="4" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5:I5">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+      <formula>"SIM"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
+      <formula>"NÃO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" sqref="E2:H5 I3:I5" xr:uid="{00000000-0002-0000-0300-000002000000}">
       <formula1>"Não Conformidade Grave,Não Conformidade,Conformidade,Observação"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation type="date" allowBlank="1" sqref="B2:B4" xr:uid="{00000000-0002-0000-0300-000003000000}">
       <formula1>DATE(2000,1,1)</formula1>
       <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="I2" xr:uid="{C9313753-9CCA-42D4-90B8-F92E160C63F1}">
+      <formula1>"Não Conformidade Grave,Não Conformidade,Conformidade,"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5166,477 +5546,477 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="50" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+    </row>
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="11">
+        <f>COUNT(Documentos!O2:O49)</f>
+        <v>5</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="12"/>
+    </row>
+    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" s="11">
+        <f>COUNTIF(Treinamento!J2:J5,"Conformidade")</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" s="12"/>
+    </row>
+    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="11">
+        <f>COUNTIF(Documentos!G2:G49,"SIM")</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-    </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="F6" s="13"/>
+    </row>
+    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B7" s="11">
+        <f>COUNTIF(Documentos!H2:H49,"SIM")</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="E7" t="s">
         <v>86</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="F7" s="13"/>
+    </row>
+    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="B8" s="11">
+        <f>IFERROR(COUNTIF(Documentos!I2:I49,"Conformidade")-COUNTIF(Documentos!I2:I49,"Não Conformidade Grave"),"")</f>
+        <v>4</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B4" s="12">
-        <f>COUNT(Documentos!P2:P49)</f>
-        <v>5</v>
-      </c>
-      <c r="D4" s="11" t="s">
+      <c r="E8" t="s">
         <v>89</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F8" s="14"/>
+    </row>
+    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="F4" s="13"/>
-    </row>
-    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+      <c r="B9" s="15">
+        <f>IFERROR(AVERAGE(Documentos!O2:O49),0)</f>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="12">
-        <f>COUNTIF(Documentos!G2:G49,"SIM")</f>
-        <v>5</v>
-      </c>
-      <c r="D5" s="11" t="s">
+      <c r="B10" s="16">
+        <f>IFERROR(COUNTIF(Documentos!E2:E49,"SIM")/COUNTA(Documentos!E2:E49),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="E5" t="s">
+      <c r="B11" s="16">
+        <f>IFERROR(COUNTIF(Documentos!G2:G49,"SIM")/COUNTA(Documentos!G2:G49),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="F5" s="13"/>
-    </row>
-    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+    </row>
+    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="B6" s="12">
-        <f>COUNTIF(Documentos!H2:H49,"SIM")</f>
+      <c r="B12" s="16">
+        <f>IFERROR(COUNTIF(Documentos!H2:H49,"SIM")/COUNTA(Documentos!H2:H49),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+    </row>
+    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+    </row>
+    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+    </row>
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D15" s="51"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+    </row>
+    <row r="17" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" s="51"/>
+    </row>
+    <row r="18" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="B18" s="19">
+        <f>COUNT(Indicadores!O2:O201)</f>
         <v>4</v>
       </c>
-      <c r="D6" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" t="s">
-        <v>96</v>
-      </c>
-      <c r="F6" s="14"/>
-    </row>
-    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="B7" s="12">
-        <f>COUNTIF(Documentos!J2:J49,"SIM")</f>
-        <v>3</v>
-      </c>
-      <c r="D7" s="11" t="s">
+    </row>
+    <row r="19" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="E7" t="s">
+      <c r="B19" s="19">
+        <f>COUNTIF(Indicadores!E2:E201,"SIM")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="B20" s="19">
+        <f>COUNTIF(Indicadores!I2:I201,"SIM")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="F7" s="14"/>
-    </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="B21" s="19">
+        <f>COUNTIF(Indicadores!G2:G201,"SIM")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="B8" s="12">
-        <f>IFERROR(COUNTIF(Documentos!K2:K49,"Conformidade")-COUNTIF(Documentos!K2:K49,"Não Conformidade Grave"),"")</f>
-        <v>2</v>
-      </c>
-      <c r="D8" s="11" t="s">
+      <c r="B22" s="19">
+        <f>IFERROR(COUNTIF(Indicadores!H2:H201,"Conformidade")*1+COUNTIF(Indicadores!H2:H201,"Não Conformidade")*0+COUNTIF(Indicadores!H2:H201,"Não Conformidade Grave")*-1,"")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="E8" t="s">
+      <c r="B23" s="20">
+        <f>IFERROR(AVERAGE(Indicadores!O2:O201),0)</f>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" s="21">
+        <f>IFERROR(COUNTIF(Indicadores!F2:F201,"SIM")/COUNTA(Indicadores!F2:F201),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="F8" s="15"/>
-    </row>
-    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="B9" s="16">
-        <f>IFERROR(AVERAGE(Documentos!P2:P49),0)</f>
-        <v>76.8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B10" s="17">
-        <f>IFERROR(COUNTIF(Documentos!G2:G49,"SIM")/COUNTA(Documentos!G2:G49),0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="B11" s="17">
-        <f>IFERROR(COUNTIF(Documentos!H2:H49,"SIM")/COUNTA(Documentos!H2:H49),0)</f>
-        <v>0.8</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="B12" s="17">
-        <f>IFERROR(COUNTIF(Documentos!J2:J49,"SIM")/COUNTA(Documentos!J2:J49),0)</f>
-        <v>0.6</v>
-      </c>
-      <c r="D12" s="54" t="s">
-        <v>108</v>
-      </c>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-    </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-    </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="53"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53"/>
-    </row>
-    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="53"/>
-    </row>
-    <row r="17" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="55" t="s">
-        <v>109</v>
-      </c>
-      <c r="B17" s="53"/>
-    </row>
-    <row r="18" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="B18" s="20">
-        <f>COUNT(Indicadores!P2:P201)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="B19" s="20">
-        <f>COUNTIF(Indicadores!F2:F201,"SIM")</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="B20" s="20">
-        <f>COUNTIF(Indicadores!H2:H201,"Automático")+COUNTIF(Indicadores!H2:H201,"Manual")</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="B21" s="20">
-        <f>COUNTIF(Indicadores!I2:I201,"SIM")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="B22" s="20">
-        <f>IFERROR(COUNTIF(Indicadores!J2:J201,"Conformidade")*1+COUNTIF(Indicadores!J2:J201,"Não Conformidade")*0+COUNTIF(Indicadores!J2:J201,"Não Conformidade Grave")*-1,"")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="B23" s="21">
-        <f>IFERROR(AVERAGE(Indicadores!P2:P201),0)</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="B24" s="22">
+      <c r="B25" s="21">
+        <f>IFERROR(COUNTIF(Indicadores!I2:I201,"SIM")/COUNTA(Indicadores!I2:I201),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26" s="21">
         <f>IFERROR(COUNTIF(Indicadores!G2:G201,"SIM")/COUNTA(Indicadores!G2:G201),0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="B25" s="22">
-        <f>IFERROR((COUNTIF(Indicadores!H2:H201,"Automático")+COUNTIF(Indicadores!H2:H201,"Manual"))/COUNTA(Indicadores!H2:H201),0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="B26" s="22">
-        <f>IFERROR(COUNTIF(Indicadores!I2:I201,"SIM")/COUNTA(Indicadores!I2:I201),0)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:2" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="55" t="s">
-        <v>117</v>
-      </c>
-      <c r="B28" s="53"/>
+      <c r="A28" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="B28" s="51"/>
     </row>
     <row r="29" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="B29" s="20">
-        <f>COUNT(Treinamento!Q2:Q5)</f>
+      <c r="A29" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="B29" s="19">
+        <f>COUNT(Treinamento!N2:N5)</f>
         <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="B30" s="20">
+      <c r="A30" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="B30" s="19">
+        <f>COUNTIF(Treinamento!E2:E5,"SIM")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="B31" s="19">
         <f>COUNTIF(Treinamento!G2:G5,"SIM")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" s="19">
+        <f>COUNTIF(Treinamento!H2:H5,"SIM")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="B33" s="19">
+        <f>COUNTIF(Treinamento!I2:I5,"Conformidade")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="B31" s="20">
-        <f>COUNTIF(Treinamento!I2:I5,"SIM")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="B32" s="20">
-        <f>COUNTIF(Treinamento!K2:K5,"SIM")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="B33" s="20">
-        <f>COUNTIF(Treinamento!L2:L5,"Conformidade")</f>
-        <v>1</v>
-      </c>
-    </row>
     <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="B34" s="21">
-        <f>IFERROR(AVERAGE(Treinamento!Q2:Q5),0)</f>
-        <v>62.5</v>
+      <c r="A34" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="B34" s="20">
+        <f>IFERROR(AVERAGE(Treinamento!N2:N5),0)</f>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="B35" s="22">
-        <f>IFERROR(COUNTIF(Treinamento!G2:G5,"SIM")/COUNTA(Treinamento!G2:G5),0)</f>
-        <v>0.75</v>
+      <c r="A35" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B35" s="21">
+        <f>IFERROR(COUNTIF(Treinamento!E2:E5,"SIM")/COUNTA(Treinamento!E2:E5),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="B36" s="22">
-        <f>IFERROR(COUNTIF(Treinamento!I2:I5,"SIM")/COUNTIF(Treinamento!I2:I5,"&lt;&gt;N/A"),0)</f>
-        <v>1</v>
+      <c r="A36" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="21">
+        <f>IFERROR(COUNTIF(Treinamento!G2:G5,"SIM")/COUNTIF(Treinamento!G2:G5,"&lt;&gt;N/A"),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="B37" s="22">
-        <f>IFERROR(COUNTIF(Treinamento!K2:K5,"SIM")/COUNTIF(Treinamento!K2:K5,"&lt;&gt;N/A"),0)</f>
-        <v>1</v>
+      <c r="A37" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="B37" s="21">
+        <f>IFERROR(COUNTIF(Treinamento!H2:H5,"SIM")/COUNTIF(Treinamento!H2:H5,"&lt;&gt;N/A"),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="55" t="s">
-        <v>124</v>
-      </c>
-      <c r="B39" s="53"/>
+      <c r="A39" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="B39" s="51"/>
     </row>
     <row r="40" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="B40" s="20">
-        <f>COUNT(Qualidade!P2:P5)</f>
+      <c r="A40" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="B40" s="19">
+        <f>COUNT(Qualidade!O2:O5)</f>
         <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="B41" s="20">
+      <c r="A41" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="B41" s="19">
+        <f>COUNTIF(Qualidade!E2:E5,"SIM")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="B42" s="19">
         <f>COUNTIF(Qualidade!G2:G5,"SIM")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="B43" s="19">
+        <f>COUNTIF(Qualidade!H2:H5,"SIM")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="B44" s="19">
+        <f>COUNTIF(Qualidade!I2:I5,"Conformidade")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="B42" s="20">
-        <f>COUNTIF(Qualidade!H2:H5,"SIM")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="B43" s="20">
-        <f>COUNTIF(Qualidade!J2:J5,"SIM")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="B44" s="20">
-        <f>COUNTIF(Qualidade!K2:K5,"Conformidade")</f>
-        <v>3</v>
-      </c>
-    </row>
     <row r="45" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="B45" s="21">
-        <f>IFERROR(AVERAGE(Qualidade!P2:P5),0)</f>
-        <v>59.5</v>
+      <c r="A45" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="B45" s="20">
+        <f>IFERROR(AVERAGE(Qualidade!O2:O5),0)</f>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="B46" s="22">
-        <f>IFERROR(COUNTIF(Qualidade!G2:G5,"SIM")/COUNTA(Qualidade!G2:G5),0)</f>
-        <v>0.75</v>
+      <c r="A46" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" s="21">
+        <f>IFERROR(COUNTIF(Qualidade!E2:E5,"SIM")/COUNTA(Qualidade!E2:E5),0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="48" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="55" t="s">
-        <v>131</v>
-      </c>
-      <c r="B48" s="53"/>
-      <c r="C48" s="53"/>
-      <c r="D48" s="53"/>
-      <c r="E48" s="53"/>
+      <c r="A48" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="B48" s="51"/>
+      <c r="C48" s="51"/>
+      <c r="D48" s="51"/>
+      <c r="E48" s="51"/>
     </row>
     <row r="49" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="B49" s="21">
+      <c r="A49" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="B49" s="20">
         <f>B9</f>
-        <v>76.8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="B50" s="21">
+      <c r="A50" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B50" s="20">
         <f>B23</f>
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="B51" s="21">
+      <c r="A51" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="B51" s="20">
         <f>B34</f>
-        <v>62.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="B52" s="21">
+      <c r="A52" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="B52" s="20">
         <f>B45</f>
-        <v>59.5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="54" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="B54" s="24">
+      <c r="A54" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B54" s="23">
         <f>IFERROR(AVERAGE(B49:B52),0)</f>
-        <v>69.7</v>
+        <v>67.25</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6685,33 +7065,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="52" t="s">
-        <v>136</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
+      <c r="A1" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="C3" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="D3" s="25" t="s">
-        <v>140</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="F3" s="25" t="s">
-        <v>142</v>
+      <c r="A3" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6719,19 +7099,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6739,517 +7119,517 @@
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+    </row>
+    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="54" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" s="51"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+    </row>
+    <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="E19" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="41.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="E21" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="F21" s="25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" s="4" t="s">
+      <c r="F22" s="25" t="s">
         <v>176</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-    </row>
-    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="B17" s="53"/>
-      <c r="C17" s="53"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="53"/>
-      <c r="F17" s="53"/>
-    </row>
-    <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>180</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>181</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>183</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="D19" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="E19" s="26" t="s">
-        <v>165</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="41.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="C20" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="E20" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="F20" s="26" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="C21" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>188</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="F22" s="26" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="56" t="s">
-        <v>117</v>
-      </c>
-      <c r="B24" s="53"/>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="53"/>
-      <c r="F24" s="53"/>
+      <c r="A24" s="54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B24" s="51"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="26" t="s">
-        <v>191</v>
-      </c>
-      <c r="B25" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="C25" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="E25" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>194</v>
+      <c r="A25" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="F25" s="25" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="B26" s="26" t="s">
-        <v>196</v>
-      </c>
-      <c r="C26" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>197</v>
-      </c>
-      <c r="F26" s="26" t="s">
-        <v>25</v>
+      <c r="A26" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="B26" s="25" t="s">
+        <v>182</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="F26" s="25" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="B27" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="C27" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="D27" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="E27" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="F27" s="26" t="s">
-        <v>25</v>
+      <c r="A27" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="F27" s="25" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="B28" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C28" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="D28" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="E28" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="F28" s="26" t="s">
-        <v>27</v>
+      <c r="A28" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="B28" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="E28" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="F28" s="25" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="26" t="s">
-        <v>133</v>
-      </c>
-      <c r="B29" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="C29" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="D29" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="E29" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="F29" s="26" t="s">
+      <c r="A29" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="E29" s="25" t="s">
         <v>190</v>
+      </c>
+      <c r="F29" s="25" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="56" t="s">
-        <v>124</v>
-      </c>
-      <c r="B31" s="53"/>
-      <c r="C31" s="53"/>
-      <c r="D31" s="53"/>
-      <c r="E31" s="53"/>
-      <c r="F31" s="53"/>
+      <c r="A31" s="54" t="s">
+        <v>110</v>
+      </c>
+      <c r="B31" s="51"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="51"/>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="B32" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="C32" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="D32" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="E32" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="F32" s="26" t="s">
-        <v>155</v>
+      <c r="A32" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="B32" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="D32" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="F32" s="25" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="26" t="s">
-        <v>208</v>
-      </c>
-      <c r="B33" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="C33" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="D33" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="E33" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="F33" s="26" t="s">
-        <v>25</v>
+      <c r="A33" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="B33" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="D33" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="E33" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="F33" s="25" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="B34" s="26" t="s">
-        <v>212</v>
-      </c>
-      <c r="C34" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="D34" s="26" t="s">
-        <v>145</v>
-      </c>
-      <c r="E34" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="F34" s="26" t="s">
-        <v>214</v>
+      <c r="A34" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="E34" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="F34" s="25" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="B35" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="C35" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="D35" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="E35" s="26" t="s">
-        <v>215</v>
-      </c>
-      <c r="F35" s="26" t="s">
-        <v>190</v>
+      <c r="A35" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="C35" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="D35" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="E35" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="F35" s="25" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8245,390 +8625,390 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="52" t="s">
-        <v>216</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
+      <c r="A1" s="50" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="C3" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="D3" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="F3" s="25" t="s">
-        <v>221</v>
-      </c>
-      <c r="G3" s="25" t="s">
-        <v>17</v>
+      <c r="A3" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="D4" s="42">
+        <v>209</v>
+      </c>
+      <c r="D4" s="41">
         <v>0.33329999999999999</v>
       </c>
-      <c r="E4" s="42">
-        <f>IFERROR(COUNTIF(Documentos!G2:G3,"SIM")/COUNTA(Documentos!G2:G3)*D4,0)</f>
-        <v>0.33329999999999999</v>
+      <c r="E4" s="41">
+        <f>IFERROR(COUNTIF(Documentos!E2:E3,"SIM")/COUNTA(Documentos!E2:E3)*D4,0)</f>
+        <v>0</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="D5" s="42">
+        <v>209</v>
+      </c>
+      <c r="D5" s="41">
         <v>0.33329999999999999</v>
       </c>
-      <c r="E5" s="42">
-        <f>IFERROR(COUNTIF(Documentos!H2:H3,"SIM")/COUNTA(Documentos!H2:H3)*D5,0)</f>
-        <v>0.33329999999999999</v>
+      <c r="E5" s="41">
+        <f>IFERROR(COUNTIF(Documentos!G2:G3,"SIM")/COUNTA(Documentos!G2:G3)*D5,0)</f>
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="D6" s="42">
+        <v>209</v>
+      </c>
+      <c r="D6" s="41">
         <v>0.33339999999999997</v>
       </c>
-      <c r="E6" s="42">
-        <f>IFERROR(COUNTIF(Documentos!J2:J3,"SIM")/COUNTA(Documentos!J2:J3)*D6,0)</f>
+      <c r="E6" s="41">
+        <f>IFERROR(COUNTIF(Documentos!H2:H3,"SIM")/COUNTA(Documentos!H2:H3)*D6,0)</f>
         <v>0</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E8" s="27" t="s">
-        <v>232</v>
-      </c>
-      <c r="F8" s="28">
+      <c r="E8" s="26" t="s">
+        <v>218</v>
+      </c>
+      <c r="F8" s="27">
         <f>SUM(E4:E6)*100</f>
-        <v>66.66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="56" t="s">
-        <v>233</v>
-      </c>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
+      <c r="A10" s="54" t="s">
+        <v>219</v>
+      </c>
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
     </row>
     <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="D11" s="44">
+      <c r="A11" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="D11" s="43">
         <v>0.33329999999999999</v>
       </c>
-      <c r="E11" s="43">
+      <c r="E11" s="42">
         <f>IFERROR(COUNTIF(#REF!,"SIM")/COUNTA(#REF!)*D11,0)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>234</v>
+      <c r="F11" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="41.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>235</v>
-      </c>
-      <c r="D12" s="44">
+      <c r="A12" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="D12" s="43">
         <v>0.33329999999999999</v>
       </c>
-      <c r="E12" s="43">
+      <c r="E12" s="42">
         <f>IFERROR((COUNTIF(#REF!,"Automático")+COUNTIF(#REF!,"Manual")*0.5)/COUNTA(#REF!)*D12,0)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="G12" s="26" t="s">
-        <v>236</v>
+      <c r="F12" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="26" t="s">
-        <v>227</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="D13" s="44">
+      <c r="A13" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="D13" s="43">
         <v>0.33339999999999997</v>
       </c>
-      <c r="E13" s="43">
+      <c r="E13" s="42">
         <f>IFERROR(COUNTIF(#REF!,"SIM")/COUNTA(#REF!)*D13,0)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="G13" s="26" t="s">
-        <v>237</v>
+      <c r="F13" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E14" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="F14" s="29">
+      <c r="E14" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="F14" s="28">
         <f>SUM(E11:E13)*100</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="56" t="s">
-        <v>238</v>
-      </c>
-      <c r="B16" s="53"/>
-      <c r="C16" s="53"/>
-      <c r="D16" s="53"/>
-      <c r="E16" s="53"/>
-      <c r="F16" s="53"/>
-      <c r="G16" s="53"/>
+      <c r="A16" s="54" t="s">
+        <v>224</v>
+      </c>
+      <c r="B16" s="51"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="51"/>
     </row>
     <row r="17" spans="1:7" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
-        <v>239</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>240</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="D17" s="44">
+      <c r="A17" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="D17" s="43">
         <v>0.33329999999999999</v>
       </c>
-      <c r="E17" s="43">
-        <f>IFERROR(COUNTIF(Treinamento!G2:G4,"SIM")/COUNTA(Treinamento!G2:G4)*D17,0)</f>
-        <v>0.22219999999999998</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="G17" s="26" t="s">
-        <v>241</v>
+      <c r="E17" s="42">
+        <f>IFERROR(COUNTIF(Treinamento!E2:E4,"SIM")/COUNTA(Treinamento!E2:E4)*D17,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>198</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="D18" s="44">
+      <c r="A18" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="D18" s="43">
         <v>0.33329999999999999</v>
       </c>
-      <c r="E18" s="43">
-        <f>IFERROR(COUNTIF(Treinamento!I2:I4,"SIM")/COUNTA(Treinamento!I2:I4)*D18,0)</f>
-        <v>0.22219999999999998</v>
-      </c>
-      <c r="F18" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="G18" s="26" t="s">
-        <v>243</v>
+      <c r="E18" s="42">
+        <f>IFERROR(COUNTIF(Treinamento!G2:G4,"SIM")/COUNTA(Treinamento!G2:G4)*D18,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="G18" s="25" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>201</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="D19" s="44">
+      <c r="A19" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="D19" s="43">
         <v>0.33339999999999997</v>
       </c>
-      <c r="E19" s="43">
-        <f>IFERROR(COUNTIF(Treinamento!J2:J4,"SIM")/COUNTA(Treinamento!J2:J4)*D19,0)</f>
+      <c r="E19" s="42">
+        <f>IFERROR(COUNTIF(Treinamento!#REF!,"SIM")/COUNTA(Treinamento!#REF!)*D19,0)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="G19" s="26" t="s">
-        <v>244</v>
+      <c r="F19" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="G19" s="25" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E20" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="F20" s="29">
+      <c r="E20" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="F20" s="28">
         <f>SUM(E17:E19)*100</f>
-        <v>44.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="56" t="s">
-        <v>245</v>
-      </c>
-      <c r="B22" s="53"/>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="53"/>
-      <c r="G22" s="53"/>
+      <c r="A22" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="B22" s="51"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+      <c r="E22" s="51"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="B23" s="26" t="s">
-        <v>208</v>
-      </c>
-      <c r="C23" s="26" t="s">
-        <v>223</v>
-      </c>
-      <c r="D23" s="44">
+      <c r="A23" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="D23" s="43">
         <v>0.5</v>
       </c>
-      <c r="E23" s="43">
-        <f>IFERROR(COUNTIF(Qualidade!G2:G3,"SIM")/COUNTA(Qualidade!G2:G3)*D23,0)</f>
+      <c r="E23" s="42">
+        <f>IFERROR(COUNTIF(Qualidade!E2:E3,"SIM")/COUNTA(Qualidade!E2:E3)*D23,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="G23" s="25" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="D24" s="43">
         <v>0.5</v>
       </c>
-      <c r="F23" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="G23" s="26" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="26" t="s">
-        <v>247</v>
-      </c>
-      <c r="B24" s="26" t="s">
-        <v>211</v>
-      </c>
-      <c r="C24" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="D24" s="44">
-        <v>0.5</v>
-      </c>
-      <c r="E24" s="43">
-        <f>IFERROR((COUNTIF(Qualidade!H2:H3,"Integral")+COUNTIF(Qualidade!H2:H3,"Amostral")*0.5)/COUNTA(Qualidade!H2:H3)*D24,0)</f>
+      <c r="E24" s="42">
+        <f>IFERROR((COUNTIF(Qualidade!G2:G3,"Integral")+COUNTIF(Qualidade!G2:G3,"Amostral")*0.5)/COUNTA(Qualidade!G2:G3)*D24,0)</f>
         <v>0</v>
       </c>
-      <c r="F24" s="26" t="s">
-        <v>224</v>
-      </c>
-      <c r="G24" s="26" t="s">
-        <v>249</v>
+      <c r="F24" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="G24" s="25" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E25" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="F25" s="29">
+      <c r="E25" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="F25" s="28">
         <f>SUM(E23:E24)*100</f>
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9631,150 +10011,150 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
+      <c r="A1" s="50" t="s">
+        <v>236</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="29" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="55.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="30" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="31" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>258</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="32" t="s">
+        <v>260</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>261</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="C16" s="33" t="s">
         <v>265</v>
       </c>
-      <c r="B8" s="4" t="s">
+    </row>
+    <row r="17" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="32" t="s">
         <v>266</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="B17" s="32" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="30" t="s">
+      <c r="C17" s="33" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="55.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="31" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="32" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="33" t="s">
-        <v>271</v>
-      </c>
-      <c r="B14" s="33" t="s">
-        <v>272</v>
-      </c>
-      <c r="C14" s="34" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="33" t="s">
-        <v>274</v>
-      </c>
-      <c r="B15" s="33" t="s">
-        <v>275</v>
-      </c>
-      <c r="C15" s="34" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="33" t="s">
-        <v>277</v>
-      </c>
-      <c r="B16" s="33" t="s">
-        <v>278</v>
-      </c>
-      <c r="C16" s="34" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="28.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="33" t="s">
-        <v>280</v>
-      </c>
-      <c r="B17" s="33" t="s">
-        <v>281</v>
-      </c>
-      <c r="C17" s="34" t="s">
-        <v>282</v>
-      </c>
-    </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="35"/>
+      <c r="A19" s="34"/>
     </row>
     <row r="20" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="57"/>
-      <c r="B20" s="53"/>
-      <c r="C20" s="53"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="53"/>
-      <c r="F20" s="53"/>
+      <c r="A20" s="55"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
